--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.37</v>
+        <v>2.75</v>
       </c>
       <c r="F14" t="n">
-        <v>12.9</v>
+        <v>12.27</v>
       </c>
       <c r="G14" t="n">
-        <v>202.3</v>
+        <v>213.2</v>
       </c>
       <c r="H14" t="n">
-        <v>41.1</v>
+        <v>38.8</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-22.7</v>
+        <v>49.61</v>
       </c>
       <c r="K14" t="n">
-        <v>51.69</v>
+        <v>58.27</v>
       </c>
       <c r="L14" t="n">
-        <v>56.46</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:51:36</t>
+          <t>05:50:39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.29</v>
+        <v>3.07</v>
       </c>
       <c r="F15" t="n">
-        <v>12.09</v>
+        <v>13.46</v>
       </c>
       <c r="G15" t="n">
-        <v>216.6</v>
+        <v>211.9</v>
       </c>
       <c r="H15" t="n">
-        <v>30.8</v>
+        <v>42</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-45.95</v>
+        <v>17.32</v>
       </c>
       <c r="K15" t="n">
-        <v>105.57</v>
+        <v>63.96</v>
       </c>
       <c r="L15" t="n">
-        <v>115.14</v>
+        <v>66.26000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:53:16</t>
+          <t>05:52:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.94</v>
+        <v>3.81</v>
       </c>
       <c r="F16" t="n">
-        <v>13.42</v>
+        <v>13.81</v>
       </c>
       <c r="G16" t="n">
-        <v>229.9</v>
+        <v>221.2</v>
       </c>
       <c r="H16" t="n">
-        <v>29.4</v>
+        <v>36.6</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>248.77</v>
+        <v>252.29</v>
       </c>
       <c r="K16" t="n">
-        <v>-18.06</v>
+        <v>-33.41</v>
       </c>
       <c r="L16" t="n">
-        <v>249.43</v>
+        <v>254.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:58:08</t>
+          <t>05:56:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>3.49</v>
       </c>
       <c r="F17" t="n">
-        <v>12.88</v>
+        <v>12.63</v>
       </c>
       <c r="G17" t="n">
-        <v>198.6</v>
+        <v>229</v>
       </c>
       <c r="H17" t="n">
-        <v>37</v>
+        <v>40.2</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>110.1</v>
+        <v>-242.18</v>
       </c>
       <c r="K17" t="n">
-        <v>-20.39</v>
+        <v>-95.09</v>
       </c>
       <c r="L17" t="n">
-        <v>111.97</v>
+        <v>260.18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:58:51</t>
+          <t>05:58:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="F18" t="n">
-        <v>12.68</v>
+        <v>12.95</v>
       </c>
       <c r="G18" t="n">
-        <v>214.5</v>
+        <v>236.1</v>
       </c>
       <c r="H18" t="n">
-        <v>38.3</v>
+        <v>45.4</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>4.56</v>
+        <v>216.52</v>
       </c>
       <c r="K18" t="n">
-        <v>-33.16</v>
+        <v>239.06</v>
       </c>
       <c r="L18" t="n">
-        <v>33.48</v>
+        <v>322.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:01:03</t>
+          <t>06:00:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="F19" t="n">
-        <v>12.97</v>
+        <v>12.98</v>
       </c>
       <c r="G19" t="n">
-        <v>222.7</v>
+        <v>210</v>
       </c>
       <c r="H19" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.74</v>
+        <v>64.2</v>
       </c>
       <c r="K19" t="n">
-        <v>-201.08</v>
+        <v>-43.11</v>
       </c>
       <c r="L19" t="n">
-        <v>201.2</v>
+        <v>77.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:06:34</t>
+          <t>06:06:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.77</v>
+        <v>2.83</v>
       </c>
       <c r="F20" t="n">
-        <v>12.94</v>
+        <v>12.91</v>
       </c>
       <c r="G20" t="n">
-        <v>219.8</v>
+        <v>214.4</v>
       </c>
       <c r="H20" t="n">
-        <v>38.2</v>
+        <v>41.4</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>86.68000000000001</v>
+        <v>-221.43</v>
       </c>
       <c r="K20" t="n">
-        <v>-235.9</v>
+        <v>-231.88</v>
       </c>
       <c r="L20" t="n">
-        <v>251.32</v>
+        <v>320.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:07:41</t>
+          <t>06:08:59</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="F21" t="n">
-        <v>12.73</v>
+        <v>13.32</v>
       </c>
       <c r="G21" t="n">
-        <v>218.9</v>
+        <v>222.2</v>
       </c>
       <c r="H21" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-262.54</v>
+        <v>356.08</v>
       </c>
       <c r="K21" t="n">
-        <v>319.28</v>
+        <v>205.97</v>
       </c>
       <c r="L21" t="n">
-        <v>413.36</v>
+        <v>411.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:08:30</t>
+          <t>06:11:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -964,31 +964,31 @@
         <v>3.96</v>
       </c>
       <c r="F22" t="n">
-        <v>13.15</v>
+        <v>13.56</v>
       </c>
       <c r="G22" t="n">
-        <v>213.2</v>
+        <v>205</v>
       </c>
       <c r="H22" t="n">
-        <v>39.1</v>
+        <v>39.6</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>166.23</v>
+        <v>-143.3</v>
       </c>
       <c r="K22" t="n">
-        <v>326.96</v>
+        <v>-396.67</v>
       </c>
       <c r="L22" t="n">
-        <v>366.79</v>
+        <v>421.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:11:23</t>
+          <t>06:15:46</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="F23" t="n">
-        <v>13.37</v>
+        <v>12.33</v>
       </c>
       <c r="G23" t="n">
-        <v>227.1</v>
+        <v>215.6</v>
       </c>
       <c r="H23" t="n">
-        <v>37.5</v>
+        <v>41.9</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>161.11</v>
+        <v>-362.78</v>
       </c>
       <c r="K23" t="n">
-        <v>-305.68</v>
+        <v>-473.1</v>
       </c>
       <c r="L23" t="n">
-        <v>345.54</v>
+        <v>596.1799999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:13:30</t>
+          <t>06:18:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.44</v>
+        <v>3.73</v>
       </c>
       <c r="F24" t="n">
-        <v>12.74</v>
+        <v>13.06</v>
       </c>
       <c r="G24" t="n">
-        <v>226</v>
+        <v>212.1</v>
       </c>
       <c r="H24" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-137.99</v>
+        <v>-60.82</v>
       </c>
       <c r="K24" t="n">
-        <v>-110.88</v>
+        <v>268.77</v>
       </c>
       <c r="L24" t="n">
-        <v>177.02</v>
+        <v>275.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:14:54</t>
+          <t>06:19:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.61</v>
+        <v>3.44</v>
       </c>
       <c r="F25" t="n">
-        <v>13.11</v>
+        <v>13.42</v>
       </c>
       <c r="G25" t="n">
-        <v>224.1</v>
+        <v>222.3</v>
       </c>
       <c r="H25" t="n">
-        <v>33.8</v>
+        <v>30.3</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>115.49</v>
+        <v>685.2</v>
       </c>
       <c r="K25" t="n">
-        <v>-299.48</v>
+        <v>-511.42</v>
       </c>
       <c r="L25" t="n">
-        <v>320.98</v>
+        <v>855.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:18:23</t>
+          <t>06:24:24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="F26" t="n">
-        <v>12.9</v>
+        <v>12.58</v>
       </c>
       <c r="G26" t="n">
-        <v>216.2</v>
+        <v>215</v>
       </c>
       <c r="H26" t="n">
-        <v>36.3</v>
+        <v>40.4</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>-59.65</v>
+        <v>21.81</v>
       </c>
       <c r="K26" t="n">
-        <v>420.61</v>
+        <v>-266.42</v>
       </c>
       <c r="L26" t="n">
-        <v>424.82</v>
+        <v>267.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:20:05</t>
+          <t>06:26:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.48</v>
+        <v>3.83</v>
       </c>
       <c r="F27" t="n">
-        <v>12.68</v>
+        <v>12.63</v>
       </c>
       <c r="G27" t="n">
-        <v>218.9</v>
+        <v>213.1</v>
       </c>
       <c r="H27" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-511.33</v>
+        <v>-32.07</v>
       </c>
       <c r="K27" t="n">
-        <v>-644.88</v>
+        <v>-917.8</v>
       </c>
       <c r="L27" t="n">
-        <v>823</v>
+        <v>918.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:21:10</t>
+          <t>06:27:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="F28" t="n">
-        <v>12.44</v>
+        <v>13.02</v>
       </c>
       <c r="G28" t="n">
-        <v>221.2</v>
+        <v>232.6</v>
       </c>
       <c r="H28" t="n">
-        <v>36.7</v>
+        <v>34.2</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>337.11</v>
+        <v>723.73</v>
       </c>
       <c r="K28" t="n">
-        <v>392.87</v>
+        <v>631.71</v>
       </c>
       <c r="L28" t="n">
-        <v>517.6799999999999</v>
+        <v>960.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:32:55</t>
+          <t>06:39:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.73</v>
+        <v>3.3</v>
       </c>
       <c r="F29" t="n">
-        <v>12.72</v>
+        <v>13.34</v>
       </c>
       <c r="G29" t="n">
-        <v>213.2</v>
+        <v>222.3</v>
       </c>
       <c r="H29" t="n">
-        <v>36.4</v>
+        <v>30.9</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-94.03</v>
+        <v>2.63</v>
       </c>
       <c r="K29" t="n">
-        <v>-130.21</v>
+        <v>148.73</v>
       </c>
       <c r="L29" t="n">
-        <v>160.61</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:34:39</t>
+          <t>06:40:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1300,31 +1300,31 @@
         <v>3.2</v>
       </c>
       <c r="F30" t="n">
-        <v>12.17</v>
+        <v>12.77</v>
       </c>
       <c r="G30" t="n">
-        <v>214.3</v>
+        <v>214.4</v>
       </c>
       <c r="H30" t="n">
-        <v>41.6</v>
+        <v>35.4</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>128.93</v>
+        <v>-39.83</v>
       </c>
       <c r="K30" t="n">
-        <v>10.49</v>
+        <v>-48.5</v>
       </c>
       <c r="L30" t="n">
-        <v>129.36</v>
+        <v>62.76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:36:04</t>
+          <t>06:41:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="F31" t="n">
-        <v>13.35</v>
+        <v>13.29</v>
       </c>
       <c r="G31" t="n">
-        <v>224.6</v>
+        <v>225.6</v>
       </c>
       <c r="H31" t="n">
-        <v>43.9</v>
+        <v>34.1</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>76.90000000000001</v>
+        <v>-67.75</v>
       </c>
       <c r="K31" t="n">
-        <v>-134.19</v>
+        <v>-116.02</v>
       </c>
       <c r="L31" t="n">
-        <v>154.67</v>
+        <v>134.36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:40:13</t>
+          <t>06:47:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.46</v>
+        <v>3.84</v>
       </c>
       <c r="F32" t="n">
-        <v>13.08</v>
+        <v>14.05</v>
       </c>
       <c r="G32" t="n">
-        <v>221.2</v>
+        <v>218.5</v>
       </c>
       <c r="H32" t="n">
-        <v>40.3</v>
+        <v>38.6</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>120.68</v>
+        <v>-491.8</v>
       </c>
       <c r="K32" t="n">
-        <v>23.8</v>
+        <v>-123.02</v>
       </c>
       <c r="L32" t="n">
-        <v>123.01</v>
+        <v>506.96</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:41:17</t>
+          <t>06:49:53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.97</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>13.07</v>
+        <v>13.39</v>
       </c>
       <c r="G33" t="n">
-        <v>226.3</v>
+        <v>211.2</v>
       </c>
       <c r="H33" t="n">
-        <v>40.3</v>
+        <v>34.9</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>87.18000000000001</v>
+        <v>177.8</v>
       </c>
       <c r="K33" t="n">
-        <v>194.05</v>
+        <v>1.5</v>
       </c>
       <c r="L33" t="n">
-        <v>212.73</v>
+        <v>177.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:43:36</t>
+          <t>06:51:26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.33</v>
+        <v>4.11</v>
       </c>
       <c r="F34" t="n">
-        <v>13.16</v>
+        <v>12.69</v>
       </c>
       <c r="G34" t="n">
-        <v>222.7</v>
+        <v>223.5</v>
       </c>
       <c r="H34" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="I34" t="n">
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-213.43</v>
+        <v>-2.32</v>
       </c>
       <c r="K34" t="n">
-        <v>17.51</v>
+        <v>-71.84999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>214.14</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:47:20</t>
+          <t>06:56:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="F35" t="n">
-        <v>12.92</v>
+        <v>13.1</v>
       </c>
       <c r="G35" t="n">
-        <v>216.9</v>
+        <v>225.2</v>
       </c>
       <c r="H35" t="n">
-        <v>38.9</v>
+        <v>37.1</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.54</v>
+        <v>-653.6900000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>60.71</v>
+        <v>439.24</v>
       </c>
       <c r="L35" t="n">
-        <v>61.07</v>
+        <v>787.5599999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:49:06</t>
+          <t>06:57:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.37</v>
+        <v>3.67</v>
       </c>
       <c r="F36" t="n">
-        <v>13.16</v>
+        <v>12</v>
       </c>
       <c r="G36" t="n">
-        <v>208.8</v>
+        <v>213.4</v>
       </c>
       <c r="H36" t="n">
-        <v>44.3</v>
+        <v>41.7</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-558.46</v>
+        <v>-30.58</v>
       </c>
       <c r="K36" t="n">
-        <v>195.97</v>
+        <v>131.95</v>
       </c>
       <c r="L36" t="n">
-        <v>591.84</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:50:49</t>
+          <t>06:59:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.18</v>
+        <v>3.29</v>
       </c>
       <c r="F37" t="n">
-        <v>12.23</v>
+        <v>13.18</v>
       </c>
       <c r="G37" t="n">
-        <v>215.4</v>
+        <v>217.2</v>
       </c>
       <c r="H37" t="n">
-        <v>38.4</v>
+        <v>42.4</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-392</v>
+        <v>218.21</v>
       </c>
       <c r="K37" t="n">
-        <v>-224.31</v>
+        <v>-233.46</v>
       </c>
       <c r="L37" t="n">
-        <v>451.64</v>
+        <v>319.56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:54:44</t>
+          <t>07:04:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.52</v>
+        <v>2.49</v>
       </c>
       <c r="F38" t="n">
-        <v>12.59</v>
+        <v>12.4</v>
       </c>
       <c r="G38" t="n">
-        <v>222.1</v>
+        <v>210.4</v>
       </c>
       <c r="H38" t="n">
-        <v>49.6</v>
+        <v>37.6</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>310.27</v>
+        <v>-74.40000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>55.96</v>
+        <v>7.44</v>
       </c>
       <c r="L38" t="n">
-        <v>315.27</v>
+        <v>74.77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:56:39</t>
+          <t>07:05:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.69</v>
+        <v>2.82</v>
       </c>
       <c r="F39" t="n">
-        <v>12.94</v>
+        <v>12.47</v>
       </c>
       <c r="G39" t="n">
-        <v>220.9</v>
+        <v>219.7</v>
       </c>
       <c r="H39" t="n">
-        <v>35.5</v>
+        <v>37.7</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-192.24</v>
+        <v>-131.07</v>
       </c>
       <c r="K39" t="n">
-        <v>106.61</v>
+        <v>-207.1</v>
       </c>
       <c r="L39" t="n">
-        <v>219.82</v>
+        <v>245.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:58:39</t>
+          <t>07:06:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.04</v>
+        <v>3.17</v>
       </c>
       <c r="F40" t="n">
-        <v>12.73</v>
+        <v>13.32</v>
       </c>
       <c r="G40" t="n">
-        <v>214.5</v>
+        <v>216.9</v>
       </c>
       <c r="H40" t="n">
-        <v>35</v>
+        <v>46.4</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>24.2</v>
+        <v>-135.21</v>
       </c>
       <c r="K40" t="n">
-        <v>-481.77</v>
+        <v>-257.99</v>
       </c>
       <c r="L40" t="n">
-        <v>482.38</v>
+        <v>291.27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:03:19</t>
+          <t>07:12:06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.26</v>
+        <v>4.36</v>
       </c>
       <c r="F41" t="n">
-        <v>13.1</v>
+        <v>11.86</v>
       </c>
       <c r="G41" t="n">
-        <v>215.2</v>
+        <v>228.3</v>
       </c>
       <c r="H41" t="n">
-        <v>31</v>
+        <v>36.9</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>9.57</v>
+        <v>214.98</v>
       </c>
       <c r="K41" t="n">
-        <v>-368.14</v>
+        <v>-508.49</v>
       </c>
       <c r="L41" t="n">
-        <v>368.27</v>
+        <v>552.0700000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:05:41</t>
+          <t>07:12:57</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="F42" t="n">
-        <v>13.05</v>
+        <v>13.12</v>
       </c>
       <c r="G42" t="n">
-        <v>218.9</v>
+        <v>226.4</v>
       </c>
       <c r="H42" t="n">
-        <v>45.4</v>
+        <v>33.6</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>159.31</v>
+        <v>-18.41</v>
       </c>
       <c r="K42" t="n">
-        <v>154.85</v>
+        <v>320.88</v>
       </c>
       <c r="L42" t="n">
-        <v>222.17</v>
+        <v>321.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:08:00</t>
+          <t>07:14:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.65</v>
+        <v>4.77</v>
       </c>
       <c r="F43" t="n">
-        <v>12.5</v>
+        <v>12.41</v>
       </c>
       <c r="G43" t="n">
-        <v>214.2</v>
+        <v>234.9</v>
       </c>
       <c r="H43" t="n">
-        <v>41.4</v>
+        <v>39.3</v>
       </c>
       <c r="I43" t="n">
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>307.18</v>
+        <v>-25.5</v>
       </c>
       <c r="K43" t="n">
-        <v>-39.99</v>
+        <v>342.53</v>
       </c>
       <c r="L43" t="n">
-        <v>309.77</v>
+        <v>343.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:17:49</t>
+          <t>07:25:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.52</v>
+        <v>2.78</v>
       </c>
       <c r="F44" t="n">
-        <v>13.52</v>
+        <v>13.17</v>
       </c>
       <c r="G44" t="n">
-        <v>221.7</v>
+        <v>225.7</v>
       </c>
       <c r="H44" t="n">
-        <v>33.9</v>
+        <v>37.8</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>76.88</v>
+        <v>-139.01</v>
       </c>
       <c r="K44" t="n">
-        <v>-332.92</v>
+        <v>-104.26</v>
       </c>
       <c r="L44" t="n">
-        <v>341.68</v>
+        <v>173.76</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:19:59</t>
+          <t>07:27:18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.23</v>
+        <v>4.16</v>
       </c>
       <c r="F45" t="n">
-        <v>13.25</v>
+        <v>13.82</v>
       </c>
       <c r="G45" t="n">
-        <v>207.9</v>
+        <v>211.2</v>
       </c>
       <c r="H45" t="n">
-        <v>30.5</v>
+        <v>39.1</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-115.34</v>
+        <v>129.87</v>
       </c>
       <c r="K45" t="n">
-        <v>-103.34</v>
+        <v>227.7</v>
       </c>
       <c r="L45" t="n">
-        <v>154.86</v>
+        <v>262.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:21:03</t>
+          <t>07:30:09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.71</v>
+        <v>5.54</v>
       </c>
       <c r="F46" t="n">
-        <v>13.23</v>
+        <v>12.7</v>
       </c>
       <c r="G46" t="n">
-        <v>213.8</v>
+        <v>219.9</v>
       </c>
       <c r="H46" t="n">
-        <v>39.6</v>
+        <v>43.7</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>41.12</v>
+        <v>-214.85</v>
       </c>
       <c r="K46" t="n">
-        <v>57.22</v>
+        <v>-394.36</v>
       </c>
       <c r="L46" t="n">
-        <v>70.45999999999999</v>
+        <v>449.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:24:52</t>
+          <t>07:34:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.84</v>
+        <v>4.29</v>
       </c>
       <c r="F47" t="n">
         <v>12.98</v>
       </c>
       <c r="G47" t="n">
-        <v>224.5</v>
+        <v>208.7</v>
       </c>
       <c r="H47" t="n">
-        <v>38.8</v>
+        <v>45.8</v>
       </c>
       <c r="I47" t="n">
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-8.300000000000001</v>
+        <v>148.54</v>
       </c>
       <c r="K47" t="n">
-        <v>222.82</v>
+        <v>-51.16</v>
       </c>
       <c r="L47" t="n">
-        <v>222.97</v>
+        <v>157.11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:26:00</t>
+          <t>07:35:37</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.25</v>
+        <v>4.88</v>
       </c>
       <c r="F48" t="n">
-        <v>13.5</v>
+        <v>13.66</v>
       </c>
       <c r="G48" t="n">
-        <v>227.9</v>
+        <v>222.9</v>
       </c>
       <c r="H48" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>61.15</v>
+        <v>297.59</v>
       </c>
       <c r="K48" t="n">
-        <v>81.15000000000001</v>
+        <v>-219.22</v>
       </c>
       <c r="L48" t="n">
-        <v>101.61</v>
+        <v>369.61</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:27:55</t>
+          <t>07:37:57</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="F49" t="n">
-        <v>13.08</v>
+        <v>13.75</v>
       </c>
       <c r="G49" t="n">
-        <v>219.9</v>
+        <v>221.2</v>
       </c>
       <c r="H49" t="n">
         <v>39.4</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>147.91</v>
+        <v>-167.52</v>
       </c>
       <c r="K49" t="n">
-        <v>132.31</v>
+        <v>-215.88</v>
       </c>
       <c r="L49" t="n">
-        <v>198.45</v>
+        <v>273.26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:32:36</t>
+          <t>07:41:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.78</v>
+        <v>3.89</v>
       </c>
       <c r="F50" t="n">
-        <v>13.08</v>
+        <v>12.83</v>
       </c>
       <c r="G50" t="n">
-        <v>221.7</v>
+        <v>217.7</v>
       </c>
       <c r="H50" t="n">
-        <v>39.7</v>
+        <v>35.6</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>385.86</v>
+        <v>-213.37</v>
       </c>
       <c r="K50" t="n">
-        <v>279.09</v>
+        <v>-682.0599999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>476.21</v>
+        <v>714.65</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:34:56</t>
+          <t>07:44:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.4</v>
+        <v>3.21</v>
       </c>
       <c r="F51" t="n">
-        <v>12.54</v>
+        <v>13.33</v>
       </c>
       <c r="G51" t="n">
-        <v>213.8</v>
+        <v>235.4</v>
       </c>
       <c r="H51" t="n">
-        <v>35.5</v>
+        <v>33.6</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>192.98</v>
+        <v>55.24</v>
       </c>
       <c r="K51" t="n">
-        <v>68.70999999999999</v>
+        <v>-101.77</v>
       </c>
       <c r="L51" t="n">
-        <v>204.85</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:37:03</t>
+          <t>07:45:56</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.13</v>
+        <v>3.4</v>
       </c>
       <c r="F52" t="n">
-        <v>12.98</v>
+        <v>13.09</v>
       </c>
       <c r="G52" t="n">
-        <v>216.3</v>
+        <v>203.9</v>
       </c>
       <c r="H52" t="n">
-        <v>39.8</v>
+        <v>41.9</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-169.05</v>
+        <v>-88.58</v>
       </c>
       <c r="K52" t="n">
-        <v>-324.56</v>
+        <v>503.31</v>
       </c>
       <c r="L52" t="n">
-        <v>365.94</v>
+        <v>511.05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:42:03</t>
+          <t>07:51:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.43</v>
+        <v>4.77</v>
       </c>
       <c r="F53" t="n">
-        <v>12.25</v>
+        <v>12.63</v>
       </c>
       <c r="G53" t="n">
-        <v>212.5</v>
+        <v>214.8</v>
       </c>
       <c r="H53" t="n">
-        <v>40.6</v>
+        <v>37.1</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>20.49</v>
+        <v>799.24</v>
       </c>
       <c r="K53" t="n">
-        <v>-381.49</v>
+        <v>603.63</v>
       </c>
       <c r="L53" t="n">
-        <v>382.04</v>
+        <v>1001.58</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:44:06</t>
+          <t>07:52:13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.15</v>
+        <v>4.27</v>
       </c>
       <c r="F54" t="n">
-        <v>12.61</v>
+        <v>13.43</v>
       </c>
       <c r="G54" t="n">
-        <v>232.3</v>
+        <v>204.8</v>
       </c>
       <c r="H54" t="n">
-        <v>37.5</v>
+        <v>34.4</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-222.81</v>
+        <v>204.29</v>
       </c>
       <c r="K54" t="n">
-        <v>-198.6</v>
+        <v>-187.99</v>
       </c>
       <c r="L54" t="n">
-        <v>298.48</v>
+        <v>277.63</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:46:43</t>
+          <t>07:53:53</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.74</v>
+        <v>4.51</v>
       </c>
       <c r="F55" t="n">
-        <v>13.26</v>
+        <v>13.71</v>
       </c>
       <c r="G55" t="n">
-        <v>207.7</v>
+        <v>222.4</v>
       </c>
       <c r="H55" t="n">
-        <v>39</v>
+        <v>31.1</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>349.86</v>
+        <v>375.21</v>
       </c>
       <c r="K55" t="n">
-        <v>117.08</v>
+        <v>-38.87</v>
       </c>
       <c r="L55" t="n">
-        <v>368.93</v>
+        <v>377.22</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:52:25</t>
+          <t>07:58:33</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.89</v>
+        <v>4.01</v>
       </c>
       <c r="F56" t="n">
-        <v>12.99</v>
+        <v>12.81</v>
       </c>
       <c r="G56" t="n">
-        <v>231.1</v>
+        <v>213.6</v>
       </c>
       <c r="H56" t="n">
-        <v>39.6</v>
+        <v>35.8</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>462.91</v>
+        <v>-858.03</v>
       </c>
       <c r="K56" t="n">
-        <v>-245.89</v>
+        <v>282.78</v>
       </c>
       <c r="L56" t="n">
-        <v>524.16</v>
+        <v>903.4299999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:53:41</t>
+          <t>08:00:23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="F57" t="n">
-        <v>12.42</v>
+        <v>13.18</v>
       </c>
       <c r="G57" t="n">
-        <v>219.3</v>
+        <v>230.4</v>
       </c>
       <c r="H57" t="n">
-        <v>36.7</v>
+        <v>41.9</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-132.03</v>
+        <v>346.94</v>
       </c>
       <c r="K57" t="n">
-        <v>44.13</v>
+        <v>555.8</v>
       </c>
       <c r="L57" t="n">
-        <v>139.21</v>
+        <v>655.1900000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:55:31</t>
+          <t>08:00:53</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.35</v>
+        <v>4.19</v>
       </c>
       <c r="F58" t="n">
-        <v>12.91</v>
+        <v>12.68</v>
       </c>
       <c r="G58" t="n">
-        <v>227</v>
+        <v>225.8</v>
       </c>
       <c r="H58" t="n">
-        <v>38.1</v>
+        <v>45.1</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>638.61</v>
+        <v>377.32</v>
       </c>
       <c r="K58" t="n">
-        <v>-240.74</v>
+        <v>594.14</v>
       </c>
       <c r="L58" t="n">
-        <v>682.48</v>
+        <v>703.83</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:04:21</t>
+          <t>08:10:08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="F59" t="n">
-        <v>12.71</v>
+        <v>13.01</v>
       </c>
       <c r="G59" t="n">
-        <v>210.6</v>
+        <v>233.7</v>
       </c>
       <c r="H59" t="n">
-        <v>33.7</v>
+        <v>42.4</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-51.33</v>
+        <v>24.28</v>
       </c>
       <c r="K59" t="n">
-        <v>-18.11</v>
+        <v>238.35</v>
       </c>
       <c r="L59" t="n">
-        <v>54.43</v>
+        <v>239.58</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:06:24</t>
+          <t>08:11:02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.94</v>
+        <v>4.09</v>
       </c>
       <c r="F60" t="n">
-        <v>12.56</v>
+        <v>12.74</v>
       </c>
       <c r="G60" t="n">
-        <v>215.6</v>
+        <v>215</v>
       </c>
       <c r="H60" t="n">
-        <v>43.5</v>
+        <v>46.2</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>273.12</v>
+        <v>215.07</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.24</v>
+        <v>254.44</v>
       </c>
       <c r="L60" t="n">
-        <v>273.14</v>
+        <v>333.16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:08:37</t>
+          <t>08:12:56</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.52</v>
+        <v>4.17</v>
       </c>
       <c r="F61" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="G61" t="n">
-        <v>226.3</v>
+        <v>211.5</v>
       </c>
       <c r="H61" t="n">
-        <v>35.3</v>
+        <v>37.3</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-78.38</v>
+        <v>-125.22</v>
       </c>
       <c r="K61" t="n">
-        <v>-102.74</v>
+        <v>53.51</v>
       </c>
       <c r="L61" t="n">
-        <v>129.23</v>
+        <v>136.17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:14:05</t>
+          <t>08:18:10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.6</v>
+        <v>3.29</v>
       </c>
       <c r="F62" t="n">
-        <v>12.29</v>
+        <v>13.08</v>
       </c>
       <c r="G62" t="n">
-        <v>219.6</v>
+        <v>226.7</v>
       </c>
       <c r="H62" t="n">
-        <v>35.6</v>
+        <v>36.9</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>20.16</v>
+        <v>-182.52</v>
       </c>
       <c r="K62" t="n">
-        <v>108.09</v>
+        <v>-123.88</v>
       </c>
       <c r="L62" t="n">
-        <v>109.95</v>
+        <v>220.59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:15:30</t>
+          <t>08:19:53</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="F63" t="n">
-        <v>12.99</v>
+        <v>13.03</v>
       </c>
       <c r="G63" t="n">
-        <v>217.6</v>
+        <v>212.5</v>
       </c>
       <c r="H63" t="n">
-        <v>38.9</v>
+        <v>40.2</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-50.95</v>
+        <v>-87.75</v>
       </c>
       <c r="K63" t="n">
-        <v>107.87</v>
+        <v>-12.65</v>
       </c>
       <c r="L63" t="n">
-        <v>119.3</v>
+        <v>88.65000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:16:17</t>
+          <t>08:22:02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.24</v>
+        <v>4.36</v>
       </c>
       <c r="F64" t="n">
-        <v>13.56</v>
+        <v>13.19</v>
       </c>
       <c r="G64" t="n">
-        <v>218.6</v>
+        <v>227.6</v>
       </c>
       <c r="H64" t="n">
-        <v>39</v>
+        <v>37.1</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>146.43</v>
+        <v>270.93</v>
       </c>
       <c r="K64" t="n">
-        <v>205.44</v>
+        <v>-271.02</v>
       </c>
       <c r="L64" t="n">
-        <v>252.29</v>
+        <v>383.21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:19:50</t>
+          <t>08:28:05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="F65" t="n">
-        <v>13.19</v>
+        <v>12.88</v>
       </c>
       <c r="G65" t="n">
-        <v>220.4</v>
+        <v>217.3</v>
       </c>
       <c r="H65" t="n">
-        <v>37.8</v>
+        <v>35.3</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>30.68</v>
+        <v>-19.59</v>
       </c>
       <c r="K65" t="n">
-        <v>403.81</v>
+        <v>609.58</v>
       </c>
       <c r="L65" t="n">
-        <v>404.97</v>
+        <v>609.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:22:12</t>
+          <t>08:29:42</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="F66" t="n">
-        <v>12.85</v>
+        <v>12.19</v>
       </c>
       <c r="G66" t="n">
-        <v>210.1</v>
+        <v>216.2</v>
       </c>
       <c r="H66" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-442.11</v>
+        <v>-347.19</v>
       </c>
       <c r="K66" t="n">
-        <v>-16.17</v>
+        <v>177.44</v>
       </c>
       <c r="L66" t="n">
-        <v>442.41</v>
+        <v>389.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:23:47</t>
+          <t>08:30:51</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.98</v>
+        <v>4.8</v>
       </c>
       <c r="F67" t="n">
-        <v>13.09</v>
+        <v>12.52</v>
       </c>
       <c r="G67" t="n">
-        <v>207.3</v>
+        <v>202.9</v>
       </c>
       <c r="H67" t="n">
-        <v>35.2</v>
+        <v>38.6</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>165.86</v>
+        <v>135.47</v>
       </c>
       <c r="K67" t="n">
-        <v>-24.33</v>
+        <v>-644.34</v>
       </c>
       <c r="L67" t="n">
-        <v>167.64</v>
+        <v>658.4299999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:28:11</t>
+          <t>08:34:53</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="F68" t="n">
-        <v>13.47</v>
+        <v>13.18</v>
       </c>
       <c r="G68" t="n">
-        <v>217.8</v>
+        <v>216.4</v>
       </c>
       <c r="H68" t="n">
-        <v>36.9</v>
+        <v>42.5</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>236.08</v>
+        <v>307.02</v>
       </c>
       <c r="K68" t="n">
-        <v>419.05</v>
+        <v>309.82</v>
       </c>
       <c r="L68" t="n">
-        <v>480.97</v>
+        <v>436.18</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:30:05</t>
+          <t>08:36:33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.04</v>
+        <v>4.14</v>
       </c>
       <c r="F69" t="n">
-        <v>12.9</v>
+        <v>12.39</v>
       </c>
       <c r="G69" t="n">
-        <v>225.8</v>
+        <v>228.6</v>
       </c>
       <c r="H69" t="n">
-        <v>37.3</v>
+        <v>35.4</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-136.36</v>
+        <v>-75.61</v>
       </c>
       <c r="K69" t="n">
-        <v>-322.93</v>
+        <v>184.68</v>
       </c>
       <c r="L69" t="n">
-        <v>350.54</v>
+        <v>199.55</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:31:57</t>
+          <t>08:38:10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.47</v>
+        <v>4.37</v>
       </c>
       <c r="F70" t="n">
-        <v>13.27</v>
+        <v>12.94</v>
       </c>
       <c r="G70" t="n">
-        <v>216.5</v>
+        <v>214</v>
       </c>
       <c r="H70" t="n">
-        <v>34.3</v>
+        <v>38.8</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-400.95</v>
+        <v>178.93</v>
       </c>
       <c r="K70" t="n">
-        <v>586.89</v>
+        <v>-500.01</v>
       </c>
       <c r="L70" t="n">
-        <v>710.77</v>
+        <v>531.0700000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:36:15</t>
+          <t>08:42:37</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="F71" t="n">
-        <v>12.4</v>
+        <v>12.11</v>
       </c>
       <c r="G71" t="n">
-        <v>235.3</v>
+        <v>217</v>
       </c>
       <c r="H71" t="n">
-        <v>44.7</v>
+        <v>34.3</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>174.26</v>
+        <v>750.6799999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>-629.6900000000001</v>
+        <v>-660.6799999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>653.36</v>
+        <v>1000.01</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:37:39</t>
+          <t>08:44:22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.76</v>
+        <v>3.51</v>
       </c>
       <c r="F72" t="n">
-        <v>12.39</v>
+        <v>13.18</v>
       </c>
       <c r="G72" t="n">
-        <v>216.8</v>
+        <v>233.3</v>
       </c>
       <c r="H72" t="n">
-        <v>36.1</v>
+        <v>42.2</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-274.14</v>
+        <v>-73.76000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>318.71</v>
+        <v>773.63</v>
       </c>
       <c r="L72" t="n">
-        <v>420.39</v>
+        <v>777.14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:39:18</t>
+          <t>08:46:12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.39</v>
+        <v>3.99</v>
       </c>
       <c r="F73" t="n">
-        <v>12.48</v>
+        <v>13.34</v>
       </c>
       <c r="G73" t="n">
-        <v>216.6</v>
+        <v>227.7</v>
       </c>
       <c r="H73" t="n">
-        <v>36.7</v>
+        <v>32.3</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>376.61</v>
+        <v>-726.3200000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>218.55</v>
+        <v>-542.25</v>
       </c>
       <c r="L73" t="n">
-        <v>435.43</v>
+        <v>906.41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:49:44</t>
+          <t>08:54:07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.87</v>
+        <v>4.45</v>
       </c>
       <c r="F74" t="n">
-        <v>12.79</v>
+        <v>13.03</v>
       </c>
       <c r="G74" t="n">
-        <v>214.1</v>
+        <v>218.2</v>
       </c>
       <c r="H74" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>-100.63</v>
+        <v>70.13</v>
       </c>
       <c r="K74" t="n">
-        <v>64.29000000000001</v>
+        <v>-12.47</v>
       </c>
       <c r="L74" t="n">
-        <v>119.41</v>
+        <v>71.23</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:52:02</t>
+          <t>08:55:40</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="F75" t="n">
-        <v>13.07</v>
+        <v>13.55</v>
       </c>
       <c r="G75" t="n">
-        <v>212.3</v>
+        <v>216.2</v>
       </c>
       <c r="H75" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-71.81999999999999</v>
+        <v>166.84</v>
       </c>
       <c r="K75" t="n">
-        <v>-63.31</v>
+        <v>371.5</v>
       </c>
       <c r="L75" t="n">
-        <v>95.73999999999999</v>
+        <v>407.25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:53:25</t>
+          <t>08:57:15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.52</v>
+        <v>4.01</v>
       </c>
       <c r="F76" t="n">
         <v>13.13</v>
       </c>
       <c r="G76" t="n">
-        <v>217.2</v>
+        <v>219.5</v>
       </c>
       <c r="H76" t="n">
-        <v>28.2</v>
+        <v>36.8</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>80.98</v>
+        <v>-74.01000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>13.46</v>
+        <v>325.78</v>
       </c>
       <c r="L76" t="n">
-        <v>82.09</v>
+        <v>334.08</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:58:19</t>
+          <t>09:01:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.31</v>
+        <v>4.08</v>
       </c>
       <c r="F77" t="n">
-        <v>13.23</v>
+        <v>13.77</v>
       </c>
       <c r="G77" t="n">
-        <v>200.6</v>
+        <v>231</v>
       </c>
       <c r="H77" t="n">
-        <v>46.4</v>
+        <v>41.9</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-342.46</v>
+        <v>-65.05</v>
       </c>
       <c r="K77" t="n">
-        <v>112.24</v>
+        <v>-384.39</v>
       </c>
       <c r="L77" t="n">
-        <v>360.39</v>
+        <v>389.86</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:00:21</t>
+          <t>09:03:41</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.48</v>
+        <v>3.78</v>
       </c>
       <c r="F78" t="n">
-        <v>13.49</v>
+        <v>13.03</v>
       </c>
       <c r="G78" t="n">
-        <v>222.4</v>
+        <v>207</v>
       </c>
       <c r="H78" t="n">
-        <v>36.7</v>
+        <v>33.8</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-114.65</v>
+        <v>-50.82</v>
       </c>
       <c r="K78" t="n">
-        <v>95.39</v>
+        <v>162.42</v>
       </c>
       <c r="L78" t="n">
-        <v>149.14</v>
+        <v>170.19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:02:30</t>
+          <t>09:05:25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.96</v>
+        <v>4.43</v>
       </c>
       <c r="F79" t="n">
-        <v>13.27</v>
+        <v>12.82</v>
       </c>
       <c r="G79" t="n">
-        <v>218.7</v>
+        <v>225.6</v>
       </c>
       <c r="H79" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>370.94</v>
+        <v>311.43</v>
       </c>
       <c r="K79" t="n">
-        <v>190.28</v>
+        <v>-189.05</v>
       </c>
       <c r="L79" t="n">
-        <v>416.9</v>
+        <v>364.32</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:07:14</t>
+          <t>09:11:09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.91</v>
+        <v>4.79</v>
       </c>
       <c r="F80" t="n">
-        <v>14.01</v>
+        <v>12.47</v>
       </c>
       <c r="G80" t="n">
-        <v>217.4</v>
+        <v>213.2</v>
       </c>
       <c r="H80" t="n">
-        <v>31.2</v>
+        <v>39.4</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-185.49</v>
+        <v>374.53</v>
       </c>
       <c r="K80" t="n">
-        <v>-31.98</v>
+        <v>-242.12</v>
       </c>
       <c r="L80" t="n">
-        <v>188.22</v>
+        <v>445.98</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:08:29</t>
+          <t>09:13:01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.06</v>
+        <v>5.79</v>
       </c>
       <c r="F81" t="n">
-        <v>12.73</v>
+        <v>13.06</v>
       </c>
       <c r="G81" t="n">
-        <v>210.5</v>
+        <v>221.2</v>
       </c>
       <c r="H81" t="n">
         <v>41.2</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>87.72</v>
+        <v>0.45</v>
       </c>
       <c r="K81" t="n">
-        <v>89.90000000000001</v>
+        <v>-249.74</v>
       </c>
       <c r="L81" t="n">
-        <v>125.61</v>
+        <v>249.74</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:11:07</t>
+          <t>09:14:34</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.75</v>
+        <v>3.73</v>
       </c>
       <c r="F82" t="n">
-        <v>13.1</v>
+        <v>13.42</v>
       </c>
       <c r="G82" t="n">
-        <v>213.8</v>
+        <v>217.1</v>
       </c>
       <c r="H82" t="n">
-        <v>45.8</v>
+        <v>36.8</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>35.98</v>
+        <v>75.69</v>
       </c>
       <c r="K82" t="n">
-        <v>-17.6</v>
+        <v>-81.2</v>
       </c>
       <c r="L82" t="n">
-        <v>40.05</v>
+        <v>111.01</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:17:00</t>
+          <t>09:19:21</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.14</v>
+        <v>4.21</v>
       </c>
       <c r="F83" t="n">
-        <v>12.35</v>
+        <v>12.96</v>
       </c>
       <c r="G83" t="n">
-        <v>221.9</v>
+        <v>227</v>
       </c>
       <c r="H83" t="n">
-        <v>43.5</v>
+        <v>37.1</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-342.95</v>
+        <v>-108.29</v>
       </c>
       <c r="K83" t="n">
-        <v>273.6</v>
+        <v>-222.76</v>
       </c>
       <c r="L83" t="n">
-        <v>438.72</v>
+        <v>247.69</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:18:15</t>
+          <t>09:21:49</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="F84" t="n">
-        <v>12.96</v>
+        <v>13.59</v>
       </c>
       <c r="G84" t="n">
-        <v>213.2</v>
+        <v>220</v>
       </c>
       <c r="H84" t="n">
-        <v>41.2</v>
+        <v>38</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>120.59</v>
+        <v>491.5</v>
       </c>
       <c r="K84" t="n">
-        <v>267.31</v>
+        <v>-159.54</v>
       </c>
       <c r="L84" t="n">
-        <v>293.25</v>
+        <v>516.74</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:20:27</t>
+          <t>09:22:59</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.72</v>
+        <v>4.67</v>
       </c>
       <c r="F85" t="n">
-        <v>13.02</v>
+        <v>13.03</v>
       </c>
       <c r="G85" t="n">
-        <v>218.8</v>
+        <v>212.2</v>
       </c>
       <c r="H85" t="n">
-        <v>34.1</v>
+        <v>42.4</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>59.48</v>
+        <v>406.6</v>
       </c>
       <c r="K85" t="n">
-        <v>401.77</v>
+        <v>439.5</v>
       </c>
       <c r="L85" t="n">
-        <v>406.15</v>
+        <v>598.73</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:25:00</t>
+          <t>09:27:13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.05</v>
+        <v>4.27</v>
       </c>
       <c r="F86" t="n">
-        <v>12.92</v>
+        <v>12.89</v>
       </c>
       <c r="G86" t="n">
-        <v>230.8</v>
+        <v>207.7</v>
       </c>
       <c r="H86" t="n">
-        <v>44.3</v>
+        <v>35.9</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>243.92</v>
+        <v>-603.0599999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>251.02</v>
+        <v>-843.52</v>
       </c>
       <c r="L86" t="n">
-        <v>350.01</v>
+        <v>1036.92</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:26:38</t>
+          <t>09:28:29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.28</v>
+        <v>3.52</v>
       </c>
       <c r="F87" t="n">
-        <v>13.31</v>
+        <v>12.69</v>
       </c>
       <c r="G87" t="n">
-        <v>224.6</v>
+        <v>217.1</v>
       </c>
       <c r="H87" t="n">
-        <v>44</v>
+        <v>40.7</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-420.15</v>
+        <v>50.53</v>
       </c>
       <c r="K87" t="n">
-        <v>75.11</v>
+        <v>-443.15</v>
       </c>
       <c r="L87" t="n">
-        <v>426.81</v>
+        <v>446.02</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:28:49</t>
+          <t>09:30:06</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,25 +3736,25 @@
         <v>4.24</v>
       </c>
       <c r="F88" t="n">
-        <v>13.15</v>
+        <v>13.07</v>
       </c>
       <c r="G88" t="n">
-        <v>213.4</v>
+        <v>227.2</v>
       </c>
       <c r="H88" t="n">
-        <v>37.9</v>
+        <v>41</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>-339.86</v>
+        <v>176</v>
       </c>
       <c r="K88" t="n">
-        <v>23.93</v>
+        <v>289.64</v>
       </c>
       <c r="L88" t="n">
-        <v>340.71</v>
+        <v>338.92</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>49.61</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>58.27</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>76.53</v>
+        <v>112.33</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>17.32</v>
+        <v>27.73</v>
       </c>
       <c r="K15" t="n">
-        <v>63.96</v>
+        <v>102.41</v>
       </c>
       <c r="L15" t="n">
-        <v>66.26000000000001</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>252.29</v>
+        <v>270.1</v>
       </c>
       <c r="K16" t="n">
-        <v>-33.41</v>
+        <v>-35.76</v>
       </c>
       <c r="L16" t="n">
-        <v>254.49</v>
+        <v>272.46</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-242.18</v>
+        <v>-274.3</v>
       </c>
       <c r="K17" t="n">
-        <v>-95.09</v>
+        <v>-107.71</v>
       </c>
       <c r="L17" t="n">
-        <v>260.18</v>
+        <v>294.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>216.52</v>
+        <v>253.04</v>
       </c>
       <c r="K18" t="n">
-        <v>239.06</v>
+        <v>279.38</v>
       </c>
       <c r="L18" t="n">
-        <v>322.54</v>
+        <v>376.94</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>64.2</v>
+        <v>131.22</v>
       </c>
       <c r="K19" t="n">
-        <v>-43.11</v>
+        <v>-88.11</v>
       </c>
       <c r="L19" t="n">
-        <v>77.33</v>
+        <v>158.06</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-221.43</v>
+        <v>-262.22</v>
       </c>
       <c r="K20" t="n">
-        <v>-231.88</v>
+        <v>-274.59</v>
       </c>
       <c r="L20" t="n">
-        <v>320.63</v>
+        <v>379.69</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>356.08</v>
+        <v>445.89</v>
       </c>
       <c r="K21" t="n">
-        <v>205.97</v>
+        <v>257.93</v>
       </c>
       <c r="L21" t="n">
-        <v>411.36</v>
+        <v>515.12</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-143.3</v>
+        <v>-177.57</v>
       </c>
       <c r="K22" t="n">
-        <v>-396.67</v>
+        <v>-491.53</v>
       </c>
       <c r="L22" t="n">
-        <v>421.76</v>
+        <v>522.63</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-362.78</v>
+        <v>-446.97</v>
       </c>
       <c r="K23" t="n">
-        <v>-473.1</v>
+        <v>-582.88</v>
       </c>
       <c r="L23" t="n">
-        <v>596.1799999999999</v>
+        <v>734.53</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-60.82</v>
+        <v>-99.97</v>
       </c>
       <c r="K24" t="n">
-        <v>268.77</v>
+        <v>441.76</v>
       </c>
       <c r="L24" t="n">
-        <v>275.57</v>
+        <v>452.93</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>685.2</v>
+        <v>807.29</v>
       </c>
       <c r="K25" t="n">
-        <v>-511.42</v>
+        <v>-602.54</v>
       </c>
       <c r="L25" t="n">
-        <v>855.02</v>
+        <v>1007.36</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>21.81</v>
+        <v>44.7</v>
       </c>
       <c r="K26" t="n">
-        <v>-266.42</v>
+        <v>-545.9299999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>267.31</v>
+        <v>547.76</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-32.07</v>
+        <v>-39.97</v>
       </c>
       <c r="K27" t="n">
-        <v>-917.8</v>
+        <v>-1143.98</v>
       </c>
       <c r="L27" t="n">
-        <v>918.36</v>
+        <v>1144.68</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>723.73</v>
+        <v>995.67</v>
       </c>
       <c r="K28" t="n">
-        <v>631.71</v>
+        <v>869.08</v>
       </c>
       <c r="L28" t="n">
-        <v>960.65</v>
+        <v>1321.62</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>2.63</v>
+        <v>3.38</v>
       </c>
       <c r="K29" t="n">
-        <v>148.73</v>
+        <v>191.17</v>
       </c>
       <c r="L29" t="n">
-        <v>148.75</v>
+        <v>191.2</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-39.83</v>
+        <v>-73.33</v>
       </c>
       <c r="K30" t="n">
-        <v>-48.5</v>
+        <v>-89.3</v>
       </c>
       <c r="L30" t="n">
-        <v>62.76</v>
+        <v>115.55</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-67.75</v>
+        <v>-93.31</v>
       </c>
       <c r="K31" t="n">
-        <v>-116.02</v>
+        <v>-159.8</v>
       </c>
       <c r="L31" t="n">
-        <v>134.36</v>
+        <v>185.04</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-491.8</v>
+        <v>-499.76</v>
       </c>
       <c r="K32" t="n">
-        <v>-123.02</v>
+        <v>-125.01</v>
       </c>
       <c r="L32" t="n">
-        <v>506.96</v>
+        <v>515.15</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>177.8</v>
+        <v>215.99</v>
       </c>
       <c r="K33" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="L33" t="n">
-        <v>177.8</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.32</v>
+        <v>-5.34</v>
       </c>
       <c r="K34" t="n">
-        <v>-71.84999999999999</v>
+        <v>-165.55</v>
       </c>
       <c r="L34" t="n">
-        <v>71.89</v>
+        <v>165.64</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-653.6900000000001</v>
+        <v>-721.73</v>
       </c>
       <c r="K35" t="n">
-        <v>439.24</v>
+        <v>484.96</v>
       </c>
       <c r="L35" t="n">
-        <v>787.5599999999999</v>
+        <v>869.53</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-30.58</v>
+        <v>-63.07</v>
       </c>
       <c r="K36" t="n">
-        <v>131.95</v>
+        <v>272.1</v>
       </c>
       <c r="L36" t="n">
-        <v>135.45</v>
+        <v>279.31</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>218.21</v>
+        <v>287.07</v>
       </c>
       <c r="K37" t="n">
-        <v>-233.46</v>
+        <v>-307.14</v>
       </c>
       <c r="L37" t="n">
-        <v>319.56</v>
+        <v>420.41</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-74.40000000000001</v>
+        <v>-185.11</v>
       </c>
       <c r="K38" t="n">
-        <v>7.44</v>
+        <v>18.5</v>
       </c>
       <c r="L38" t="n">
-        <v>74.77</v>
+        <v>186.04</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-131.07</v>
+        <v>-184.48</v>
       </c>
       <c r="K39" t="n">
-        <v>-207.1</v>
+        <v>-291.48</v>
       </c>
       <c r="L39" t="n">
-        <v>245.09</v>
+        <v>344.95</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-135.21</v>
+        <v>-214.01</v>
       </c>
       <c r="K40" t="n">
-        <v>-257.99</v>
+        <v>-408.33</v>
       </c>
       <c r="L40" t="n">
-        <v>291.27</v>
+        <v>461.01</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>214.98</v>
+        <v>362.13</v>
       </c>
       <c r="K41" t="n">
-        <v>-508.49</v>
+        <v>-856.55</v>
       </c>
       <c r="L41" t="n">
-        <v>552.0700000000001</v>
+        <v>929.96</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-18.41</v>
+        <v>-35.29</v>
       </c>
       <c r="K42" t="n">
-        <v>320.88</v>
+        <v>615.01</v>
       </c>
       <c r="L42" t="n">
-        <v>321.4</v>
+        <v>616.02</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-25.5</v>
+        <v>-54.2</v>
       </c>
       <c r="K43" t="n">
-        <v>342.53</v>
+        <v>728.01</v>
       </c>
       <c r="L43" t="n">
-        <v>343.47</v>
+        <v>730.03</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-139.01</v>
+        <v>-143.62</v>
       </c>
       <c r="K44" t="n">
-        <v>-104.26</v>
+        <v>-107.72</v>
       </c>
       <c r="L44" t="n">
-        <v>173.76</v>
+        <v>179.53</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>129.87</v>
+        <v>149.12</v>
       </c>
       <c r="K45" t="n">
-        <v>227.7</v>
+        <v>261.46</v>
       </c>
       <c r="L45" t="n">
-        <v>262.13</v>
+        <v>301</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-214.85</v>
+        <v>-260.86</v>
       </c>
       <c r="K46" t="n">
-        <v>-394.36</v>
+        <v>-478.81</v>
       </c>
       <c r="L46" t="n">
-        <v>449.09</v>
+        <v>545.26</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>148.54</v>
+        <v>233.61</v>
       </c>
       <c r="K47" t="n">
-        <v>-51.16</v>
+        <v>-80.45999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>157.11</v>
+        <v>247.08</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>297.59</v>
+        <v>371.97</v>
       </c>
       <c r="K48" t="n">
-        <v>-219.22</v>
+        <v>-274.02</v>
       </c>
       <c r="L48" t="n">
-        <v>369.61</v>
+        <v>462</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-167.52</v>
+        <v>-208.69</v>
       </c>
       <c r="K49" t="n">
-        <v>-215.88</v>
+        <v>-268.93</v>
       </c>
       <c r="L49" t="n">
-        <v>273.26</v>
+        <v>340.41</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-213.37</v>
+        <v>-243.47</v>
       </c>
       <c r="K50" t="n">
-        <v>-682.0599999999999</v>
+        <v>-778.29</v>
       </c>
       <c r="L50" t="n">
-        <v>714.65</v>
+        <v>815.49</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>55.24</v>
+        <v>114.96</v>
       </c>
       <c r="K51" t="n">
-        <v>-101.77</v>
+        <v>-211.81</v>
       </c>
       <c r="L51" t="n">
-        <v>115.8</v>
+        <v>240.99</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-88.58</v>
+        <v>-102.4</v>
       </c>
       <c r="K52" t="n">
-        <v>503.31</v>
+        <v>581.86</v>
       </c>
       <c r="L52" t="n">
-        <v>511.05</v>
+        <v>590.8</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>799.24</v>
+        <v>1069.52</v>
       </c>
       <c r="K53" t="n">
-        <v>603.63</v>
+        <v>807.76</v>
       </c>
       <c r="L53" t="n">
-        <v>1001.58</v>
+        <v>1340.28</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>204.29</v>
+        <v>366.46</v>
       </c>
       <c r="K54" t="n">
-        <v>-187.99</v>
+        <v>-337.22</v>
       </c>
       <c r="L54" t="n">
-        <v>277.63</v>
+        <v>498</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>375.21</v>
+        <v>659.11</v>
       </c>
       <c r="K55" t="n">
-        <v>-38.87</v>
+        <v>-68.28</v>
       </c>
       <c r="L55" t="n">
-        <v>377.22</v>
+        <v>662.63</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-858.03</v>
+        <v>-1196.8</v>
       </c>
       <c r="K56" t="n">
-        <v>282.78</v>
+        <v>394.42</v>
       </c>
       <c r="L56" t="n">
-        <v>903.4299999999999</v>
+        <v>1260.12</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>346.94</v>
+        <v>504.69</v>
       </c>
       <c r="K57" t="n">
-        <v>555.8</v>
+        <v>808.51</v>
       </c>
       <c r="L57" t="n">
-        <v>655.1900000000001</v>
+        <v>953.1</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>377.32</v>
+        <v>579.97</v>
       </c>
       <c r="K58" t="n">
-        <v>594.14</v>
+        <v>913.25</v>
       </c>
       <c r="L58" t="n">
-        <v>703.83</v>
+        <v>1081.85</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>24.28</v>
+        <v>29.7</v>
       </c>
       <c r="K59" t="n">
-        <v>238.35</v>
+        <v>291.58</v>
       </c>
       <c r="L59" t="n">
-        <v>239.58</v>
+        <v>293.09</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>215.07</v>
+        <v>243.73</v>
       </c>
       <c r="K60" t="n">
-        <v>254.44</v>
+        <v>288.33</v>
       </c>
       <c r="L60" t="n">
-        <v>333.16</v>
+        <v>377.54</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-125.22</v>
+        <v>-200.08</v>
       </c>
       <c r="K61" t="n">
-        <v>53.51</v>
+        <v>85.5</v>
       </c>
       <c r="L61" t="n">
-        <v>136.17</v>
+        <v>217.59</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-182.52</v>
+        <v>-202.21</v>
       </c>
       <c r="K62" t="n">
-        <v>-123.88</v>
+        <v>-137.25</v>
       </c>
       <c r="L62" t="n">
-        <v>220.59</v>
+        <v>244.39</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-87.75</v>
+        <v>-169.18</v>
       </c>
       <c r="K63" t="n">
-        <v>-12.65</v>
+        <v>-24.39</v>
       </c>
       <c r="L63" t="n">
-        <v>88.65000000000001</v>
+        <v>170.93</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>270.93</v>
+        <v>302.69</v>
       </c>
       <c r="K64" t="n">
-        <v>-271.02</v>
+        <v>-302.8</v>
       </c>
       <c r="L64" t="n">
-        <v>383.21</v>
+        <v>428.15</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-19.59</v>
+        <v>-21.96</v>
       </c>
       <c r="K65" t="n">
-        <v>609.58</v>
+        <v>683.22</v>
       </c>
       <c r="L65" t="n">
-        <v>609.9</v>
+        <v>683.5700000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-347.19</v>
+        <v>-401.22</v>
       </c>
       <c r="K66" t="n">
-        <v>177.44</v>
+        <v>205.06</v>
       </c>
       <c r="L66" t="n">
-        <v>389.9</v>
+        <v>450.58</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>135.47</v>
+        <v>169.68</v>
       </c>
       <c r="K67" t="n">
-        <v>-644.34</v>
+        <v>-807.0599999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>658.4299999999999</v>
+        <v>824.7</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>307.02</v>
+        <v>488.35</v>
       </c>
       <c r="K68" t="n">
-        <v>309.82</v>
+        <v>492.81</v>
       </c>
       <c r="L68" t="n">
-        <v>436.18</v>
+        <v>693.8</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-75.61</v>
+        <v>-176.08</v>
       </c>
       <c r="K69" t="n">
-        <v>184.68</v>
+        <v>430.09</v>
       </c>
       <c r="L69" t="n">
-        <v>199.55</v>
+        <v>464.74</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>178.93</v>
+        <v>275.69</v>
       </c>
       <c r="K70" t="n">
-        <v>-500.01</v>
+        <v>-770.38</v>
       </c>
       <c r="L70" t="n">
-        <v>531.0700000000001</v>
+        <v>818.22</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>750.6799999999999</v>
+        <v>1020.14</v>
       </c>
       <c r="K71" t="n">
-        <v>-660.6799999999999</v>
+        <v>-897.83</v>
       </c>
       <c r="L71" t="n">
-        <v>1000.01</v>
+        <v>1358.96</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-73.76000000000001</v>
+        <v>-101.34</v>
       </c>
       <c r="K72" t="n">
-        <v>773.63</v>
+        <v>1062.84</v>
       </c>
       <c r="L72" t="n">
-        <v>777.14</v>
+        <v>1067.66</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-726.3200000000001</v>
+        <v>-1009.2</v>
       </c>
       <c r="K73" t="n">
-        <v>-542.25</v>
+        <v>-753.4400000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>906.41</v>
+        <v>1259.42</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>70.13</v>
+        <v>165.86</v>
       </c>
       <c r="K74" t="n">
-        <v>-12.47</v>
+        <v>-29.48</v>
       </c>
       <c r="L74" t="n">
-        <v>71.23</v>
+        <v>168.46</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>166.84</v>
+        <v>200.62</v>
       </c>
       <c r="K75" t="n">
-        <v>371.5</v>
+        <v>446.72</v>
       </c>
       <c r="L75" t="n">
-        <v>407.25</v>
+        <v>489.7</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-74.01000000000001</v>
+        <v>-82.8</v>
       </c>
       <c r="K76" t="n">
-        <v>325.78</v>
+        <v>364.51</v>
       </c>
       <c r="L76" t="n">
-        <v>334.08</v>
+        <v>373.79</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-65.05</v>
+        <v>-76.01000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-384.39</v>
+        <v>-449.12</v>
       </c>
       <c r="L77" t="n">
-        <v>389.86</v>
+        <v>455.51</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-50.82</v>
+        <v>-69.43000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>162.42</v>
+        <v>221.94</v>
       </c>
       <c r="L78" t="n">
-        <v>170.19</v>
+        <v>232.54</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>311.43</v>
+        <v>365.05</v>
       </c>
       <c r="K79" t="n">
-        <v>-189.05</v>
+        <v>-221.6</v>
       </c>
       <c r="L79" t="n">
-        <v>364.32</v>
+        <v>427.05</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>374.53</v>
+        <v>501.36</v>
       </c>
       <c r="K80" t="n">
-        <v>-242.12</v>
+        <v>-324.12</v>
       </c>
       <c r="L80" t="n">
-        <v>445.98</v>
+        <v>597.01</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="K81" t="n">
-        <v>-249.74</v>
+        <v>-510.09</v>
       </c>
       <c r="L81" t="n">
-        <v>249.74</v>
+        <v>510.09</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>75.69</v>
+        <v>180.43</v>
       </c>
       <c r="K82" t="n">
-        <v>-81.2</v>
+        <v>-193.58</v>
       </c>
       <c r="L82" t="n">
-        <v>111.01</v>
+        <v>264.64</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-108.29</v>
+        <v>-226.8</v>
       </c>
       <c r="K83" t="n">
-        <v>-222.76</v>
+        <v>-466.53</v>
       </c>
       <c r="L83" t="n">
-        <v>247.69</v>
+        <v>518.74</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>491.5</v>
+        <v>763.47</v>
       </c>
       <c r="K84" t="n">
-        <v>-159.54</v>
+        <v>-247.81</v>
       </c>
       <c r="L84" t="n">
-        <v>516.74</v>
+        <v>802.6799999999999</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>406.6</v>
+        <v>566.34</v>
       </c>
       <c r="K85" t="n">
-        <v>439.5</v>
+        <v>612.1799999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>598.73</v>
+        <v>833.97</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-603.0599999999999</v>
+        <v>-831.58</v>
       </c>
       <c r="K86" t="n">
-        <v>-843.52</v>
+        <v>-1163.16</v>
       </c>
       <c r="L86" t="n">
-        <v>1036.92</v>
+        <v>1429.85</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>50.53</v>
+        <v>84.66</v>
       </c>
       <c r="K87" t="n">
-        <v>-443.15</v>
+        <v>-742.4400000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>446.02</v>
+        <v>747.25</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>176</v>
+        <v>341.96</v>
       </c>
       <c r="K88" t="n">
-        <v>289.64</v>
+        <v>562.75</v>
       </c>
       <c r="L88" t="n">
-        <v>338.92</v>
+        <v>658.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>72.81999999999999</v>
+        <v>49.17</v>
       </c>
       <c r="K14" t="n">
-        <v>85.54000000000001</v>
+        <v>57.76</v>
       </c>
       <c r="L14" t="n">
-        <v>112.33</v>
+        <v>75.84999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>27.73</v>
+        <v>19.93</v>
       </c>
       <c r="K15" t="n">
-        <v>102.41</v>
+        <v>73.58</v>
       </c>
       <c r="L15" t="n">
-        <v>106.1</v>
+        <v>76.23</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>270.1</v>
+        <v>183.93</v>
       </c>
       <c r="K16" t="n">
-        <v>-35.76</v>
+        <v>-24.35</v>
       </c>
       <c r="L16" t="n">
-        <v>272.46</v>
+        <v>185.53</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-274.3</v>
+        <v>-172.33</v>
       </c>
       <c r="K17" t="n">
-        <v>-107.71</v>
+        <v>-67.66</v>
       </c>
       <c r="L17" t="n">
-        <v>294.69</v>
+        <v>185.14</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>253.04</v>
+        <v>149.12</v>
       </c>
       <c r="K18" t="n">
-        <v>279.38</v>
+        <v>164.64</v>
       </c>
       <c r="L18" t="n">
-        <v>376.94</v>
+        <v>222.13</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>131.22</v>
+        <v>83.38</v>
       </c>
       <c r="K19" t="n">
-        <v>-88.11</v>
+        <v>-55.99</v>
       </c>
       <c r="L19" t="n">
-        <v>158.06</v>
+        <v>100.44</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-262.22</v>
+        <v>-143.21</v>
       </c>
       <c r="K20" t="n">
-        <v>-274.59</v>
+        <v>-149.96</v>
       </c>
       <c r="L20" t="n">
-        <v>379.69</v>
+        <v>207.36</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>445.89</v>
+        <v>244.02</v>
       </c>
       <c r="K21" t="n">
-        <v>257.93</v>
+        <v>141.16</v>
       </c>
       <c r="L21" t="n">
-        <v>515.12</v>
+        <v>281.91</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-177.57</v>
+        <v>-97.26000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-491.53</v>
+        <v>-269.23</v>
       </c>
       <c r="L22" t="n">
-        <v>522.63</v>
+        <v>286.26</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-446.97</v>
+        <v>-220.61</v>
       </c>
       <c r="K23" t="n">
-        <v>-582.88</v>
+        <v>-287.69</v>
       </c>
       <c r="L23" t="n">
-        <v>734.53</v>
+        <v>362.53</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-99.97</v>
+        <v>-50.23</v>
       </c>
       <c r="K24" t="n">
-        <v>441.76</v>
+        <v>221.96</v>
       </c>
       <c r="L24" t="n">
-        <v>452.93</v>
+        <v>227.58</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>807.29</v>
+        <v>373.18</v>
       </c>
       <c r="K25" t="n">
-        <v>-602.54</v>
+        <v>-278.54</v>
       </c>
       <c r="L25" t="n">
-        <v>1007.36</v>
+        <v>465.67</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>44.7</v>
+        <v>19.44</v>
       </c>
       <c r="K26" t="n">
-        <v>-545.9299999999999</v>
+        <v>-237.48</v>
       </c>
       <c r="L26" t="n">
-        <v>547.76</v>
+        <v>238.27</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-39.97</v>
+        <v>-18.4</v>
       </c>
       <c r="K27" t="n">
-        <v>-1143.98</v>
+        <v>-526.51</v>
       </c>
       <c r="L27" t="n">
-        <v>1144.68</v>
+        <v>526.84</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>995.67</v>
+        <v>412.31</v>
       </c>
       <c r="K28" t="n">
-        <v>869.08</v>
+        <v>359.89</v>
       </c>
       <c r="L28" t="n">
-        <v>1321.62</v>
+        <v>547.28</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>3.38</v>
+        <v>2.16</v>
       </c>
       <c r="K29" t="n">
-        <v>191.17</v>
+        <v>121.87</v>
       </c>
       <c r="L29" t="n">
-        <v>191.2</v>
+        <v>121.89</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-73.33</v>
+        <v>-49.41</v>
       </c>
       <c r="K30" t="n">
-        <v>-89.3</v>
+        <v>-60.16</v>
       </c>
       <c r="L30" t="n">
-        <v>115.55</v>
+        <v>77.84999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-93.31</v>
+        <v>-62.1</v>
       </c>
       <c r="K31" t="n">
-        <v>-159.8</v>
+        <v>-106.36</v>
       </c>
       <c r="L31" t="n">
-        <v>185.04</v>
+        <v>123.16</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-499.76</v>
+        <v>-307.06</v>
       </c>
       <c r="K32" t="n">
-        <v>-125.01</v>
+        <v>-76.81</v>
       </c>
       <c r="L32" t="n">
-        <v>515.15</v>
+        <v>316.52</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>215.99</v>
+        <v>134.31</v>
       </c>
       <c r="K33" t="n">
-        <v>1.82</v>
+        <v>1.13</v>
       </c>
       <c r="L33" t="n">
-        <v>216</v>
+        <v>134.32</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.34</v>
+        <v>-3.41</v>
       </c>
       <c r="K34" t="n">
-        <v>-165.55</v>
+        <v>-105.68</v>
       </c>
       <c r="L34" t="n">
-        <v>165.64</v>
+        <v>105.73</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-721.73</v>
+        <v>-370.63</v>
       </c>
       <c r="K35" t="n">
-        <v>484.96</v>
+        <v>249.04</v>
       </c>
       <c r="L35" t="n">
-        <v>869.53</v>
+        <v>446.53</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-63.07</v>
+        <v>-33.31</v>
       </c>
       <c r="K36" t="n">
-        <v>272.1</v>
+        <v>143.7</v>
       </c>
       <c r="L36" t="n">
-        <v>279.31</v>
+        <v>147.51</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>287.07</v>
+        <v>151.2</v>
       </c>
       <c r="K37" t="n">
-        <v>-307.14</v>
+        <v>-161.77</v>
       </c>
       <c r="L37" t="n">
-        <v>420.41</v>
+        <v>221.43</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-185.11</v>
+        <v>-102.02</v>
       </c>
       <c r="K38" t="n">
-        <v>18.5</v>
+        <v>10.2</v>
       </c>
       <c r="L38" t="n">
-        <v>186.04</v>
+        <v>102.53</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-184.48</v>
+        <v>-98.43000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>-291.48</v>
+        <v>-155.51</v>
       </c>
       <c r="L39" t="n">
-        <v>344.95</v>
+        <v>184.04</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-214.01</v>
+        <v>-100.65</v>
       </c>
       <c r="K40" t="n">
-        <v>-408.33</v>
+        <v>-192.03</v>
       </c>
       <c r="L40" t="n">
-        <v>461.01</v>
+        <v>216.81</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>362.13</v>
+        <v>151.79</v>
       </c>
       <c r="K41" t="n">
-        <v>-856.55</v>
+        <v>-359.04</v>
       </c>
       <c r="L41" t="n">
-        <v>929.96</v>
+        <v>389.81</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-35.29</v>
+        <v>-15.79</v>
       </c>
       <c r="K42" t="n">
-        <v>615.01</v>
+        <v>275.19</v>
       </c>
       <c r="L42" t="n">
-        <v>616.02</v>
+        <v>275.64</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-54.2</v>
+        <v>-23.25</v>
       </c>
       <c r="K43" t="n">
-        <v>728.01</v>
+        <v>312.3</v>
       </c>
       <c r="L43" t="n">
-        <v>730.03</v>
+        <v>313.16</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-143.62</v>
+        <v>-96.59</v>
       </c>
       <c r="K44" t="n">
-        <v>-107.72</v>
+        <v>-72.45</v>
       </c>
       <c r="L44" t="n">
-        <v>179.53</v>
+        <v>120.75</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>149.12</v>
+        <v>97.17</v>
       </c>
       <c r="K45" t="n">
-        <v>261.46</v>
+        <v>170.37</v>
       </c>
       <c r="L45" t="n">
-        <v>301</v>
+        <v>196.13</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-260.86</v>
+        <v>-154.59</v>
       </c>
       <c r="K46" t="n">
-        <v>-478.81</v>
+        <v>-283.76</v>
       </c>
       <c r="L46" t="n">
-        <v>545.26</v>
+        <v>323.13</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>233.61</v>
+        <v>144</v>
       </c>
       <c r="K47" t="n">
-        <v>-80.45999999999999</v>
+        <v>-49.6</v>
       </c>
       <c r="L47" t="n">
-        <v>247.08</v>
+        <v>152.3</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>371.97</v>
+        <v>221.08</v>
       </c>
       <c r="K48" t="n">
-        <v>-274.02</v>
+        <v>-162.86</v>
       </c>
       <c r="L48" t="n">
-        <v>462</v>
+        <v>274.59</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-208.69</v>
+        <v>-131.53</v>
       </c>
       <c r="K49" t="n">
-        <v>-268.93</v>
+        <v>-169.5</v>
       </c>
       <c r="L49" t="n">
-        <v>340.41</v>
+        <v>214.54</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-243.47</v>
+        <v>-124.42</v>
       </c>
       <c r="K50" t="n">
-        <v>-778.29</v>
+        <v>-397.73</v>
       </c>
       <c r="L50" t="n">
-        <v>815.49</v>
+        <v>416.74</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>114.96</v>
+        <v>60.86</v>
       </c>
       <c r="K51" t="n">
-        <v>-211.81</v>
+        <v>-112.14</v>
       </c>
       <c r="L51" t="n">
-        <v>240.99</v>
+        <v>127.59</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-102.4</v>
+        <v>-53.6</v>
       </c>
       <c r="K52" t="n">
-        <v>581.86</v>
+        <v>304.55</v>
       </c>
       <c r="L52" t="n">
-        <v>590.8</v>
+        <v>309.23</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>1069.52</v>
+        <v>469.79</v>
       </c>
       <c r="K53" t="n">
-        <v>807.76</v>
+        <v>354.81</v>
       </c>
       <c r="L53" t="n">
-        <v>1340.28</v>
+        <v>588.72</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>366.46</v>
+        <v>179.83</v>
       </c>
       <c r="K54" t="n">
-        <v>-337.22</v>
+        <v>-165.48</v>
       </c>
       <c r="L54" t="n">
-        <v>498</v>
+        <v>244.38</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>659.11</v>
+        <v>297.41</v>
       </c>
       <c r="K55" t="n">
-        <v>-68.28</v>
+        <v>-30.81</v>
       </c>
       <c r="L55" t="n">
-        <v>662.63</v>
+        <v>299</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-1196.8</v>
+        <v>-495.76</v>
       </c>
       <c r="K56" t="n">
-        <v>394.42</v>
+        <v>163.38</v>
       </c>
       <c r="L56" t="n">
-        <v>1260.12</v>
+        <v>521.99</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>504.69</v>
+        <v>219.94</v>
       </c>
       <c r="K57" t="n">
-        <v>808.51</v>
+        <v>352.34</v>
       </c>
       <c r="L57" t="n">
-        <v>953.1</v>
+        <v>415.35</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>579.97</v>
+        <v>238.84</v>
       </c>
       <c r="K58" t="n">
-        <v>913.25</v>
+        <v>376.1</v>
       </c>
       <c r="L58" t="n">
-        <v>1081.85</v>
+        <v>445.53</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>29.7</v>
+        <v>18.18</v>
       </c>
       <c r="K59" t="n">
-        <v>291.58</v>
+        <v>178.51</v>
       </c>
       <c r="L59" t="n">
-        <v>293.09</v>
+        <v>179.43</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>243.73</v>
+        <v>148.2</v>
       </c>
       <c r="K60" t="n">
-        <v>288.33</v>
+        <v>175.33</v>
       </c>
       <c r="L60" t="n">
-        <v>377.54</v>
+        <v>229.57</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-200.08</v>
+        <v>-121.23</v>
       </c>
       <c r="K61" t="n">
-        <v>85.5</v>
+        <v>51.8</v>
       </c>
       <c r="L61" t="n">
-        <v>217.59</v>
+        <v>131.83</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-202.21</v>
+        <v>-132.33</v>
       </c>
       <c r="K62" t="n">
-        <v>-137.25</v>
+        <v>-89.81999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>244.39</v>
+        <v>159.94</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-169.18</v>
+        <v>-104.62</v>
       </c>
       <c r="K63" t="n">
-        <v>-24.39</v>
+        <v>-15.08</v>
       </c>
       <c r="L63" t="n">
-        <v>170.93</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>302.69</v>
+        <v>191.09</v>
       </c>
       <c r="K64" t="n">
-        <v>-302.8</v>
+        <v>-191.16</v>
       </c>
       <c r="L64" t="n">
-        <v>428.15</v>
+        <v>270.29</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-21.96</v>
+        <v>-12.24</v>
       </c>
       <c r="K65" t="n">
-        <v>683.22</v>
+        <v>381.02</v>
       </c>
       <c r="L65" t="n">
-        <v>683.5700000000001</v>
+        <v>381.22</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-401.22</v>
+        <v>-226.38</v>
       </c>
       <c r="K66" t="n">
-        <v>205.06</v>
+        <v>115.7</v>
       </c>
       <c r="L66" t="n">
-        <v>450.58</v>
+        <v>254.24</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>169.68</v>
+        <v>87.92</v>
       </c>
       <c r="K67" t="n">
-        <v>-807.0599999999999</v>
+        <v>-418.21</v>
       </c>
       <c r="L67" t="n">
-        <v>824.7</v>
+        <v>427.35</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>488.35</v>
+        <v>218.51</v>
       </c>
       <c r="K68" t="n">
-        <v>492.81</v>
+        <v>220.51</v>
       </c>
       <c r="L68" t="n">
-        <v>693.8</v>
+        <v>310.44</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-176.08</v>
+        <v>-78.66</v>
       </c>
       <c r="K69" t="n">
-        <v>430.09</v>
+        <v>192.13</v>
       </c>
       <c r="L69" t="n">
-        <v>464.74</v>
+        <v>207.6</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>275.69</v>
+        <v>122.07</v>
       </c>
       <c r="K70" t="n">
-        <v>-770.38</v>
+        <v>-341.1</v>
       </c>
       <c r="L70" t="n">
-        <v>818.22</v>
+        <v>362.29</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>1020.14</v>
+        <v>422.3</v>
       </c>
       <c r="K71" t="n">
-        <v>-897.83</v>
+        <v>-371.67</v>
       </c>
       <c r="L71" t="n">
-        <v>1358.96</v>
+        <v>562.5599999999999</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-101.34</v>
+        <v>-42.76</v>
       </c>
       <c r="K72" t="n">
-        <v>1062.84</v>
+        <v>448.46</v>
       </c>
       <c r="L72" t="n">
-        <v>1067.66</v>
+        <v>450.5</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-1009.2</v>
+        <v>-418.33</v>
       </c>
       <c r="K73" t="n">
-        <v>-753.4400000000001</v>
+        <v>-312.31</v>
       </c>
       <c r="L73" t="n">
-        <v>1259.42</v>
+        <v>522.05</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>165.86</v>
+        <v>101.64</v>
       </c>
       <c r="K74" t="n">
-        <v>-29.48</v>
+        <v>-18.07</v>
       </c>
       <c r="L74" t="n">
-        <v>168.46</v>
+        <v>103.23</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>200.62</v>
+        <v>122.2</v>
       </c>
       <c r="K75" t="n">
-        <v>446.72</v>
+        <v>272.1</v>
       </c>
       <c r="L75" t="n">
-        <v>489.7</v>
+        <v>298.28</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-82.8</v>
+        <v>-50.54</v>
       </c>
       <c r="K76" t="n">
-        <v>364.51</v>
+        <v>222.49</v>
       </c>
       <c r="L76" t="n">
-        <v>373.79</v>
+        <v>228.16</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-76.01000000000001</v>
+        <v>-44</v>
       </c>
       <c r="K77" t="n">
-        <v>-449.12</v>
+        <v>-260.01</v>
       </c>
       <c r="L77" t="n">
-        <v>455.51</v>
+        <v>263.71</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-69.43000000000001</v>
+        <v>-43.91</v>
       </c>
       <c r="K78" t="n">
-        <v>221.94</v>
+        <v>140.35</v>
       </c>
       <c r="L78" t="n">
-        <v>232.54</v>
+        <v>147.06</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>365.05</v>
+        <v>223.73</v>
       </c>
       <c r="K79" t="n">
-        <v>-221.6</v>
+        <v>-135.81</v>
       </c>
       <c r="L79" t="n">
-        <v>427.05</v>
+        <v>261.73</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>501.36</v>
+        <v>266.55</v>
       </c>
       <c r="K80" t="n">
-        <v>-324.12</v>
+        <v>-172.32</v>
       </c>
       <c r="L80" t="n">
-        <v>597.01</v>
+        <v>317.4</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>0.91</v>
+        <v>0.44</v>
       </c>
       <c r="K81" t="n">
-        <v>-510.09</v>
+        <v>-246.13</v>
       </c>
       <c r="L81" t="n">
-        <v>510.09</v>
+        <v>246.13</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>180.43</v>
+        <v>92.87</v>
       </c>
       <c r="K82" t="n">
-        <v>-193.58</v>
+        <v>-99.64</v>
       </c>
       <c r="L82" t="n">
-        <v>264.64</v>
+        <v>136.21</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-226.8</v>
+        <v>-101.03</v>
       </c>
       <c r="K83" t="n">
-        <v>-466.53</v>
+        <v>-207.83</v>
       </c>
       <c r="L83" t="n">
-        <v>518.74</v>
+        <v>231.08</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>763.47</v>
+        <v>351.69</v>
       </c>
       <c r="K84" t="n">
-        <v>-247.81</v>
+        <v>-114.15</v>
       </c>
       <c r="L84" t="n">
-        <v>802.6799999999999</v>
+        <v>369.75</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>566.34</v>
+        <v>275.15</v>
       </c>
       <c r="K85" t="n">
-        <v>612.1799999999999</v>
+        <v>297.42</v>
       </c>
       <c r="L85" t="n">
-        <v>833.97</v>
+        <v>405.17</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-831.58</v>
+        <v>-341.62</v>
       </c>
       <c r="K86" t="n">
-        <v>-1163.16</v>
+        <v>-477.83</v>
       </c>
       <c r="L86" t="n">
-        <v>1429.85</v>
+        <v>587.38</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>84.66</v>
+        <v>35.71</v>
       </c>
       <c r="K87" t="n">
-        <v>-742.4400000000001</v>
+        <v>-313.14</v>
       </c>
       <c r="L87" t="n">
-        <v>747.25</v>
+        <v>315.17</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>341.96</v>
+        <v>151.15</v>
       </c>
       <c r="K88" t="n">
-        <v>562.75</v>
+        <v>248.75</v>
       </c>
       <c r="L88" t="n">
-        <v>658.5</v>
+        <v>291.07</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>49.17</v>
+        <v>49.39</v>
       </c>
       <c r="K14" t="n">
-        <v>57.76</v>
+        <v>58.01</v>
       </c>
       <c r="L14" t="n">
-        <v>75.84999999999999</v>
+        <v>76.19</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>19.93</v>
+        <v>19.78</v>
       </c>
       <c r="K15" t="n">
-        <v>73.58</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>76.23</v>
+        <v>75.67</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>183.93</v>
+        <v>183.77</v>
       </c>
       <c r="K16" t="n">
-        <v>-24.35</v>
+        <v>-24.33</v>
       </c>
       <c r="L16" t="n">
-        <v>185.53</v>
+        <v>185.38</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-172.33</v>
+        <v>-179.46</v>
       </c>
       <c r="K17" t="n">
-        <v>-67.66</v>
+        <v>-70.47</v>
       </c>
       <c r="L17" t="n">
-        <v>185.14</v>
+        <v>192.8</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>149.12</v>
+        <v>157.28</v>
       </c>
       <c r="K18" t="n">
-        <v>164.64</v>
+        <v>173.66</v>
       </c>
       <c r="L18" t="n">
-        <v>222.13</v>
+        <v>234.3</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>83.38</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-55.99</v>
+        <v>-57.48</v>
       </c>
       <c r="L19" t="n">
-        <v>100.44</v>
+        <v>103.11</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-143.21</v>
+        <v>-155.41</v>
       </c>
       <c r="K20" t="n">
-        <v>-149.96</v>
+        <v>-162.74</v>
       </c>
       <c r="L20" t="n">
-        <v>207.36</v>
+        <v>225.03</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>244.02</v>
+        <v>261.71</v>
       </c>
       <c r="K21" t="n">
-        <v>141.16</v>
+        <v>151.39</v>
       </c>
       <c r="L21" t="n">
-        <v>281.91</v>
+        <v>302.34</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-97.26000000000001</v>
+        <v>-104.02</v>
       </c>
       <c r="K22" t="n">
-        <v>-269.23</v>
+        <v>-287.92</v>
       </c>
       <c r="L22" t="n">
-        <v>286.26</v>
+        <v>306.13</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-220.61</v>
+        <v>-242.02</v>
       </c>
       <c r="K23" t="n">
-        <v>-287.69</v>
+        <v>-315.61</v>
       </c>
       <c r="L23" t="n">
-        <v>362.53</v>
+        <v>397.72</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-50.23</v>
+        <v>-54.7</v>
       </c>
       <c r="K24" t="n">
-        <v>221.96</v>
+        <v>241.71</v>
       </c>
       <c r="L24" t="n">
-        <v>227.58</v>
+        <v>247.82</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>373.18</v>
+        <v>407.15</v>
       </c>
       <c r="K25" t="n">
-        <v>-278.54</v>
+        <v>-303.89</v>
       </c>
       <c r="L25" t="n">
-        <v>465.67</v>
+        <v>508.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>19.44</v>
+        <v>21.7</v>
       </c>
       <c r="K26" t="n">
-        <v>-237.48</v>
+        <v>-265.07</v>
       </c>
       <c r="L26" t="n">
-        <v>238.27</v>
+        <v>265.96</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-18.4</v>
+        <v>-20.41</v>
       </c>
       <c r="K27" t="n">
-        <v>-526.51</v>
+        <v>-584.25</v>
       </c>
       <c r="L27" t="n">
-        <v>526.84</v>
+        <v>584.61</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>412.31</v>
+        <v>464.31</v>
       </c>
       <c r="K28" t="n">
-        <v>359.89</v>
+        <v>405.28</v>
       </c>
       <c r="L28" t="n">
-        <v>547.28</v>
+        <v>616.3099999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="K29" t="n">
-        <v>121.87</v>
+        <v>121.23</v>
       </c>
       <c r="L29" t="n">
-        <v>121.89</v>
+        <v>121.24</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-49.41</v>
+        <v>-49</v>
       </c>
       <c r="K30" t="n">
-        <v>-60.16</v>
+        <v>-59.67</v>
       </c>
       <c r="L30" t="n">
-        <v>77.84999999999999</v>
+        <v>77.20999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-62.1</v>
+        <v>-62</v>
       </c>
       <c r="K31" t="n">
-        <v>-106.36</v>
+        <v>-106.18</v>
       </c>
       <c r="L31" t="n">
-        <v>123.16</v>
+        <v>122.96</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-307.06</v>
+        <v>-318.01</v>
       </c>
       <c r="K32" t="n">
-        <v>-76.81</v>
+        <v>-79.55</v>
       </c>
       <c r="L32" t="n">
-        <v>316.52</v>
+        <v>327.81</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>134.31</v>
+        <v>139.9</v>
       </c>
       <c r="K33" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="L33" t="n">
-        <v>134.32</v>
+        <v>139.91</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.41</v>
+        <v>-3.53</v>
       </c>
       <c r="K34" t="n">
-        <v>-105.68</v>
+        <v>-109.26</v>
       </c>
       <c r="L34" t="n">
-        <v>105.73</v>
+        <v>109.31</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-370.63</v>
+        <v>-399.78</v>
       </c>
       <c r="K35" t="n">
-        <v>249.04</v>
+        <v>268.63</v>
       </c>
       <c r="L35" t="n">
-        <v>446.53</v>
+        <v>481.64</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-33.31</v>
+        <v>-36.02</v>
       </c>
       <c r="K36" t="n">
-        <v>143.7</v>
+        <v>155.4</v>
       </c>
       <c r="L36" t="n">
-        <v>147.51</v>
+        <v>159.52</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>151.2</v>
+        <v>164.31</v>
       </c>
       <c r="K37" t="n">
-        <v>-161.77</v>
+        <v>-175.8</v>
       </c>
       <c r="L37" t="n">
-        <v>221.43</v>
+        <v>240.63</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-102.02</v>
+        <v>-111.24</v>
       </c>
       <c r="K38" t="n">
-        <v>10.2</v>
+        <v>11.12</v>
       </c>
       <c r="L38" t="n">
-        <v>102.53</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-98.43000000000001</v>
+        <v>-106.94</v>
       </c>
       <c r="K39" t="n">
-        <v>-155.51</v>
+        <v>-168.97</v>
       </c>
       <c r="L39" t="n">
-        <v>184.04</v>
+        <v>199.97</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-100.65</v>
+        <v>-112.18</v>
       </c>
       <c r="K40" t="n">
-        <v>-192.03</v>
+        <v>-214.04</v>
       </c>
       <c r="L40" t="n">
-        <v>216.81</v>
+        <v>241.65</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>151.79</v>
+        <v>171.89</v>
       </c>
       <c r="K41" t="n">
-        <v>-359.04</v>
+        <v>-406.58</v>
       </c>
       <c r="L41" t="n">
-        <v>389.81</v>
+        <v>441.43</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-15.79</v>
+        <v>-17.51</v>
       </c>
       <c r="K42" t="n">
-        <v>275.19</v>
+        <v>305.08</v>
       </c>
       <c r="L42" t="n">
-        <v>275.64</v>
+        <v>305.59</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-23.25</v>
+        <v>-26.35</v>
       </c>
       <c r="K43" t="n">
-        <v>312.3</v>
+        <v>353.88</v>
       </c>
       <c r="L43" t="n">
-        <v>313.16</v>
+        <v>354.86</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-96.59</v>
+        <v>-96.89</v>
       </c>
       <c r="K44" t="n">
-        <v>-72.45</v>
+        <v>-72.67</v>
       </c>
       <c r="L44" t="n">
-        <v>120.75</v>
+        <v>121.11</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>97.17</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>170.37</v>
+        <v>172.72</v>
       </c>
       <c r="L45" t="n">
-        <v>196.13</v>
+        <v>198.84</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-154.59</v>
+        <v>-161.89</v>
       </c>
       <c r="K46" t="n">
-        <v>-283.76</v>
+        <v>-297.15</v>
       </c>
       <c r="L46" t="n">
-        <v>323.13</v>
+        <v>338.39</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>144</v>
+        <v>149.52</v>
       </c>
       <c r="K47" t="n">
-        <v>-49.6</v>
+        <v>-51.5</v>
       </c>
       <c r="L47" t="n">
-        <v>152.3</v>
+        <v>158.14</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>221.08</v>
+        <v>225.6</v>
       </c>
       <c r="K48" t="n">
-        <v>-162.86</v>
+        <v>-166.19</v>
       </c>
       <c r="L48" t="n">
-        <v>274.59</v>
+        <v>280.2</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-131.53</v>
+        <v>-134.67</v>
       </c>
       <c r="K49" t="n">
-        <v>-169.5</v>
+        <v>-173.55</v>
       </c>
       <c r="L49" t="n">
-        <v>214.54</v>
+        <v>219.68</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-124.42</v>
+        <v>-133.92</v>
       </c>
       <c r="K50" t="n">
-        <v>-397.73</v>
+        <v>-428.1</v>
       </c>
       <c r="L50" t="n">
-        <v>416.74</v>
+        <v>448.56</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>60.86</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-112.14</v>
+        <v>-120.36</v>
       </c>
       <c r="L51" t="n">
-        <v>127.59</v>
+        <v>136.94</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-53.6</v>
+        <v>-58.21</v>
       </c>
       <c r="K52" t="n">
-        <v>304.55</v>
+        <v>330.73</v>
       </c>
       <c r="L52" t="n">
-        <v>309.23</v>
+        <v>335.82</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>469.79</v>
+        <v>522.5700000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>354.81</v>
+        <v>394.67</v>
       </c>
       <c r="L53" t="n">
-        <v>588.72</v>
+        <v>654.86</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>179.83</v>
+        <v>195.48</v>
       </c>
       <c r="K54" t="n">
-        <v>-165.48</v>
+        <v>-179.88</v>
       </c>
       <c r="L54" t="n">
-        <v>244.38</v>
+        <v>265.65</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>297.41</v>
+        <v>326.32</v>
       </c>
       <c r="K55" t="n">
-        <v>-30.81</v>
+        <v>-33.8</v>
       </c>
       <c r="L55" t="n">
-        <v>299</v>
+        <v>328.06</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-495.76</v>
+        <v>-559.46</v>
       </c>
       <c r="K56" t="n">
-        <v>163.38</v>
+        <v>184.38</v>
       </c>
       <c r="L56" t="n">
-        <v>521.99</v>
+        <v>589.0599999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>219.94</v>
+        <v>247.88</v>
       </c>
       <c r="K57" t="n">
-        <v>352.34</v>
+        <v>397.1</v>
       </c>
       <c r="L57" t="n">
-        <v>415.35</v>
+        <v>468.11</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>238.84</v>
+        <v>273.93</v>
       </c>
       <c r="K58" t="n">
-        <v>376.1</v>
+        <v>431.35</v>
       </c>
       <c r="L58" t="n">
-        <v>445.53</v>
+        <v>510.98</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>18.18</v>
+        <v>18.67</v>
       </c>
       <c r="K59" t="n">
-        <v>178.51</v>
+        <v>183.32</v>
       </c>
       <c r="L59" t="n">
-        <v>179.43</v>
+        <v>184.26</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>148.2</v>
+        <v>153.41</v>
       </c>
       <c r="K60" t="n">
-        <v>175.33</v>
+        <v>181.49</v>
       </c>
       <c r="L60" t="n">
-        <v>229.57</v>
+        <v>237.64</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-121.23</v>
+        <v>-124.1</v>
       </c>
       <c r="K61" t="n">
-        <v>51.8</v>
+        <v>53.03</v>
       </c>
       <c r="L61" t="n">
-        <v>131.83</v>
+        <v>134.96</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-132.33</v>
+        <v>-136.91</v>
       </c>
       <c r="K62" t="n">
-        <v>-89.81999999999999</v>
+        <v>-92.93000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>159.94</v>
+        <v>165.47</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-104.62</v>
+        <v>-108.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-15.08</v>
+        <v>-15.67</v>
       </c>
       <c r="L63" t="n">
-        <v>105.7</v>
+        <v>109.82</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>191.09</v>
+        <v>195.07</v>
       </c>
       <c r="K64" t="n">
-        <v>-191.16</v>
+        <v>-195.14</v>
       </c>
       <c r="L64" t="n">
-        <v>270.29</v>
+        <v>275.92</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.24</v>
+        <v>-12.96</v>
       </c>
       <c r="K65" t="n">
-        <v>381.02</v>
+        <v>403.28</v>
       </c>
       <c r="L65" t="n">
-        <v>381.22</v>
+        <v>403.48</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-226.38</v>
+        <v>-241.7</v>
       </c>
       <c r="K66" t="n">
-        <v>115.7</v>
+        <v>123.53</v>
       </c>
       <c r="L66" t="n">
-        <v>254.24</v>
+        <v>271.43</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>87.92</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-418.21</v>
+        <v>-448.48</v>
       </c>
       <c r="L67" t="n">
-        <v>427.35</v>
+        <v>458.28</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>218.51</v>
+        <v>243.94</v>
       </c>
       <c r="K68" t="n">
-        <v>220.51</v>
+        <v>246.17</v>
       </c>
       <c r="L68" t="n">
-        <v>310.44</v>
+        <v>346.56</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-78.66</v>
+        <v>-86.95999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>192.13</v>
+        <v>212.4</v>
       </c>
       <c r="L69" t="n">
-        <v>207.6</v>
+        <v>229.52</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>122.07</v>
+        <v>135.82</v>
       </c>
       <c r="K70" t="n">
-        <v>-341.1</v>
+        <v>-379.52</v>
       </c>
       <c r="L70" t="n">
-        <v>362.29</v>
+        <v>403.09</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>422.3</v>
+        <v>475.71</v>
       </c>
       <c r="K71" t="n">
-        <v>-371.67</v>
+        <v>-418.68</v>
       </c>
       <c r="L71" t="n">
-        <v>562.5599999999999</v>
+        <v>633.71</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-42.76</v>
+        <v>-48.23</v>
       </c>
       <c r="K72" t="n">
-        <v>448.46</v>
+        <v>505.79</v>
       </c>
       <c r="L72" t="n">
-        <v>450.5</v>
+        <v>508.08</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-418.33</v>
+        <v>-469.57</v>
       </c>
       <c r="K73" t="n">
-        <v>-312.31</v>
+        <v>-350.57</v>
       </c>
       <c r="L73" t="n">
-        <v>522.05</v>
+        <v>586</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>101.64</v>
+        <v>104.53</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.07</v>
+        <v>-18.58</v>
       </c>
       <c r="L74" t="n">
-        <v>103.23</v>
+        <v>106.17</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>122.2</v>
+        <v>127.69</v>
       </c>
       <c r="K75" t="n">
-        <v>272.1</v>
+        <v>284.33</v>
       </c>
       <c r="L75" t="n">
-        <v>298.28</v>
+        <v>311.68</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-50.54</v>
+        <v>-51.56</v>
       </c>
       <c r="K76" t="n">
-        <v>222.49</v>
+        <v>226.95</v>
       </c>
       <c r="L76" t="n">
-        <v>228.16</v>
+        <v>232.73</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-44</v>
+        <v>-46.06</v>
       </c>
       <c r="K77" t="n">
-        <v>-260.01</v>
+        <v>-272.18</v>
       </c>
       <c r="L77" t="n">
-        <v>263.71</v>
+        <v>276.05</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-43.91</v>
+        <v>-45</v>
       </c>
       <c r="K78" t="n">
-        <v>140.35</v>
+        <v>143.84</v>
       </c>
       <c r="L78" t="n">
-        <v>147.06</v>
+        <v>150.71</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>223.73</v>
+        <v>233.14</v>
       </c>
       <c r="K79" t="n">
-        <v>-135.81</v>
+        <v>-141.53</v>
       </c>
       <c r="L79" t="n">
-        <v>261.73</v>
+        <v>272.74</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>266.55</v>
+        <v>284.98</v>
       </c>
       <c r="K80" t="n">
-        <v>-172.32</v>
+        <v>-184.23</v>
       </c>
       <c r="L80" t="n">
-        <v>317.4</v>
+        <v>339.35</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="K81" t="n">
-        <v>-246.13</v>
+        <v>-267.03</v>
       </c>
       <c r="L81" t="n">
-        <v>246.13</v>
+        <v>267.03</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>92.87</v>
+        <v>100.13</v>
       </c>
       <c r="K82" t="n">
-        <v>-99.64</v>
+        <v>-107.43</v>
       </c>
       <c r="L82" t="n">
-        <v>136.21</v>
+        <v>146.86</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-101.03</v>
+        <v>-112.02</v>
       </c>
       <c r="K83" t="n">
-        <v>-207.83</v>
+        <v>-230.43</v>
       </c>
       <c r="L83" t="n">
-        <v>231.08</v>
+        <v>256.21</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>351.69</v>
+        <v>388.65</v>
       </c>
       <c r="K84" t="n">
-        <v>-114.15</v>
+        <v>-126.15</v>
       </c>
       <c r="L84" t="n">
-        <v>369.75</v>
+        <v>408.61</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>275.15</v>
+        <v>303.24</v>
       </c>
       <c r="K85" t="n">
-        <v>297.42</v>
+        <v>327.79</v>
       </c>
       <c r="L85" t="n">
-        <v>405.17</v>
+        <v>446.54</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-341.62</v>
+        <v>-387.26</v>
       </c>
       <c r="K86" t="n">
-        <v>-477.83</v>
+        <v>-541.67</v>
       </c>
       <c r="L86" t="n">
-        <v>587.38</v>
+        <v>665.86</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>35.71</v>
+        <v>40.2</v>
       </c>
       <c r="K87" t="n">
-        <v>-313.14</v>
+        <v>-352.5</v>
       </c>
       <c r="L87" t="n">
-        <v>315.17</v>
+        <v>354.78</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>151.15</v>
+        <v>170.43</v>
       </c>
       <c r="K88" t="n">
-        <v>248.75</v>
+        <v>280.47</v>
       </c>
       <c r="L88" t="n">
-        <v>291.07</v>
+        <v>328.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>49.39</v>
+        <v>29.14</v>
       </c>
       <c r="K14" t="n">
-        <v>58.01</v>
+        <v>34.22</v>
       </c>
       <c r="L14" t="n">
-        <v>76.19</v>
+        <v>44.95</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>19.78</v>
+        <v>11.07</v>
       </c>
       <c r="K15" t="n">
-        <v>73.04000000000001</v>
+        <v>40.87</v>
       </c>
       <c r="L15" t="n">
-        <v>75.67</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>183.77</v>
+        <v>87.17</v>
       </c>
       <c r="K16" t="n">
-        <v>-24.33</v>
+        <v>-11.54</v>
       </c>
       <c r="L16" t="n">
-        <v>185.38</v>
+        <v>87.93000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-179.46</v>
+        <v>-91.84999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-70.47</v>
+        <v>-36.07</v>
       </c>
       <c r="L17" t="n">
-        <v>192.8</v>
+        <v>98.68000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>157.28</v>
+        <v>76.41</v>
       </c>
       <c r="K18" t="n">
-        <v>173.66</v>
+        <v>84.36</v>
       </c>
       <c r="L18" t="n">
-        <v>234.3</v>
+        <v>113.82</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>85.59999999999999</v>
+        <v>41.99</v>
       </c>
       <c r="K19" t="n">
-        <v>-57.48</v>
+        <v>-28.19</v>
       </c>
       <c r="L19" t="n">
-        <v>103.11</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-155.41</v>
+        <v>-87.52</v>
       </c>
       <c r="K20" t="n">
-        <v>-162.74</v>
+        <v>-91.65000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>225.03</v>
+        <v>126.73</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>261.71</v>
+        <v>129.26</v>
       </c>
       <c r="K21" t="n">
-        <v>151.39</v>
+        <v>74.77</v>
       </c>
       <c r="L21" t="n">
-        <v>302.34</v>
+        <v>149.33</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-104.02</v>
+        <v>-51.43</v>
       </c>
       <c r="K22" t="n">
-        <v>-287.92</v>
+        <v>-142.36</v>
       </c>
       <c r="L22" t="n">
-        <v>306.13</v>
+        <v>151.36</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-242.02</v>
+        <v>-130.6</v>
       </c>
       <c r="K23" t="n">
-        <v>-315.61</v>
+        <v>-170.31</v>
       </c>
       <c r="L23" t="n">
-        <v>397.72</v>
+        <v>214.62</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-54.7</v>
+        <v>-28.49</v>
       </c>
       <c r="K24" t="n">
-        <v>241.71</v>
+        <v>125.9</v>
       </c>
       <c r="L24" t="n">
-        <v>247.82</v>
+        <v>129.08</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>407.15</v>
+        <v>225.53</v>
       </c>
       <c r="K25" t="n">
-        <v>-303.89</v>
+        <v>-168.33</v>
       </c>
       <c r="L25" t="n">
-        <v>508.05</v>
+        <v>281.43</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>21.7</v>
+        <v>12.25</v>
       </c>
       <c r="K26" t="n">
-        <v>-265.07</v>
+        <v>-149.59</v>
       </c>
       <c r="L26" t="n">
-        <v>265.96</v>
+        <v>150.09</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-20.41</v>
+        <v>-11.21</v>
       </c>
       <c r="K27" t="n">
-        <v>-584.25</v>
+        <v>-320.9</v>
       </c>
       <c r="L27" t="n">
-        <v>584.61</v>
+        <v>321.09</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>464.31</v>
+        <v>252.69</v>
       </c>
       <c r="K28" t="n">
-        <v>405.28</v>
+        <v>220.56</v>
       </c>
       <c r="L28" t="n">
-        <v>616.3099999999999</v>
+        <v>335.41</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>2.15</v>
+        <v>1.15</v>
       </c>
       <c r="K29" t="n">
-        <v>121.23</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>121.24</v>
+        <v>65.22</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-49</v>
+        <v>-26.91</v>
       </c>
       <c r="K30" t="n">
-        <v>-59.67</v>
+        <v>-32.77</v>
       </c>
       <c r="L30" t="n">
-        <v>77.20999999999999</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-62</v>
+        <v>-29.88</v>
       </c>
       <c r="K31" t="n">
-        <v>-106.18</v>
+        <v>-51.17</v>
       </c>
       <c r="L31" t="n">
-        <v>122.96</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-318.01</v>
+        <v>-151.91</v>
       </c>
       <c r="K32" t="n">
-        <v>-79.55</v>
+        <v>-38</v>
       </c>
       <c r="L32" t="n">
-        <v>327.81</v>
+        <v>156.59</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>139.9</v>
+        <v>78.94</v>
       </c>
       <c r="K33" t="n">
-        <v>1.18</v>
+        <v>0.66</v>
       </c>
       <c r="L33" t="n">
-        <v>139.91</v>
+        <v>78.94</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.53</v>
+        <v>-1.52</v>
       </c>
       <c r="K34" t="n">
-        <v>-109.26</v>
+        <v>-46.95</v>
       </c>
       <c r="L34" t="n">
-        <v>109.31</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-399.78</v>
+        <v>-199.56</v>
       </c>
       <c r="K35" t="n">
-        <v>268.63</v>
+        <v>134.09</v>
       </c>
       <c r="L35" t="n">
-        <v>481.64</v>
+        <v>240.42</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-36.02</v>
+        <v>-18.09</v>
       </c>
       <c r="K36" t="n">
-        <v>155.4</v>
+        <v>78.05</v>
       </c>
       <c r="L36" t="n">
-        <v>159.52</v>
+        <v>80.12</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>164.31</v>
+        <v>84.5</v>
       </c>
       <c r="K37" t="n">
-        <v>-175.8</v>
+        <v>-90.40000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>240.63</v>
+        <v>123.74</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-111.24</v>
+        <v>-41.19</v>
       </c>
       <c r="K38" t="n">
-        <v>11.12</v>
+        <v>4.12</v>
       </c>
       <c r="L38" t="n">
-        <v>111.8</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-106.94</v>
+        <v>-65.87</v>
       </c>
       <c r="K39" t="n">
-        <v>-168.97</v>
+        <v>-104.07</v>
       </c>
       <c r="L39" t="n">
-        <v>199.97</v>
+        <v>123.17</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-112.18</v>
+        <v>-65.61</v>
       </c>
       <c r="K40" t="n">
-        <v>-214.04</v>
+        <v>-125.18</v>
       </c>
       <c r="L40" t="n">
-        <v>241.65</v>
+        <v>141.33</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>171.89</v>
+        <v>92.14</v>
       </c>
       <c r="K41" t="n">
-        <v>-406.58</v>
+        <v>-217.95</v>
       </c>
       <c r="L41" t="n">
-        <v>441.43</v>
+        <v>236.63</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-17.51</v>
+        <v>-9.6</v>
       </c>
       <c r="K42" t="n">
-        <v>305.08</v>
+        <v>167.24</v>
       </c>
       <c r="L42" t="n">
-        <v>305.59</v>
+        <v>167.51</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-26.35</v>
+        <v>-13.91</v>
       </c>
       <c r="K43" t="n">
-        <v>353.88</v>
+        <v>186.91</v>
       </c>
       <c r="L43" t="n">
-        <v>354.86</v>
+        <v>187.42</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-96.89</v>
+        <v>-56.85</v>
       </c>
       <c r="K44" t="n">
-        <v>-72.67</v>
+        <v>-42.64</v>
       </c>
       <c r="L44" t="n">
-        <v>121.11</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>98.51000000000001</v>
+        <v>43.43</v>
       </c>
       <c r="K45" t="n">
-        <v>172.72</v>
+        <v>76.16</v>
       </c>
       <c r="L45" t="n">
-        <v>198.84</v>
+        <v>87.67</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-161.89</v>
+        <v>-65.41</v>
       </c>
       <c r="K46" t="n">
-        <v>-297.15</v>
+        <v>-120.06</v>
       </c>
       <c r="L46" t="n">
-        <v>338.39</v>
+        <v>136.72</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>149.52</v>
+        <v>66.2</v>
       </c>
       <c r="K47" t="n">
-        <v>-51.5</v>
+        <v>-22.8</v>
       </c>
       <c r="L47" t="n">
-        <v>158.14</v>
+        <v>70.02</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>225.6</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-166.19</v>
+        <v>-69.3</v>
       </c>
       <c r="L48" t="n">
-        <v>280.2</v>
+        <v>116.84</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-134.67</v>
+        <v>-58.64</v>
       </c>
       <c r="K49" t="n">
-        <v>-173.55</v>
+        <v>-75.56999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>219.68</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-133.92</v>
+        <v>-66.45999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-428.1</v>
+        <v>-212.44</v>
       </c>
       <c r="L50" t="n">
-        <v>448.56</v>
+        <v>222.59</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>65.31999999999999</v>
+        <v>33.95</v>
       </c>
       <c r="K51" t="n">
-        <v>-120.36</v>
+        <v>-62.54</v>
       </c>
       <c r="L51" t="n">
-        <v>136.94</v>
+        <v>71.16</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-58.21</v>
+        <v>-29.72</v>
       </c>
       <c r="K52" t="n">
-        <v>330.73</v>
+        <v>168.85</v>
       </c>
       <c r="L52" t="n">
-        <v>335.82</v>
+        <v>171.45</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>522.5700000000001</v>
+        <v>227.62</v>
       </c>
       <c r="K53" t="n">
-        <v>394.67</v>
+        <v>171.91</v>
       </c>
       <c r="L53" t="n">
-        <v>654.86</v>
+        <v>285.24</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>195.48</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-179.88</v>
+        <v>-84.65000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>265.65</v>
+        <v>125.01</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>326.32</v>
+        <v>147.46</v>
       </c>
       <c r="K55" t="n">
-        <v>-33.8</v>
+        <v>-15.28</v>
       </c>
       <c r="L55" t="n">
-        <v>328.06</v>
+        <v>148.25</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-559.46</v>
+        <v>-304.62</v>
       </c>
       <c r="K56" t="n">
-        <v>184.38</v>
+        <v>100.39</v>
       </c>
       <c r="L56" t="n">
-        <v>589.0599999999999</v>
+        <v>320.73</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>247.88</v>
+        <v>135.68</v>
       </c>
       <c r="K57" t="n">
-        <v>397.1</v>
+        <v>217.35</v>
       </c>
       <c r="L57" t="n">
-        <v>468.11</v>
+        <v>256.22</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>273.93</v>
+        <v>147.93</v>
       </c>
       <c r="K58" t="n">
-        <v>431.35</v>
+        <v>232.93</v>
       </c>
       <c r="L58" t="n">
-        <v>510.98</v>
+        <v>275.94</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>18.67</v>
+        <v>8.59</v>
       </c>
       <c r="K59" t="n">
-        <v>183.32</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>184.26</v>
+        <v>84.79000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>153.41</v>
+        <v>68.59</v>
       </c>
       <c r="K60" t="n">
-        <v>181.49</v>
+        <v>81.14</v>
       </c>
       <c r="L60" t="n">
-        <v>237.64</v>
+        <v>106.24</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-124.1</v>
+        <v>-54.61</v>
       </c>
       <c r="K61" t="n">
-        <v>53.03</v>
+        <v>23.34</v>
       </c>
       <c r="L61" t="n">
-        <v>134.96</v>
+        <v>59.39</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-136.91</v>
+        <v>-73.23999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-92.93000000000001</v>
+        <v>-49.71</v>
       </c>
       <c r="L62" t="n">
-        <v>165.47</v>
+        <v>88.52</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-108.7</v>
+        <v>-53.01</v>
       </c>
       <c r="K63" t="n">
-        <v>-15.67</v>
+        <v>-7.64</v>
       </c>
       <c r="L63" t="n">
-        <v>109.82</v>
+        <v>53.56</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>195.07</v>
+        <v>85.45</v>
       </c>
       <c r="K64" t="n">
-        <v>-195.14</v>
+        <v>-85.48</v>
       </c>
       <c r="L64" t="n">
-        <v>275.92</v>
+        <v>120.87</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.96</v>
+        <v>-6.34</v>
       </c>
       <c r="K65" t="n">
-        <v>403.28</v>
+        <v>197.24</v>
       </c>
       <c r="L65" t="n">
-        <v>403.48</v>
+        <v>197.34</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-241.7</v>
+        <v>-123.8</v>
       </c>
       <c r="K66" t="n">
-        <v>123.53</v>
+        <v>63.27</v>
       </c>
       <c r="L66" t="n">
-        <v>271.43</v>
+        <v>139.03</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>94.29000000000001</v>
+        <v>45.01</v>
       </c>
       <c r="K67" t="n">
-        <v>-448.48</v>
+        <v>-214.08</v>
       </c>
       <c r="L67" t="n">
-        <v>458.28</v>
+        <v>218.76</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>243.94</v>
+        <v>118.32</v>
       </c>
       <c r="K68" t="n">
-        <v>246.17</v>
+        <v>119.41</v>
       </c>
       <c r="L68" t="n">
-        <v>346.56</v>
+        <v>168.1</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-86.95999999999999</v>
+        <v>-41.88</v>
       </c>
       <c r="K69" t="n">
-        <v>212.4</v>
+        <v>102.28</v>
       </c>
       <c r="L69" t="n">
-        <v>229.52</v>
+        <v>110.52</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>135.82</v>
+        <v>62.82</v>
       </c>
       <c r="K70" t="n">
-        <v>-379.52</v>
+        <v>-175.55</v>
       </c>
       <c r="L70" t="n">
-        <v>403.09</v>
+        <v>186.45</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>475.71</v>
+        <v>258.77</v>
       </c>
       <c r="K71" t="n">
-        <v>-418.68</v>
+        <v>-227.75</v>
       </c>
       <c r="L71" t="n">
-        <v>633.71</v>
+        <v>344.72</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-48.23</v>
+        <v>-26.94</v>
       </c>
       <c r="K72" t="n">
-        <v>505.79</v>
+        <v>282.52</v>
       </c>
       <c r="L72" t="n">
-        <v>508.08</v>
+        <v>283.8</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-469.57</v>
+        <v>-255.91</v>
       </c>
       <c r="K73" t="n">
-        <v>-350.57</v>
+        <v>-191.06</v>
       </c>
       <c r="L73" t="n">
-        <v>586</v>
+        <v>319.37</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>104.53</v>
+        <v>43.66</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.58</v>
+        <v>-7.76</v>
       </c>
       <c r="L74" t="n">
-        <v>106.17</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>127.69</v>
+        <v>51.45</v>
       </c>
       <c r="K75" t="n">
-        <v>284.33</v>
+        <v>114.57</v>
       </c>
       <c r="L75" t="n">
-        <v>311.68</v>
+        <v>125.6</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-51.56</v>
+        <v>-23.43</v>
       </c>
       <c r="K76" t="n">
-        <v>226.95</v>
+        <v>103.13</v>
       </c>
       <c r="L76" t="n">
-        <v>232.73</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-46.06</v>
+        <v>-21.1</v>
       </c>
       <c r="K77" t="n">
-        <v>-272.18</v>
+        <v>-124.66</v>
       </c>
       <c r="L77" t="n">
-        <v>276.05</v>
+        <v>126.43</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-45</v>
+        <v>-21.74</v>
       </c>
       <c r="K78" t="n">
-        <v>143.84</v>
+        <v>69.48</v>
       </c>
       <c r="L78" t="n">
-        <v>150.71</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>233.14</v>
+        <v>101.06</v>
       </c>
       <c r="K79" t="n">
-        <v>-141.53</v>
+        <v>-61.35</v>
       </c>
       <c r="L79" t="n">
-        <v>272.74</v>
+        <v>118.23</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>284.98</v>
+        <v>136.03</v>
       </c>
       <c r="K80" t="n">
-        <v>-184.23</v>
+        <v>-87.94</v>
       </c>
       <c r="L80" t="n">
-        <v>339.35</v>
+        <v>161.98</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>0.48</v>
+        <v>0.23</v>
       </c>
       <c r="K81" t="n">
-        <v>-267.03</v>
+        <v>-127.79</v>
       </c>
       <c r="L81" t="n">
-        <v>267.03</v>
+        <v>127.79</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>100.13</v>
+        <v>50.12</v>
       </c>
       <c r="K82" t="n">
-        <v>-107.43</v>
+        <v>-53.78</v>
       </c>
       <c r="L82" t="n">
-        <v>146.86</v>
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-112.02</v>
+        <v>-53.27</v>
       </c>
       <c r="K83" t="n">
-        <v>-230.43</v>
+        <v>-109.58</v>
       </c>
       <c r="L83" t="n">
-        <v>256.21</v>
+        <v>121.85</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>388.65</v>
+        <v>169.06</v>
       </c>
       <c r="K84" t="n">
-        <v>-126.15</v>
+        <v>-54.88</v>
       </c>
       <c r="L84" t="n">
-        <v>408.61</v>
+        <v>177.75</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>303.24</v>
+        <v>133.56</v>
       </c>
       <c r="K85" t="n">
-        <v>327.79</v>
+        <v>144.37</v>
       </c>
       <c r="L85" t="n">
-        <v>446.54</v>
+        <v>196.68</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-387.26</v>
+        <v>-208.39</v>
       </c>
       <c r="K86" t="n">
-        <v>-541.67</v>
+        <v>-291.48</v>
       </c>
       <c r="L86" t="n">
-        <v>665.86</v>
+        <v>358.32</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>40.2</v>
+        <v>22.44</v>
       </c>
       <c r="K87" t="n">
-        <v>-352.5</v>
+        <v>-196.79</v>
       </c>
       <c r="L87" t="n">
-        <v>354.78</v>
+        <v>198.06</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>170.43</v>
+        <v>91.83</v>
       </c>
       <c r="K88" t="n">
-        <v>280.47</v>
+        <v>151.12</v>
       </c>
       <c r="L88" t="n">
-        <v>328.19</v>
+        <v>176.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>29.14</v>
+        <v>31.02</v>
       </c>
       <c r="K14" t="n">
-        <v>34.22</v>
+        <v>36.43</v>
       </c>
       <c r="L14" t="n">
-        <v>44.95</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>11.07</v>
+        <v>11.93</v>
       </c>
       <c r="K15" t="n">
-        <v>40.87</v>
+        <v>44.06</v>
       </c>
       <c r="L15" t="n">
-        <v>42.34</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>87.17</v>
+        <v>84.06</v>
       </c>
       <c r="K16" t="n">
-        <v>-11.54</v>
+        <v>-11.13</v>
       </c>
       <c r="L16" t="n">
-        <v>87.93000000000001</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-91.84999999999999</v>
+        <v>-90.04000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-36.07</v>
+        <v>-35.36</v>
       </c>
       <c r="L17" t="n">
-        <v>98.68000000000001</v>
+        <v>96.73999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>76.41</v>
+        <v>73.7</v>
       </c>
       <c r="K18" t="n">
-        <v>84.36</v>
+        <v>81.38</v>
       </c>
       <c r="L18" t="n">
-        <v>113.82</v>
+        <v>109.79</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>41.99</v>
+        <v>45.22</v>
       </c>
       <c r="K19" t="n">
-        <v>-28.19</v>
+        <v>-30.36</v>
       </c>
       <c r="L19" t="n">
-        <v>50.57</v>
+        <v>54.47</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-87.52</v>
+        <v>-86.94</v>
       </c>
       <c r="K20" t="n">
-        <v>-91.65000000000001</v>
+        <v>-91.04000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>126.73</v>
+        <v>125.89</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>129.26</v>
+        <v>126.61</v>
       </c>
       <c r="K21" t="n">
-        <v>74.77</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>149.33</v>
+        <v>146.26</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-51.43</v>
+        <v>-50.27</v>
       </c>
       <c r="K22" t="n">
-        <v>-142.36</v>
+        <v>-139.16</v>
       </c>
       <c r="L22" t="n">
-        <v>151.36</v>
+        <v>147.96</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-130.6</v>
+        <v>-127.67</v>
       </c>
       <c r="K23" t="n">
-        <v>-170.31</v>
+        <v>-166.49</v>
       </c>
       <c r="L23" t="n">
-        <v>214.62</v>
+        <v>209.8</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-28.49</v>
+        <v>-29.69</v>
       </c>
       <c r="K24" t="n">
-        <v>125.9</v>
+        <v>131.2</v>
       </c>
       <c r="L24" t="n">
-        <v>129.08</v>
+        <v>134.52</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>225.53</v>
+        <v>215.49</v>
       </c>
       <c r="K25" t="n">
-        <v>-168.33</v>
+        <v>-160.84</v>
       </c>
       <c r="L25" t="n">
-        <v>281.43</v>
+        <v>268.89</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>12.25</v>
+        <v>13.12</v>
       </c>
       <c r="K26" t="n">
-        <v>-149.59</v>
+        <v>-160.31</v>
       </c>
       <c r="L26" t="n">
-        <v>150.09</v>
+        <v>160.85</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-11.21</v>
+        <v>-11.2</v>
       </c>
       <c r="K27" t="n">
-        <v>-320.9</v>
+        <v>-320.58</v>
       </c>
       <c r="L27" t="n">
-        <v>321.09</v>
+        <v>320.78</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>252.69</v>
+        <v>256.04</v>
       </c>
       <c r="K28" t="n">
-        <v>220.56</v>
+        <v>223.49</v>
       </c>
       <c r="L28" t="n">
-        <v>335.41</v>
+        <v>339.86</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="K29" t="n">
-        <v>65.20999999999999</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>65.22</v>
+        <v>66.52</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-26.91</v>
+        <v>-29.32</v>
       </c>
       <c r="K30" t="n">
-        <v>-32.77</v>
+        <v>-35.71</v>
       </c>
       <c r="L30" t="n">
-        <v>42.4</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.88</v>
+        <v>-30.41</v>
       </c>
       <c r="K31" t="n">
-        <v>-51.17</v>
+        <v>-52.08</v>
       </c>
       <c r="L31" t="n">
-        <v>59.25</v>
+        <v>60.31</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-151.91</v>
+        <v>-141.55</v>
       </c>
       <c r="K32" t="n">
-        <v>-38</v>
+        <v>-35.41</v>
       </c>
       <c r="L32" t="n">
-        <v>156.59</v>
+        <v>145.91</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>78.94</v>
+        <v>79.89</v>
       </c>
       <c r="K33" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="L33" t="n">
-        <v>78.94</v>
+        <v>79.89</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.52</v>
+        <v>-1.44</v>
       </c>
       <c r="K34" t="n">
-        <v>-46.95</v>
+        <v>-44.58</v>
       </c>
       <c r="L34" t="n">
-        <v>46.97</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-199.56</v>
+        <v>-187.77</v>
       </c>
       <c r="K35" t="n">
-        <v>134.09</v>
+        <v>126.17</v>
       </c>
       <c r="L35" t="n">
-        <v>240.42</v>
+        <v>226.23</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.09</v>
+        <v>-19.44</v>
       </c>
       <c r="K36" t="n">
-        <v>78.05</v>
+        <v>83.89</v>
       </c>
       <c r="L36" t="n">
-        <v>80.12</v>
+        <v>86.11</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>84.5</v>
+        <v>84.66</v>
       </c>
       <c r="K37" t="n">
-        <v>-90.40000000000001</v>
+        <v>-90.58</v>
       </c>
       <c r="L37" t="n">
-        <v>123.74</v>
+        <v>123.98</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-41.19</v>
+        <v>-40.31</v>
       </c>
       <c r="K38" t="n">
-        <v>4.12</v>
+        <v>4.03</v>
       </c>
       <c r="L38" t="n">
-        <v>41.4</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-65.87</v>
+        <v>-67.81999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.07</v>
+        <v>-107.15</v>
       </c>
       <c r="L39" t="n">
-        <v>123.17</v>
+        <v>126.81</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-65.61</v>
+        <v>-67.56999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-125.18</v>
+        <v>-128.91</v>
       </c>
       <c r="L40" t="n">
-        <v>141.33</v>
+        <v>145.55</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>92.14</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-217.95</v>
+        <v>-235.77</v>
       </c>
       <c r="L41" t="n">
-        <v>236.63</v>
+        <v>255.97</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-9.6</v>
+        <v>-10.47</v>
       </c>
       <c r="K42" t="n">
-        <v>167.24</v>
+        <v>182.39</v>
       </c>
       <c r="L42" t="n">
-        <v>167.51</v>
+        <v>182.69</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-13.91</v>
+        <v>-16.66</v>
       </c>
       <c r="K43" t="n">
-        <v>186.91</v>
+        <v>223.81</v>
       </c>
       <c r="L43" t="n">
-        <v>187.42</v>
+        <v>224.42</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.85</v>
+        <v>-56.5</v>
       </c>
       <c r="K44" t="n">
-        <v>-42.64</v>
+        <v>-42.38</v>
       </c>
       <c r="L44" t="n">
-        <v>71.06</v>
+        <v>70.62</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>43.43</v>
+        <v>41.59</v>
       </c>
       <c r="K45" t="n">
-        <v>76.16</v>
+        <v>72.91</v>
       </c>
       <c r="L45" t="n">
-        <v>87.67</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-65.41</v>
+        <v>-51.91</v>
       </c>
       <c r="K46" t="n">
-        <v>-120.06</v>
+        <v>-95.28</v>
       </c>
       <c r="L46" t="n">
-        <v>136.72</v>
+        <v>108.51</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>66.2</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-22.8</v>
+        <v>-23.01</v>
       </c>
       <c r="L47" t="n">
-        <v>70.02</v>
+        <v>70.64</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>94.06999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="K48" t="n">
-        <v>-69.3</v>
+        <v>-63.61</v>
       </c>
       <c r="L48" t="n">
-        <v>116.84</v>
+        <v>107.26</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-58.64</v>
+        <v>-56.37</v>
       </c>
       <c r="K49" t="n">
-        <v>-75.56999999999999</v>
+        <v>-72.64</v>
       </c>
       <c r="L49" t="n">
-        <v>95.65000000000001</v>
+        <v>91.94</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-66.45999999999999</v>
+        <v>-62.8</v>
       </c>
       <c r="K50" t="n">
-        <v>-212.44</v>
+        <v>-200.74</v>
       </c>
       <c r="L50" t="n">
-        <v>222.59</v>
+        <v>210.33</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>33.95</v>
+        <v>36.84</v>
       </c>
       <c r="K51" t="n">
-        <v>-62.54</v>
+        <v>-67.87</v>
       </c>
       <c r="L51" t="n">
-        <v>71.16</v>
+        <v>77.23</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-29.72</v>
+        <v>-28.69</v>
       </c>
       <c r="K52" t="n">
-        <v>168.85</v>
+        <v>163.02</v>
       </c>
       <c r="L52" t="n">
-        <v>171.45</v>
+        <v>165.53</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>227.62</v>
+        <v>231.38</v>
       </c>
       <c r="K53" t="n">
-        <v>171.91</v>
+        <v>174.75</v>
       </c>
       <c r="L53" t="n">
-        <v>285.24</v>
+        <v>289.95</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>91.98999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>-84.65000000000001</v>
+        <v>-89.16</v>
       </c>
       <c r="L54" t="n">
-        <v>125.01</v>
+        <v>131.68</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>147.46</v>
+        <v>153.11</v>
       </c>
       <c r="K55" t="n">
-        <v>-15.28</v>
+        <v>-15.86</v>
       </c>
       <c r="L55" t="n">
-        <v>148.25</v>
+        <v>153.93</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-304.62</v>
+        <v>-309.25</v>
       </c>
       <c r="K56" t="n">
-        <v>100.39</v>
+        <v>101.92</v>
       </c>
       <c r="L56" t="n">
-        <v>320.73</v>
+        <v>325.62</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>135.68</v>
+        <v>139.76</v>
       </c>
       <c r="K57" t="n">
-        <v>217.35</v>
+        <v>223.89</v>
       </c>
       <c r="L57" t="n">
-        <v>256.22</v>
+        <v>263.92</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>147.93</v>
+        <v>154.62</v>
       </c>
       <c r="K58" t="n">
-        <v>232.93</v>
+        <v>243.47</v>
       </c>
       <c r="L58" t="n">
-        <v>275.94</v>
+        <v>288.42</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>8.59</v>
+        <v>8.34</v>
       </c>
       <c r="K59" t="n">
-        <v>84.34999999999999</v>
+        <v>81.89</v>
       </c>
       <c r="L59" t="n">
-        <v>84.79000000000001</v>
+        <v>82.31</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>68.59</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>81.14</v>
+        <v>76.72</v>
       </c>
       <c r="L60" t="n">
-        <v>106.24</v>
+        <v>100.45</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-54.61</v>
+        <v>-55.38</v>
       </c>
       <c r="K61" t="n">
-        <v>23.34</v>
+        <v>23.66</v>
       </c>
       <c r="L61" t="n">
-        <v>59.39</v>
+        <v>60.22</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-73.23999999999999</v>
+        <v>-72.56999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-49.71</v>
+        <v>-49.26</v>
       </c>
       <c r="L62" t="n">
-        <v>88.52</v>
+        <v>87.70999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-53.01</v>
+        <v>-56.41</v>
       </c>
       <c r="K63" t="n">
-        <v>-7.64</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>53.56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>85.45</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-85.48</v>
+        <v>-80.09999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>120.87</v>
+        <v>113.26</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.34</v>
+        <v>-6.01</v>
       </c>
       <c r="K65" t="n">
-        <v>197.24</v>
+        <v>187.17</v>
       </c>
       <c r="L65" t="n">
-        <v>197.34</v>
+        <v>187.27</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-123.8</v>
+        <v>-121.21</v>
       </c>
       <c r="K66" t="n">
-        <v>63.27</v>
+        <v>61.95</v>
       </c>
       <c r="L66" t="n">
-        <v>139.03</v>
+        <v>136.12</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>45.01</v>
+        <v>36.04</v>
       </c>
       <c r="K67" t="n">
-        <v>-214.08</v>
+        <v>-171.44</v>
       </c>
       <c r="L67" t="n">
-        <v>218.76</v>
+        <v>175.18</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>118.32</v>
+        <v>120.33</v>
       </c>
       <c r="K68" t="n">
-        <v>119.41</v>
+        <v>121.43</v>
       </c>
       <c r="L68" t="n">
-        <v>168.1</v>
+        <v>170.96</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-41.88</v>
+        <v>-45.46</v>
       </c>
       <c r="K69" t="n">
-        <v>102.28</v>
+        <v>111.04</v>
       </c>
       <c r="L69" t="n">
-        <v>110.52</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>62.82</v>
+        <v>63.29</v>
       </c>
       <c r="K70" t="n">
-        <v>-175.55</v>
+        <v>-176.85</v>
       </c>
       <c r="L70" t="n">
-        <v>186.45</v>
+        <v>187.83</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>258.77</v>
+        <v>260.96</v>
       </c>
       <c r="K71" t="n">
-        <v>-227.75</v>
+        <v>-229.67</v>
       </c>
       <c r="L71" t="n">
-        <v>344.72</v>
+        <v>347.63</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-26.94</v>
+        <v>-26.78</v>
       </c>
       <c r="K72" t="n">
-        <v>282.52</v>
+        <v>280.9</v>
       </c>
       <c r="L72" t="n">
-        <v>283.8</v>
+        <v>282.17</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-255.91</v>
+        <v>-259.27</v>
       </c>
       <c r="K73" t="n">
-        <v>-191.06</v>
+        <v>-193.57</v>
       </c>
       <c r="L73" t="n">
-        <v>319.37</v>
+        <v>323.56</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>43.66</v>
+        <v>42.13</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.76</v>
+        <v>-7.49</v>
       </c>
       <c r="L74" t="n">
-        <v>44.35</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>51.45</v>
+        <v>41.99</v>
       </c>
       <c r="K75" t="n">
-        <v>114.57</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>125.6</v>
+        <v>102.49</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-23.43</v>
+        <v>-22.17</v>
       </c>
       <c r="K76" t="n">
-        <v>103.13</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>105.76</v>
+        <v>100.08</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-21.1</v>
+        <v>-19.94</v>
       </c>
       <c r="K77" t="n">
-        <v>-124.66</v>
+        <v>-117.81</v>
       </c>
       <c r="L77" t="n">
-        <v>126.43</v>
+        <v>119.48</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-21.74</v>
+        <v>-21.88</v>
       </c>
       <c r="K78" t="n">
-        <v>69.48</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>72.8</v>
+        <v>73.27</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>101.06</v>
+        <v>95.11</v>
       </c>
       <c r="K79" t="n">
-        <v>-61.35</v>
+        <v>-57.74</v>
       </c>
       <c r="L79" t="n">
-        <v>118.23</v>
+        <v>111.27</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>136.03</v>
+        <v>132.19</v>
       </c>
       <c r="K80" t="n">
-        <v>-87.94</v>
+        <v>-85.45999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>161.98</v>
+        <v>157.41</v>
       </c>
     </row>
     <row r="81">
@@ -3457,10 +3457,10 @@
         <v>0.23</v>
       </c>
       <c r="K81" t="n">
-        <v>-127.79</v>
+        <v>-130.97</v>
       </c>
       <c r="L81" t="n">
-        <v>127.79</v>
+        <v>130.97</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>50.12</v>
+        <v>54.63</v>
       </c>
       <c r="K82" t="n">
-        <v>-53.78</v>
+        <v>-58.62</v>
       </c>
       <c r="L82" t="n">
-        <v>73.51000000000001</v>
+        <v>80.13</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-53.27</v>
+        <v>-56.93</v>
       </c>
       <c r="K83" t="n">
-        <v>-109.58</v>
+        <v>-117.1</v>
       </c>
       <c r="L83" t="n">
-        <v>121.85</v>
+        <v>130.21</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>169.06</v>
+        <v>179.6</v>
       </c>
       <c r="K84" t="n">
-        <v>-54.88</v>
+        <v>-58.3</v>
       </c>
       <c r="L84" t="n">
-        <v>177.75</v>
+        <v>188.83</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>133.56</v>
+        <v>137.19</v>
       </c>
       <c r="K85" t="n">
-        <v>144.37</v>
+        <v>148.29</v>
       </c>
       <c r="L85" t="n">
-        <v>196.68</v>
+        <v>202.02</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-208.39</v>
+        <v>-212.41</v>
       </c>
       <c r="K86" t="n">
-        <v>-291.48</v>
+        <v>-297.11</v>
       </c>
       <c r="L86" t="n">
-        <v>358.32</v>
+        <v>365.23</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>22.44</v>
+        <v>23.33</v>
       </c>
       <c r="K87" t="n">
-        <v>-196.79</v>
+        <v>-204.59</v>
       </c>
       <c r="L87" t="n">
-        <v>198.06</v>
+        <v>205.91</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>91.83</v>
+        <v>101.59</v>
       </c>
       <c r="K88" t="n">
-        <v>151.12</v>
+        <v>167.18</v>
       </c>
       <c r="L88" t="n">
-        <v>176.84</v>
+        <v>195.63</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>31.02</v>
+        <v>33.16</v>
       </c>
       <c r="K14" t="n">
-        <v>36.43</v>
+        <v>38.96</v>
       </c>
       <c r="L14" t="n">
-        <v>47.85</v>
+        <v>51.16</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>11.93</v>
+        <v>12.92</v>
       </c>
       <c r="K15" t="n">
-        <v>44.06</v>
+        <v>47.71</v>
       </c>
       <c r="L15" t="n">
-        <v>45.65</v>
+        <v>49.43</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>84.06</v>
+        <v>82.14</v>
       </c>
       <c r="K16" t="n">
-        <v>-11.13</v>
+        <v>-10.88</v>
       </c>
       <c r="L16" t="n">
-        <v>84.8</v>
+        <v>82.86</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-90.04000000000001</v>
+        <v>-88.73999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-35.36</v>
+        <v>-34.84</v>
       </c>
       <c r="L17" t="n">
-        <v>96.73999999999999</v>
+        <v>95.34</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>73.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>81.38</v>
+        <v>79.39</v>
       </c>
       <c r="L18" t="n">
-        <v>109.79</v>
+        <v>107.11</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>45.22</v>
+        <v>49.54</v>
       </c>
       <c r="K19" t="n">
-        <v>-30.36</v>
+        <v>-33.26</v>
       </c>
       <c r="L19" t="n">
-        <v>54.47</v>
+        <v>59.67</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-86.94</v>
+        <v>-86.28</v>
       </c>
       <c r="K20" t="n">
-        <v>-91.04000000000001</v>
+        <v>-90.34999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>125.89</v>
+        <v>124.93</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>126.61</v>
+        <v>124.69</v>
       </c>
       <c r="K21" t="n">
-        <v>73.23999999999999</v>
+        <v>72.13</v>
       </c>
       <c r="L21" t="n">
-        <v>146.26</v>
+        <v>144.05</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-50.27</v>
+        <v>-49.39</v>
       </c>
       <c r="K22" t="n">
-        <v>-139.16</v>
+        <v>-136.71</v>
       </c>
       <c r="L22" t="n">
-        <v>147.96</v>
+        <v>145.35</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-127.67</v>
+        <v>-123.97</v>
       </c>
       <c r="K23" t="n">
-        <v>-166.49</v>
+        <v>-161.67</v>
       </c>
       <c r="L23" t="n">
-        <v>209.8</v>
+        <v>203.73</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-29.69</v>
+        <v>-30.95</v>
       </c>
       <c r="K24" t="n">
-        <v>131.2</v>
+        <v>136.77</v>
       </c>
       <c r="L24" t="n">
-        <v>134.52</v>
+        <v>140.23</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>215.49</v>
+        <v>203.64</v>
       </c>
       <c r="K25" t="n">
-        <v>-160.84</v>
+        <v>-152</v>
       </c>
       <c r="L25" t="n">
-        <v>268.89</v>
+        <v>254.11</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>13.12</v>
+        <v>14.07</v>
       </c>
       <c r="K26" t="n">
-        <v>-160.31</v>
+        <v>-171.82</v>
       </c>
       <c r="L26" t="n">
-        <v>160.85</v>
+        <v>172.4</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-11.2</v>
+        <v>-10.81</v>
       </c>
       <c r="K27" t="n">
-        <v>-320.58</v>
+        <v>-309.4</v>
       </c>
       <c r="L27" t="n">
-        <v>320.78</v>
+        <v>309.59</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>256.04</v>
+        <v>248.86</v>
       </c>
       <c r="K28" t="n">
-        <v>223.49</v>
+        <v>217.22</v>
       </c>
       <c r="L28" t="n">
-        <v>339.86</v>
+        <v>330.33</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="K29" t="n">
-        <v>66.51000000000001</v>
+        <v>68.11</v>
       </c>
       <c r="L29" t="n">
-        <v>66.52</v>
+        <v>68.12</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-29.32</v>
+        <v>-32.08</v>
       </c>
       <c r="K30" t="n">
-        <v>-35.71</v>
+        <v>-39.07</v>
       </c>
       <c r="L30" t="n">
-        <v>46.21</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-30.41</v>
+        <v>-31.51</v>
       </c>
       <c r="K31" t="n">
-        <v>-52.08</v>
+        <v>-53.96</v>
       </c>
       <c r="L31" t="n">
-        <v>60.31</v>
+        <v>62.49</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-141.55</v>
+        <v>-132.72</v>
       </c>
       <c r="K32" t="n">
-        <v>-35.41</v>
+        <v>-33.2</v>
       </c>
       <c r="L32" t="n">
-        <v>145.91</v>
+        <v>136.81</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>79.89</v>
+        <v>80.98</v>
       </c>
       <c r="K33" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="L33" t="n">
-        <v>79.89</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.44</v>
+        <v>-1.58</v>
       </c>
       <c r="K34" t="n">
-        <v>-44.58</v>
+        <v>-48.83</v>
       </c>
       <c r="L34" t="n">
-        <v>44.61</v>
+        <v>48.86</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-187.77</v>
+        <v>-175.61</v>
       </c>
       <c r="K35" t="n">
-        <v>126.17</v>
+        <v>118</v>
       </c>
       <c r="L35" t="n">
-        <v>226.23</v>
+        <v>211.58</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.44</v>
+        <v>-21.08</v>
       </c>
       <c r="K36" t="n">
-        <v>83.89</v>
+        <v>90.95</v>
       </c>
       <c r="L36" t="n">
-        <v>86.11</v>
+        <v>93.36</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>84.66</v>
+        <v>84.89</v>
       </c>
       <c r="K37" t="n">
-        <v>-90.58</v>
+        <v>-90.81999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>123.98</v>
+        <v>124.32</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-40.31</v>
+        <v>-43.78</v>
       </c>
       <c r="K38" t="n">
-        <v>4.03</v>
+        <v>4.38</v>
       </c>
       <c r="L38" t="n">
-        <v>40.51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-67.81999999999999</v>
+        <v>-70.04000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>-107.15</v>
+        <v>-110.67</v>
       </c>
       <c r="L39" t="n">
-        <v>126.81</v>
+        <v>130.97</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-67.56999999999999</v>
+        <v>-69.8</v>
       </c>
       <c r="K40" t="n">
-        <v>-128.91</v>
+        <v>-133.18</v>
       </c>
       <c r="L40" t="n">
-        <v>145.55</v>
+        <v>150.36</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>99.68000000000001</v>
+        <v>102.67</v>
       </c>
       <c r="K41" t="n">
-        <v>-235.77</v>
+        <v>-242.85</v>
       </c>
       <c r="L41" t="n">
-        <v>255.97</v>
+        <v>263.66</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-10.47</v>
+        <v>-11.12</v>
       </c>
       <c r="K42" t="n">
-        <v>182.39</v>
+        <v>193.81</v>
       </c>
       <c r="L42" t="n">
-        <v>182.69</v>
+        <v>194.13</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-16.66</v>
+        <v>-17.95</v>
       </c>
       <c r="K43" t="n">
-        <v>223.81</v>
+        <v>241.15</v>
       </c>
       <c r="L43" t="n">
-        <v>224.42</v>
+        <v>241.82</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.5</v>
+        <v>-56.1</v>
       </c>
       <c r="K44" t="n">
-        <v>-42.38</v>
+        <v>-42.08</v>
       </c>
       <c r="L44" t="n">
-        <v>70.62</v>
+        <v>70.13</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>41.59</v>
+        <v>40.75</v>
       </c>
       <c r="K45" t="n">
-        <v>72.91</v>
+        <v>71.45</v>
       </c>
       <c r="L45" t="n">
-        <v>83.94</v>
+        <v>82.26000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-51.91</v>
+        <v>-49.64</v>
       </c>
       <c r="K46" t="n">
-        <v>-95.28</v>
+        <v>-91.12</v>
       </c>
       <c r="L46" t="n">
-        <v>108.51</v>
+        <v>103.76</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>66.79000000000001</v>
+        <v>69.63</v>
       </c>
       <c r="K47" t="n">
-        <v>-23.01</v>
+        <v>-23.98</v>
       </c>
       <c r="L47" t="n">
-        <v>70.64</v>
+        <v>73.64</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>86.36</v>
+        <v>84.3</v>
       </c>
       <c r="K48" t="n">
-        <v>-63.61</v>
+        <v>-62.1</v>
       </c>
       <c r="L48" t="n">
-        <v>107.26</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-56.37</v>
+        <v>-55.89</v>
       </c>
       <c r="K49" t="n">
-        <v>-72.64</v>
+        <v>-72.03</v>
       </c>
       <c r="L49" t="n">
-        <v>91.94</v>
+        <v>91.17</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-62.8</v>
+        <v>-59.13</v>
       </c>
       <c r="K50" t="n">
-        <v>-200.74</v>
+        <v>-189.01</v>
       </c>
       <c r="L50" t="n">
-        <v>210.33</v>
+        <v>198.05</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>36.84</v>
+        <v>40.14</v>
       </c>
       <c r="K51" t="n">
-        <v>-67.87</v>
+        <v>-73.95999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>77.23</v>
+        <v>84.15000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-28.69</v>
+        <v>-27.58</v>
       </c>
       <c r="K52" t="n">
-        <v>163.02</v>
+        <v>156.69</v>
       </c>
       <c r="L52" t="n">
-        <v>165.53</v>
+        <v>159.1</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>231.38</v>
+        <v>221.47</v>
       </c>
       <c r="K53" t="n">
-        <v>174.75</v>
+        <v>167.27</v>
       </c>
       <c r="L53" t="n">
-        <v>289.95</v>
+        <v>277.54</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>96.90000000000001</v>
+        <v>101.75</v>
       </c>
       <c r="K54" t="n">
-        <v>-89.16</v>
+        <v>-93.64</v>
       </c>
       <c r="L54" t="n">
-        <v>131.68</v>
+        <v>138.28</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>153.11</v>
+        <v>158.09</v>
       </c>
       <c r="K55" t="n">
-        <v>-15.86</v>
+        <v>-16.38</v>
       </c>
       <c r="L55" t="n">
-        <v>153.93</v>
+        <v>158.94</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-309.25</v>
+        <v>-301.44</v>
       </c>
       <c r="K56" t="n">
-        <v>101.92</v>
+        <v>99.34</v>
       </c>
       <c r="L56" t="n">
-        <v>325.62</v>
+        <v>317.39</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>139.76</v>
+        <v>139.37</v>
       </c>
       <c r="K57" t="n">
-        <v>223.89</v>
+        <v>223.26</v>
       </c>
       <c r="L57" t="n">
-        <v>263.92</v>
+        <v>263.19</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>154.62</v>
+        <v>154.61</v>
       </c>
       <c r="K58" t="n">
-        <v>243.47</v>
+        <v>243.46</v>
       </c>
       <c r="L58" t="n">
-        <v>288.42</v>
+        <v>288.4</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>8.34</v>
+        <v>8.25</v>
       </c>
       <c r="K59" t="n">
-        <v>81.89</v>
+        <v>81.02</v>
       </c>
       <c r="L59" t="n">
-        <v>82.31</v>
+        <v>81.44</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>64.84999999999999</v>
+        <v>62.46</v>
       </c>
       <c r="K60" t="n">
-        <v>76.72</v>
+        <v>73.89</v>
       </c>
       <c r="L60" t="n">
-        <v>100.45</v>
+        <v>96.75</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-55.38</v>
+        <v>-57.86</v>
       </c>
       <c r="K61" t="n">
-        <v>23.66</v>
+        <v>24.73</v>
       </c>
       <c r="L61" t="n">
-        <v>60.22</v>
+        <v>62.92</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-72.56999999999999</v>
+        <v>-71.90000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-49.26</v>
+        <v>-48.8</v>
       </c>
       <c r="L62" t="n">
-        <v>87.70999999999999</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-56.41</v>
+        <v>-61.15</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.130000000000001</v>
+        <v>-8.81</v>
       </c>
       <c r="L63" t="n">
-        <v>57</v>
+        <v>61.78</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>80.06999999999999</v>
+        <v>76.94</v>
       </c>
       <c r="K64" t="n">
-        <v>-80.09999999999999</v>
+        <v>-76.97</v>
       </c>
       <c r="L64" t="n">
-        <v>113.26</v>
+        <v>108.83</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.01</v>
+        <v>-5.71</v>
       </c>
       <c r="K65" t="n">
-        <v>187.17</v>
+        <v>177.78</v>
       </c>
       <c r="L65" t="n">
-        <v>187.27</v>
+        <v>177.87</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-121.21</v>
+        <v>-118.41</v>
       </c>
       <c r="K66" t="n">
-        <v>61.95</v>
+        <v>60.52</v>
       </c>
       <c r="L66" t="n">
-        <v>136.12</v>
+        <v>132.98</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>36.04</v>
+        <v>35.07</v>
       </c>
       <c r="K67" t="n">
-        <v>-171.44</v>
+        <v>-166.82</v>
       </c>
       <c r="L67" t="n">
-        <v>175.18</v>
+        <v>170.46</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>120.33</v>
+        <v>121.81</v>
       </c>
       <c r="K68" t="n">
-        <v>121.43</v>
+        <v>122.93</v>
       </c>
       <c r="L68" t="n">
-        <v>170.96</v>
+        <v>173.06</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-45.46</v>
+        <v>-49.26</v>
       </c>
       <c r="K69" t="n">
-        <v>111.04</v>
+        <v>120.32</v>
       </c>
       <c r="L69" t="n">
-        <v>119.99</v>
+        <v>130.01</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>63.29</v>
+        <v>63.25</v>
       </c>
       <c r="K70" t="n">
-        <v>-176.85</v>
+        <v>-176.75</v>
       </c>
       <c r="L70" t="n">
-        <v>187.83</v>
+        <v>187.73</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>260.96</v>
+        <v>252.04</v>
       </c>
       <c r="K71" t="n">
-        <v>-229.67</v>
+        <v>-221.82</v>
       </c>
       <c r="L71" t="n">
-        <v>347.63</v>
+        <v>335.75</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-26.78</v>
+        <v>-26.18</v>
       </c>
       <c r="K72" t="n">
-        <v>280.9</v>
+        <v>274.59</v>
       </c>
       <c r="L72" t="n">
-        <v>282.17</v>
+        <v>275.83</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-259.27</v>
+        <v>-252.35</v>
       </c>
       <c r="K73" t="n">
-        <v>-193.57</v>
+        <v>-188.4</v>
       </c>
       <c r="L73" t="n">
-        <v>323.56</v>
+        <v>314.92</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>42.13</v>
+        <v>46.18</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.49</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>42.79</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>41.99</v>
+        <v>40.31</v>
       </c>
       <c r="K75" t="n">
-        <v>93.48999999999999</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>102.49</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-22.17</v>
+        <v>-21.32</v>
       </c>
       <c r="K76" t="n">
-        <v>97.59999999999999</v>
+        <v>93.86</v>
       </c>
       <c r="L76" t="n">
-        <v>100.08</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-19.94</v>
+        <v>-19.18</v>
       </c>
       <c r="K77" t="n">
-        <v>-117.81</v>
+        <v>-113.36</v>
       </c>
       <c r="L77" t="n">
-        <v>119.48</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-21.88</v>
+        <v>-22.42</v>
       </c>
       <c r="K78" t="n">
-        <v>69.93000000000001</v>
+        <v>71.66</v>
       </c>
       <c r="L78" t="n">
-        <v>73.27</v>
+        <v>75.09</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>95.11</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-57.74</v>
+        <v>-55.89</v>
       </c>
       <c r="L79" t="n">
-        <v>111.27</v>
+        <v>107.71</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>132.19</v>
+        <v>130.27</v>
       </c>
       <c r="K80" t="n">
-        <v>-85.45999999999999</v>
+        <v>-84.22</v>
       </c>
       <c r="L80" t="n">
-        <v>157.41</v>
+        <v>155.12</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="K81" t="n">
-        <v>-130.97</v>
+        <v>-138.3</v>
       </c>
       <c r="L81" t="n">
-        <v>130.97</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>54.63</v>
+        <v>60.08</v>
       </c>
       <c r="K82" t="n">
-        <v>-58.62</v>
+        <v>-64.45999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>80.13</v>
+        <v>88.12</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-56.93</v>
+        <v>-60.7</v>
       </c>
       <c r="K83" t="n">
-        <v>-117.1</v>
+        <v>-124.85</v>
       </c>
       <c r="L83" t="n">
-        <v>130.21</v>
+        <v>138.82</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>179.6</v>
+        <v>181.29</v>
       </c>
       <c r="K84" t="n">
-        <v>-58.3</v>
+        <v>-58.84</v>
       </c>
       <c r="L84" t="n">
-        <v>188.83</v>
+        <v>190.6</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>137.19</v>
+        <v>135.89</v>
       </c>
       <c r="K85" t="n">
-        <v>148.29</v>
+        <v>146.88</v>
       </c>
       <c r="L85" t="n">
-        <v>202.02</v>
+        <v>200.1</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-212.41</v>
+        <v>-205.36</v>
       </c>
       <c r="K86" t="n">
-        <v>-297.11</v>
+        <v>-287.25</v>
       </c>
       <c r="L86" t="n">
-        <v>365.23</v>
+        <v>353.11</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>23.33</v>
+        <v>23.98</v>
       </c>
       <c r="K87" t="n">
-        <v>-204.59</v>
+        <v>-210.31</v>
       </c>
       <c r="L87" t="n">
-        <v>205.91</v>
+        <v>211.68</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>101.59</v>
+        <v>107.83</v>
       </c>
       <c r="K88" t="n">
-        <v>167.18</v>
+        <v>177.45</v>
       </c>
       <c r="L88" t="n">
-        <v>195.63</v>
+        <v>207.64</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -628,25 +628,25 @@
         <v>2.75</v>
       </c>
       <c r="F14" t="n">
-        <v>12.27</v>
+        <v>8.69</v>
       </c>
       <c r="G14" t="n">
-        <v>213.2</v>
+        <v>205</v>
       </c>
       <c r="H14" t="n">
-        <v>38.8</v>
+        <v>35.2</v>
       </c>
       <c r="I14" t="n">
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>33.16</v>
+        <v>40.48</v>
       </c>
       <c r="K14" t="n">
-        <v>38.96</v>
+        <v>46.2</v>
       </c>
       <c r="L14" t="n">
-        <v>51.16</v>
+        <v>61.43</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>3.07</v>
       </c>
       <c r="F15" t="n">
-        <v>13.46</v>
+        <v>9.18</v>
       </c>
       <c r="G15" t="n">
-        <v>211.9</v>
+        <v>228.9</v>
       </c>
       <c r="H15" t="n">
-        <v>42</v>
+        <v>34.6</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>12.92</v>
+        <v>13.3</v>
       </c>
       <c r="K15" t="n">
-        <v>47.71</v>
+        <v>58.22</v>
       </c>
       <c r="L15" t="n">
-        <v>49.43</v>
+        <v>59.72</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>3.81</v>
       </c>
       <c r="F16" t="n">
-        <v>13.81</v>
+        <v>10.88</v>
       </c>
       <c r="G16" t="n">
-        <v>221.2</v>
+        <v>235.9</v>
       </c>
       <c r="H16" t="n">
-        <v>36.6</v>
+        <v>39.2</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>82.14</v>
+        <v>98.58</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.88</v>
+        <v>-13.62</v>
       </c>
       <c r="L16" t="n">
-        <v>82.86</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>3.49</v>
       </c>
       <c r="F17" t="n">
-        <v>12.63</v>
+        <v>14.94</v>
       </c>
       <c r="G17" t="n">
-        <v>229</v>
+        <v>212.3</v>
       </c>
       <c r="H17" t="n">
-        <v>40.2</v>
+        <v>43.2</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-88.73999999999999</v>
+        <v>-116.75</v>
       </c>
       <c r="K17" t="n">
-        <v>-34.84</v>
+        <v>-49.18</v>
       </c>
       <c r="L17" t="n">
-        <v>95.34</v>
+        <v>126.69</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>3.75</v>
       </c>
       <c r="F18" t="n">
-        <v>12.95</v>
+        <v>14.95</v>
       </c>
       <c r="G18" t="n">
-        <v>236.1</v>
+        <v>218.6</v>
       </c>
       <c r="H18" t="n">
-        <v>45.4</v>
+        <v>46.7</v>
       </c>
       <c r="I18" t="n">
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>71.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="K18" t="n">
-        <v>79.39</v>
+        <v>95.69</v>
       </c>
       <c r="L18" t="n">
-        <v>107.11</v>
+        <v>130.34</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>3.7</v>
       </c>
       <c r="F19" t="n">
-        <v>12.98</v>
+        <v>12.68</v>
       </c>
       <c r="G19" t="n">
-        <v>210</v>
+        <v>219.3</v>
       </c>
       <c r="H19" t="n">
-        <v>34.5</v>
+        <v>33.6</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>49.54</v>
+        <v>53.79</v>
       </c>
       <c r="K19" t="n">
-        <v>-33.26</v>
+        <v>-49.95</v>
       </c>
       <c r="L19" t="n">
-        <v>59.67</v>
+        <v>73.41</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>2.83</v>
       </c>
       <c r="F20" t="n">
-        <v>12.91</v>
+        <v>10.37</v>
       </c>
       <c r="G20" t="n">
-        <v>214.4</v>
+        <v>217.8</v>
       </c>
       <c r="H20" t="n">
-        <v>41.4</v>
+        <v>35.8</v>
       </c>
       <c r="I20" t="n">
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-86.28</v>
+        <v>-106.2</v>
       </c>
       <c r="K20" t="n">
-        <v>-90.34999999999999</v>
+        <v>-112.21</v>
       </c>
       <c r="L20" t="n">
-        <v>124.93</v>
+        <v>154.5</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>3.98</v>
       </c>
       <c r="F21" t="n">
-        <v>13.32</v>
+        <v>13.8</v>
       </c>
       <c r="G21" t="n">
-        <v>222.2</v>
+        <v>226.1</v>
       </c>
       <c r="H21" t="n">
-        <v>41.6</v>
+        <v>39.8</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>124.69</v>
+        <v>151.17</v>
       </c>
       <c r="K21" t="n">
-        <v>72.13</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>144.05</v>
+        <v>172.56</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>3.96</v>
       </c>
       <c r="F22" t="n">
-        <v>13.56</v>
+        <v>13.01</v>
       </c>
       <c r="G22" t="n">
-        <v>205</v>
+        <v>230.9</v>
       </c>
       <c r="H22" t="n">
-        <v>39.6</v>
+        <v>31.2</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-49.39</v>
+        <v>-73.78</v>
       </c>
       <c r="K22" t="n">
-        <v>-136.71</v>
+        <v>-166.54</v>
       </c>
       <c r="L22" t="n">
-        <v>145.35</v>
+        <v>182.15</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>3.56</v>
       </c>
       <c r="F23" t="n">
-        <v>12.33</v>
+        <v>14.92</v>
       </c>
       <c r="G23" t="n">
-        <v>215.6</v>
+        <v>206.4</v>
       </c>
       <c r="H23" t="n">
-        <v>41.9</v>
+        <v>36.4</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-123.97</v>
+        <v>-163.71</v>
       </c>
       <c r="K23" t="n">
-        <v>-161.67</v>
+        <v>-228.63</v>
       </c>
       <c r="L23" t="n">
-        <v>203.73</v>
+        <v>281.2</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>3.73</v>
       </c>
       <c r="F24" t="n">
-        <v>13.06</v>
+        <v>11.86</v>
       </c>
       <c r="G24" t="n">
-        <v>212.1</v>
+        <v>220.9</v>
       </c>
       <c r="H24" t="n">
-        <v>38.6</v>
+        <v>34.7</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-30.95</v>
+        <v>-93.41</v>
       </c>
       <c r="K24" t="n">
-        <v>136.77</v>
+        <v>146.1</v>
       </c>
       <c r="L24" t="n">
-        <v>140.23</v>
+        <v>173.41</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>3.44</v>
       </c>
       <c r="F25" t="n">
-        <v>13.42</v>
+        <v>6.95</v>
       </c>
       <c r="G25" t="n">
-        <v>222.3</v>
+        <v>228.1</v>
       </c>
       <c r="H25" t="n">
-        <v>30.3</v>
+        <v>39.8</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>203.64</v>
+        <v>189.15</v>
       </c>
       <c r="K25" t="n">
-        <v>-152</v>
+        <v>-169.47</v>
       </c>
       <c r="L25" t="n">
-        <v>254.11</v>
+        <v>253.97</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>3.33</v>
       </c>
       <c r="F26" t="n">
-        <v>12.58</v>
+        <v>11.53</v>
       </c>
       <c r="G26" t="n">
-        <v>215</v>
+        <v>211.2</v>
       </c>
       <c r="H26" t="n">
-        <v>40.4</v>
+        <v>36.2</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>14.07</v>
+        <v>-24.27</v>
       </c>
       <c r="K26" t="n">
-        <v>-171.82</v>
+        <v>-225.35</v>
       </c>
       <c r="L26" t="n">
-        <v>172.4</v>
+        <v>226.66</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>3.83</v>
       </c>
       <c r="F27" t="n">
-        <v>12.63</v>
+        <v>11.93</v>
       </c>
       <c r="G27" t="n">
-        <v>213.1</v>
+        <v>212.3</v>
       </c>
       <c r="H27" t="n">
-        <v>37.8</v>
+        <v>35.2</v>
       </c>
       <c r="I27" t="n">
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-10.81</v>
+        <v>-29.92</v>
       </c>
       <c r="K27" t="n">
-        <v>-309.4</v>
+        <v>-363.86</v>
       </c>
       <c r="L27" t="n">
-        <v>309.59</v>
+        <v>365.09</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>4.02</v>
       </c>
       <c r="F28" t="n">
-        <v>13.02</v>
+        <v>10.69</v>
       </c>
       <c r="G28" t="n">
-        <v>232.6</v>
+        <v>220</v>
       </c>
       <c r="H28" t="n">
-        <v>34.2</v>
+        <v>45</v>
       </c>
       <c r="I28" t="n">
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>248.86</v>
+        <v>272.6</v>
       </c>
       <c r="K28" t="n">
-        <v>217.22</v>
+        <v>217.41</v>
       </c>
       <c r="L28" t="n">
-        <v>330.33</v>
+        <v>348.68</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>3.3</v>
       </c>
       <c r="F29" t="n">
-        <v>13.34</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>222.3</v>
+        <v>226.5</v>
       </c>
       <c r="H29" t="n">
-        <v>30.9</v>
+        <v>39.8</v>
       </c>
       <c r="I29" t="n">
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>1.21</v>
+        <v>0.17</v>
       </c>
       <c r="K29" t="n">
-        <v>68.11</v>
+        <v>79.78</v>
       </c>
       <c r="L29" t="n">
-        <v>68.12</v>
+        <v>79.79000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>3.2</v>
       </c>
       <c r="F30" t="n">
-        <v>12.77</v>
+        <v>8.75</v>
       </c>
       <c r="G30" t="n">
-        <v>214.4</v>
+        <v>215.1</v>
       </c>
       <c r="H30" t="n">
-        <v>35.4</v>
+        <v>35.9</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-32.08</v>
+        <v>-39.5</v>
       </c>
       <c r="K30" t="n">
-        <v>-39.07</v>
+        <v>-48.4</v>
       </c>
       <c r="L30" t="n">
-        <v>50.56</v>
+        <v>62.47</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>3.74</v>
       </c>
       <c r="F31" t="n">
-        <v>13.29</v>
+        <v>12.39</v>
       </c>
       <c r="G31" t="n">
-        <v>225.6</v>
+        <v>225.5</v>
       </c>
       <c r="H31" t="n">
-        <v>34.1</v>
+        <v>41.4</v>
       </c>
       <c r="I31" t="n">
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-31.51</v>
+        <v>-39.17</v>
       </c>
       <c r="K31" t="n">
-        <v>-53.96</v>
+        <v>-66.06</v>
       </c>
       <c r="L31" t="n">
-        <v>62.49</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>3.84</v>
       </c>
       <c r="F32" t="n">
-        <v>14.05</v>
+        <v>12.5</v>
       </c>
       <c r="G32" t="n">
-        <v>218.5</v>
+        <v>240.7</v>
       </c>
       <c r="H32" t="n">
-        <v>38.6</v>
+        <v>37.9</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-132.72</v>
+        <v>-148.61</v>
       </c>
       <c r="K32" t="n">
-        <v>-33.2</v>
+        <v>-36.98</v>
       </c>
       <c r="L32" t="n">
-        <v>136.81</v>
+        <v>153.14</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>13.39</v>
+        <v>7.12</v>
       </c>
       <c r="G33" t="n">
-        <v>211.2</v>
+        <v>227.4</v>
       </c>
       <c r="H33" t="n">
-        <v>34.9</v>
+        <v>34.2</v>
       </c>
       <c r="I33" t="n">
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>80.98</v>
+        <v>87.7</v>
       </c>
       <c r="K33" t="n">
-        <v>0.68</v>
+        <v>-0.88</v>
       </c>
       <c r="L33" t="n">
-        <v>80.98</v>
+        <v>87.70999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>4.11</v>
       </c>
       <c r="F34" t="n">
-        <v>12.69</v>
+        <v>14.95</v>
       </c>
       <c r="G34" t="n">
-        <v>223.5</v>
+        <v>213.5</v>
       </c>
       <c r="H34" t="n">
-        <v>44.9</v>
+        <v>40.4</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.58</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-48.83</v>
+        <v>-79.89</v>
       </c>
       <c r="L34" t="n">
-        <v>48.86</v>
+        <v>80.31</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>3.78</v>
       </c>
       <c r="F35" t="n">
-        <v>13.1</v>
+        <v>8.06</v>
       </c>
       <c r="G35" t="n">
-        <v>225.2</v>
+        <v>221.7</v>
       </c>
       <c r="H35" t="n">
-        <v>37.1</v>
+        <v>41.2</v>
       </c>
       <c r="I35" t="n">
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-175.61</v>
+        <v>-185.87</v>
       </c>
       <c r="K35" t="n">
-        <v>118</v>
+        <v>112.53</v>
       </c>
       <c r="L35" t="n">
-        <v>211.58</v>
+        <v>217.28</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>3.67</v>
       </c>
       <c r="F36" t="n">
-        <v>12</v>
+        <v>13.55</v>
       </c>
       <c r="G36" t="n">
-        <v>213.4</v>
+        <v>199.7</v>
       </c>
       <c r="H36" t="n">
-        <v>41.7</v>
+        <v>35.3</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-21.08</v>
+        <v>-46.3</v>
       </c>
       <c r="K36" t="n">
-        <v>90.95</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>93.36</v>
+        <v>107.68</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>3.29</v>
       </c>
       <c r="F37" t="n">
-        <v>13.18</v>
+        <v>11.09</v>
       </c>
       <c r="G37" t="n">
-        <v>217.2</v>
+        <v>223.2</v>
       </c>
       <c r="H37" t="n">
-        <v>42.4</v>
+        <v>37.3</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>84.89</v>
+        <v>87.55</v>
       </c>
       <c r="K37" t="n">
-        <v>-90.81999999999999</v>
+        <v>-114.93</v>
       </c>
       <c r="L37" t="n">
-        <v>124.32</v>
+        <v>144.48</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>2.49</v>
       </c>
       <c r="F38" t="n">
-        <v>12.4</v>
+        <v>7.69</v>
       </c>
       <c r="G38" t="n">
-        <v>210.4</v>
+        <v>207.6</v>
       </c>
       <c r="H38" t="n">
-        <v>37.6</v>
+        <v>33.9</v>
       </c>
       <c r="I38" t="n">
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-43.78</v>
+        <v>-100.29</v>
       </c>
       <c r="K38" t="n">
-        <v>4.38</v>
+        <v>-57.41</v>
       </c>
       <c r="L38" t="n">
-        <v>44</v>
+        <v>115.56</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>2.82</v>
       </c>
       <c r="F39" t="n">
-        <v>12.47</v>
+        <v>11.5</v>
       </c>
       <c r="G39" t="n">
-        <v>219.7</v>
+        <v>209</v>
       </c>
       <c r="H39" t="n">
-        <v>37.7</v>
+        <v>38.5</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>-70.04000000000001</v>
+        <v>-92.86</v>
       </c>
       <c r="K39" t="n">
-        <v>-110.67</v>
+        <v>-156.92</v>
       </c>
       <c r="L39" t="n">
-        <v>130.97</v>
+        <v>182.34</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>3.17</v>
       </c>
       <c r="F40" t="n">
-        <v>13.32</v>
+        <v>14.34</v>
       </c>
       <c r="G40" t="n">
-        <v>216.9</v>
+        <v>226</v>
       </c>
       <c r="H40" t="n">
-        <v>46.4</v>
+        <v>37.1</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-69.8</v>
+        <v>-110.97</v>
       </c>
       <c r="K40" t="n">
-        <v>-133.18</v>
+        <v>-174.69</v>
       </c>
       <c r="L40" t="n">
-        <v>150.36</v>
+        <v>206.96</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>4.36</v>
       </c>
       <c r="F41" t="n">
-        <v>11.86</v>
+        <v>12.76</v>
       </c>
       <c r="G41" t="n">
-        <v>228.3</v>
+        <v>197</v>
       </c>
       <c r="H41" t="n">
-        <v>36.9</v>
+        <v>42.8</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>102.67</v>
+        <v>111.32</v>
       </c>
       <c r="K41" t="n">
-        <v>-242.85</v>
+        <v>-299.65</v>
       </c>
       <c r="L41" t="n">
-        <v>263.66</v>
+        <v>319.66</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>3.87</v>
       </c>
       <c r="F42" t="n">
-        <v>13.12</v>
+        <v>10.27</v>
       </c>
       <c r="G42" t="n">
-        <v>226.4</v>
+        <v>222.1</v>
       </c>
       <c r="H42" t="n">
-        <v>33.6</v>
+        <v>41.9</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-11.12</v>
+        <v>-83.97</v>
       </c>
       <c r="K42" t="n">
-        <v>193.81</v>
+        <v>211.11</v>
       </c>
       <c r="L42" t="n">
-        <v>194.13</v>
+        <v>227.2</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>4.77</v>
       </c>
       <c r="F43" t="n">
-        <v>12.41</v>
+        <v>14.95</v>
       </c>
       <c r="G43" t="n">
-        <v>234.9</v>
+        <v>208</v>
       </c>
       <c r="H43" t="n">
-        <v>39.3</v>
+        <v>46.1</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>-17.95</v>
+        <v>-31.02</v>
       </c>
       <c r="K43" t="n">
-        <v>241.15</v>
+        <v>273.98</v>
       </c>
       <c r="L43" t="n">
-        <v>241.82</v>
+        <v>275.73</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>2.78</v>
       </c>
       <c r="F44" t="n">
-        <v>13.17</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>225.7</v>
+        <v>223.1</v>
       </c>
       <c r="H44" t="n">
-        <v>37.8</v>
+        <v>41.5</v>
       </c>
       <c r="I44" t="n">
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.1</v>
+        <v>-65.77</v>
       </c>
       <c r="K44" t="n">
-        <v>-42.08</v>
+        <v>-49.6</v>
       </c>
       <c r="L44" t="n">
-        <v>70.13</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>4.16</v>
       </c>
       <c r="F45" t="n">
-        <v>13.82</v>
+        <v>12.57</v>
       </c>
       <c r="G45" t="n">
-        <v>211.2</v>
+        <v>236.1</v>
       </c>
       <c r="H45" t="n">
-        <v>39.1</v>
+        <v>34.3</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>40.75</v>
+        <v>45.52</v>
       </c>
       <c r="K45" t="n">
-        <v>71.45</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>82.26000000000001</v>
+        <v>94.36</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>5.54</v>
       </c>
       <c r="F46" t="n">
-        <v>12.7</v>
+        <v>14.95</v>
       </c>
       <c r="G46" t="n">
-        <v>219.9</v>
+        <v>213.7</v>
       </c>
       <c r="H46" t="n">
-        <v>43.7</v>
+        <v>38.6</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-49.64</v>
+        <v>-55.13</v>
       </c>
       <c r="K46" t="n">
-        <v>-91.12</v>
+        <v>-101.39</v>
       </c>
       <c r="L46" t="n">
-        <v>103.76</v>
+        <v>115.41</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>4.29</v>
       </c>
       <c r="F47" t="n">
-        <v>12.98</v>
+        <v>14.95</v>
       </c>
       <c r="G47" t="n">
-        <v>208.7</v>
+        <v>219.4</v>
       </c>
       <c r="H47" t="n">
-        <v>45.8</v>
+        <v>33</v>
       </c>
       <c r="I47" t="n">
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>69.63</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-23.98</v>
+        <v>-34.7</v>
       </c>
       <c r="L47" t="n">
-        <v>73.64</v>
+        <v>88.20999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>4.88</v>
       </c>
       <c r="F48" t="n">
-        <v>13.66</v>
+        <v>12.78</v>
       </c>
       <c r="G48" t="n">
-        <v>222.9</v>
+        <v>232.9</v>
       </c>
       <c r="H48" t="n">
-        <v>31.5</v>
+        <v>40.1</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>84.3</v>
+        <v>88.88</v>
       </c>
       <c r="K48" t="n">
-        <v>-62.1</v>
+        <v>-70.63</v>
       </c>
       <c r="L48" t="n">
-        <v>104.7</v>
+        <v>113.52</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>4.4</v>
       </c>
       <c r="F49" t="n">
-        <v>13.75</v>
+        <v>13.22</v>
       </c>
       <c r="G49" t="n">
-        <v>221.2</v>
+        <v>234.6</v>
       </c>
       <c r="H49" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-55.89</v>
+        <v>-71.70999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-72.03</v>
+        <v>-88.56999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>91.17</v>
+        <v>113.96</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>3.89</v>
       </c>
       <c r="F50" t="n">
-        <v>12.83</v>
+        <v>11.6</v>
       </c>
       <c r="G50" t="n">
-        <v>217.7</v>
+        <v>216.3</v>
       </c>
       <c r="H50" t="n">
-        <v>35.6</v>
+        <v>37.5</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-59.13</v>
+        <v>-67.08</v>
       </c>
       <c r="K50" t="n">
-        <v>-189.01</v>
+        <v>-203.08</v>
       </c>
       <c r="L50" t="n">
-        <v>198.05</v>
+        <v>213.87</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>3.21</v>
       </c>
       <c r="F51" t="n">
-        <v>13.33</v>
+        <v>9.6</v>
       </c>
       <c r="G51" t="n">
-        <v>235.4</v>
+        <v>226.3</v>
       </c>
       <c r="H51" t="n">
-        <v>33.6</v>
+        <v>46.3</v>
       </c>
       <c r="I51" t="n">
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>40.14</v>
+        <v>23.29</v>
       </c>
       <c r="K51" t="n">
-        <v>-73.95999999999999</v>
+        <v>-103.38</v>
       </c>
       <c r="L51" t="n">
-        <v>84.15000000000001</v>
+        <v>105.97</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>3.4</v>
       </c>
       <c r="F52" t="n">
-        <v>13.09</v>
+        <v>13.13</v>
       </c>
       <c r="G52" t="n">
-        <v>203.9</v>
+        <v>221.5</v>
       </c>
       <c r="H52" t="n">
-        <v>41.9</v>
+        <v>30.6</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-27.58</v>
+        <v>-39.99</v>
       </c>
       <c r="K52" t="n">
-        <v>156.69</v>
+        <v>168.58</v>
       </c>
       <c r="L52" t="n">
-        <v>159.1</v>
+        <v>173.26</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>4.77</v>
       </c>
       <c r="F53" t="n">
-        <v>12.63</v>
+        <v>14.95</v>
       </c>
       <c r="G53" t="n">
-        <v>214.8</v>
+        <v>212.3</v>
       </c>
       <c r="H53" t="n">
-        <v>37.1</v>
+        <v>36.1</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>221.47</v>
+        <v>236.35</v>
       </c>
       <c r="K53" t="n">
-        <v>167.27</v>
+        <v>163.9</v>
       </c>
       <c r="L53" t="n">
-        <v>277.54</v>
+        <v>287.62</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>4.27</v>
       </c>
       <c r="F54" t="n">
-        <v>13.43</v>
+        <v>12.33</v>
       </c>
       <c r="G54" t="n">
-        <v>204.8</v>
+        <v>228.2</v>
       </c>
       <c r="H54" t="n">
-        <v>34.4</v>
+        <v>31</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>101.75</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-93.64</v>
+        <v>-156.16</v>
       </c>
       <c r="L54" t="n">
-        <v>138.28</v>
+        <v>171.03</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>4.51</v>
       </c>
       <c r="F55" t="n">
-        <v>13.71</v>
+        <v>14.95</v>
       </c>
       <c r="G55" t="n">
-        <v>222.4</v>
+        <v>233.9</v>
       </c>
       <c r="H55" t="n">
-        <v>31.1</v>
+        <v>39.9</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>158.09</v>
+        <v>167.11</v>
       </c>
       <c r="K55" t="n">
-        <v>-16.38</v>
+        <v>-53.28</v>
       </c>
       <c r="L55" t="n">
-        <v>158.94</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>4.01</v>
       </c>
       <c r="F56" t="n">
-        <v>12.81</v>
+        <v>12.23</v>
       </c>
       <c r="G56" t="n">
-        <v>213.6</v>
+        <v>215.9</v>
       </c>
       <c r="H56" t="n">
-        <v>35.8</v>
+        <v>35.4</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-301.44</v>
+        <v>-339.55</v>
       </c>
       <c r="K56" t="n">
-        <v>99.34</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>317.39</v>
+        <v>347.72</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>3.9</v>
       </c>
       <c r="F57" t="n">
-        <v>13.18</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>230.4</v>
+        <v>223.2</v>
       </c>
       <c r="H57" t="n">
-        <v>41.9</v>
+        <v>43.8</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>139.37</v>
+        <v>142.79</v>
       </c>
       <c r="K57" t="n">
-        <v>223.26</v>
+        <v>236.58</v>
       </c>
       <c r="L57" t="n">
-        <v>263.19</v>
+        <v>276.33</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>4.19</v>
       </c>
       <c r="F58" t="n">
-        <v>12.68</v>
+        <v>14.95</v>
       </c>
       <c r="G58" t="n">
-        <v>225.8</v>
+        <v>213.3</v>
       </c>
       <c r="H58" t="n">
-        <v>45.1</v>
+        <v>41.5</v>
       </c>
       <c r="I58" t="n">
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>154.61</v>
+        <v>184.46</v>
       </c>
       <c r="K58" t="n">
-        <v>243.46</v>
+        <v>268.15</v>
       </c>
       <c r="L58" t="n">
-        <v>288.4</v>
+        <v>325.47</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>3.95</v>
       </c>
       <c r="F59" t="n">
-        <v>13.01</v>
+        <v>13.67</v>
       </c>
       <c r="G59" t="n">
-        <v>233.7</v>
+        <v>219.9</v>
       </c>
       <c r="H59" t="n">
-        <v>42.4</v>
+        <v>45.5</v>
       </c>
       <c r="I59" t="n">
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>8.25</v>
+        <v>9.32</v>
       </c>
       <c r="K59" t="n">
-        <v>81.02</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>81.44</v>
+        <v>96.69</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>4.09</v>
       </c>
       <c r="F60" t="n">
-        <v>12.74</v>
+        <v>14.95</v>
       </c>
       <c r="G60" t="n">
-        <v>215</v>
+        <v>214.5</v>
       </c>
       <c r="H60" t="n">
-        <v>46.2</v>
+        <v>36.1</v>
       </c>
       <c r="I60" t="n">
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>62.46</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>73.89</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>96.75</v>
+        <v>112.75</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>4.17</v>
       </c>
       <c r="F61" t="n">
-        <v>12.8</v>
+        <v>14.22</v>
       </c>
       <c r="G61" t="n">
-        <v>211.5</v>
+        <v>215.8</v>
       </c>
       <c r="H61" t="n">
-        <v>37.3</v>
+        <v>34.4</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-57.86</v>
+        <v>-68.01000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>24.73</v>
+        <v>26.52</v>
       </c>
       <c r="L61" t="n">
-        <v>62.92</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>3.29</v>
       </c>
       <c r="F62" t="n">
-        <v>13.08</v>
+        <v>10.47</v>
       </c>
       <c r="G62" t="n">
-        <v>226.7</v>
+        <v>221.2</v>
       </c>
       <c r="H62" t="n">
-        <v>36.9</v>
+        <v>42</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-71.90000000000001</v>
+        <v>-89.09999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-48.8</v>
+        <v>-61.78</v>
       </c>
       <c r="L62" t="n">
-        <v>86.90000000000001</v>
+        <v>108.42</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>3.73</v>
       </c>
       <c r="F63" t="n">
-        <v>13.03</v>
+        <v>14.95</v>
       </c>
       <c r="G63" t="n">
-        <v>212.5</v>
+        <v>220.4</v>
       </c>
       <c r="H63" t="n">
-        <v>40.2</v>
+        <v>34.9</v>
       </c>
       <c r="I63" t="n">
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-61.15</v>
+        <v>-80.04000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.81</v>
+        <v>-16.82</v>
       </c>
       <c r="L63" t="n">
-        <v>61.78</v>
+        <v>81.79000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>4.36</v>
       </c>
       <c r="F64" t="n">
-        <v>13.19</v>
+        <v>14.26</v>
       </c>
       <c r="G64" t="n">
-        <v>227.6</v>
+        <v>223.5</v>
       </c>
       <c r="H64" t="n">
-        <v>37.1</v>
+        <v>42.4</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>76.94</v>
+        <v>93.16</v>
       </c>
       <c r="K64" t="n">
-        <v>-76.97</v>
+        <v>-98.55</v>
       </c>
       <c r="L64" t="n">
-        <v>108.83</v>
+        <v>135.61</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>4.18</v>
       </c>
       <c r="F65" t="n">
-        <v>12.88</v>
+        <v>11.98</v>
       </c>
       <c r="G65" t="n">
         <v>217.3</v>
       </c>
       <c r="H65" t="n">
-        <v>35.3</v>
+        <v>37.3</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.71</v>
+        <v>-14.94</v>
       </c>
       <c r="K65" t="n">
-        <v>177.78</v>
+        <v>197.58</v>
       </c>
       <c r="L65" t="n">
-        <v>177.87</v>
+        <v>198.14</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>3.35</v>
       </c>
       <c r="F66" t="n">
-        <v>12.19</v>
+        <v>11.5</v>
       </c>
       <c r="G66" t="n">
-        <v>216.2</v>
+        <v>203.6</v>
       </c>
       <c r="H66" t="n">
-        <v>38.4</v>
+        <v>36.7</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>-118.41</v>
+        <v>-140.45</v>
       </c>
       <c r="K66" t="n">
-        <v>60.52</v>
+        <v>58.91</v>
       </c>
       <c r="L66" t="n">
-        <v>132.98</v>
+        <v>152.3</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>4.8</v>
       </c>
       <c r="F67" t="n">
-        <v>12.52</v>
+        <v>14.95</v>
       </c>
       <c r="G67" t="n">
-        <v>202.9</v>
+        <v>210.1</v>
       </c>
       <c r="H67" t="n">
-        <v>38.6</v>
+        <v>30.1</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>35.07</v>
+        <v>28.1</v>
       </c>
       <c r="K67" t="n">
-        <v>-166.82</v>
+        <v>-203.92</v>
       </c>
       <c r="L67" t="n">
-        <v>170.46</v>
+        <v>205.85</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>4.1</v>
       </c>
       <c r="F68" t="n">
-        <v>13.18</v>
+        <v>14.95</v>
       </c>
       <c r="G68" t="n">
-        <v>216.4</v>
+        <v>223.2</v>
       </c>
       <c r="H68" t="n">
-        <v>42.5</v>
+        <v>36.8</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>121.81</v>
+        <v>127.52</v>
       </c>
       <c r="K68" t="n">
-        <v>122.93</v>
+        <v>132.2</v>
       </c>
       <c r="L68" t="n">
-        <v>173.06</v>
+        <v>183.68</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>4.14</v>
       </c>
       <c r="F69" t="n">
-        <v>12.39</v>
+        <v>14.85</v>
       </c>
       <c r="G69" t="n">
-        <v>228.6</v>
+        <v>207.5</v>
       </c>
       <c r="H69" t="n">
-        <v>35.4</v>
+        <v>42.9</v>
       </c>
       <c r="I69" t="n">
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-49.26</v>
+        <v>-120.57</v>
       </c>
       <c r="K69" t="n">
-        <v>120.32</v>
+        <v>62.69</v>
       </c>
       <c r="L69" t="n">
-        <v>130.01</v>
+        <v>135.89</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>4.37</v>
       </c>
       <c r="F70" t="n">
-        <v>12.94</v>
+        <v>14.95</v>
       </c>
       <c r="G70" t="n">
-        <v>214</v>
+        <v>218.5</v>
       </c>
       <c r="H70" t="n">
-        <v>38.8</v>
+        <v>35.6</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>63.25</v>
+        <v>41.46</v>
       </c>
       <c r="K70" t="n">
-        <v>-176.75</v>
+        <v>-211.17</v>
       </c>
       <c r="L70" t="n">
-        <v>187.73</v>
+        <v>215.2</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>4.03</v>
       </c>
       <c r="F71" t="n">
-        <v>12.11</v>
+        <v>14.33</v>
       </c>
       <c r="G71" t="n">
-        <v>217</v>
+        <v>201.8</v>
       </c>
       <c r="H71" t="n">
-        <v>34.3</v>
+        <v>37.1</v>
       </c>
       <c r="I71" t="n">
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>252.04</v>
+        <v>283.12</v>
       </c>
       <c r="K71" t="n">
-        <v>-221.82</v>
+        <v>-294.24</v>
       </c>
       <c r="L71" t="n">
-        <v>335.75</v>
+        <v>408.34</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>3.51</v>
       </c>
       <c r="F72" t="n">
-        <v>13.18</v>
+        <v>14.02</v>
       </c>
       <c r="G72" t="n">
-        <v>233.3</v>
+        <v>223.3</v>
       </c>
       <c r="H72" t="n">
-        <v>42.2</v>
+        <v>45.3</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-26.18</v>
+        <v>-62.21</v>
       </c>
       <c r="K72" t="n">
-        <v>274.59</v>
+        <v>314.3</v>
       </c>
       <c r="L72" t="n">
-        <v>275.83</v>
+        <v>320.4</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>3.99</v>
       </c>
       <c r="F73" t="n">
-        <v>13.34</v>
+        <v>14.34</v>
       </c>
       <c r="G73" t="n">
-        <v>227.7</v>
+        <v>226.5</v>
       </c>
       <c r="H73" t="n">
-        <v>32.3</v>
+        <v>42.5</v>
       </c>
       <c r="I73" t="n">
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-252.35</v>
+        <v>-315.69</v>
       </c>
       <c r="K73" t="n">
-        <v>-188.4</v>
+        <v>-242.51</v>
       </c>
       <c r="L73" t="n">
-        <v>314.92</v>
+        <v>398.08</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>4.45</v>
       </c>
       <c r="F74" t="n">
-        <v>13.03</v>
+        <v>14.95</v>
       </c>
       <c r="G74" t="n">
-        <v>218.2</v>
+        <v>220.3</v>
       </c>
       <c r="H74" t="n">
-        <v>40.1</v>
+        <v>37.8</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>46.18</v>
+        <v>53.45</v>
       </c>
       <c r="K74" t="n">
-        <v>-8.210000000000001</v>
+        <v>-14.23</v>
       </c>
       <c r="L74" t="n">
-        <v>46.9</v>
+        <v>55.31</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>5.4</v>
       </c>
       <c r="F75" t="n">
-        <v>13.55</v>
+        <v>14.95</v>
       </c>
       <c r="G75" t="n">
-        <v>216.2</v>
+        <v>230.6</v>
       </c>
       <c r="H75" t="n">
-        <v>46</v>
+        <v>36.7</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>40.31</v>
+        <v>43.97</v>
       </c>
       <c r="K75" t="n">
-        <v>89.76000000000001</v>
+        <v>101.1</v>
       </c>
       <c r="L75" t="n">
-        <v>98.40000000000001</v>
+        <v>110.25</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>4.01</v>
       </c>
       <c r="F76" t="n">
-        <v>13.13</v>
+        <v>13.14</v>
       </c>
       <c r="G76" t="n">
-        <v>219.5</v>
+        <v>222.3</v>
       </c>
       <c r="H76" t="n">
-        <v>36.8</v>
+        <v>38.4</v>
       </c>
       <c r="I76" t="n">
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.32</v>
+        <v>-25.54</v>
       </c>
       <c r="K76" t="n">
-        <v>93.86</v>
+        <v>107.66</v>
       </c>
       <c r="L76" t="n">
-        <v>96.25</v>
+        <v>110.65</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>4.08</v>
       </c>
       <c r="F77" t="n">
-        <v>13.77</v>
+        <v>14.95</v>
       </c>
       <c r="G77" t="n">
-        <v>231</v>
+        <v>235.1</v>
       </c>
       <c r="H77" t="n">
-        <v>41.9</v>
+        <v>44.1</v>
       </c>
       <c r="I77" t="n">
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-19.18</v>
+        <v>-25.76</v>
       </c>
       <c r="K77" t="n">
-        <v>-113.36</v>
+        <v>-135.8</v>
       </c>
       <c r="L77" t="n">
-        <v>114.97</v>
+        <v>138.23</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>3.78</v>
       </c>
       <c r="F78" t="n">
-        <v>13.03</v>
+        <v>10.87</v>
       </c>
       <c r="G78" t="n">
-        <v>207</v>
+        <v>220.2</v>
       </c>
       <c r="H78" t="n">
-        <v>33.8</v>
+        <v>32.2</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-22.42</v>
+        <v>-31.73</v>
       </c>
       <c r="K78" t="n">
-        <v>71.66</v>
+        <v>85.11</v>
       </c>
       <c r="L78" t="n">
-        <v>75.09</v>
+        <v>90.84</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>4.43</v>
       </c>
       <c r="F79" t="n">
-        <v>12.82</v>
+        <v>14.95</v>
       </c>
       <c r="G79" t="n">
-        <v>225.6</v>
+        <v>216</v>
       </c>
       <c r="H79" t="n">
-        <v>49</v>
+        <v>41.4</v>
       </c>
       <c r="I79" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>92.06999999999999</v>
+        <v>109.9</v>
       </c>
       <c r="K79" t="n">
-        <v>-55.89</v>
+        <v>-71.62</v>
       </c>
       <c r="L79" t="n">
-        <v>107.71</v>
+        <v>131.18</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>4.79</v>
       </c>
       <c r="F80" t="n">
-        <v>12.47</v>
+        <v>14.95</v>
       </c>
       <c r="G80" t="n">
-        <v>213.2</v>
+        <v>209.1</v>
       </c>
       <c r="H80" t="n">
-        <v>39.4</v>
+        <v>35.3</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>130.27</v>
+        <v>145.64</v>
       </c>
       <c r="K80" t="n">
-        <v>-84.22</v>
+        <v>-120.5</v>
       </c>
       <c r="L80" t="n">
-        <v>155.12</v>
+        <v>189.03</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>5.79</v>
       </c>
       <c r="F81" t="n">
-        <v>13.06</v>
+        <v>14.95</v>
       </c>
       <c r="G81" t="n">
-        <v>221.2</v>
+        <v>220.9</v>
       </c>
       <c r="H81" t="n">
-        <v>41.2</v>
+        <v>39.3</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>0.25</v>
+        <v>-28.83</v>
       </c>
       <c r="K81" t="n">
-        <v>-138.3</v>
+        <v>-154.1</v>
       </c>
       <c r="L81" t="n">
-        <v>138.3</v>
+        <v>156.77</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>3.73</v>
       </c>
       <c r="F82" t="n">
-        <v>13.42</v>
+        <v>12.27</v>
       </c>
       <c r="G82" t="n">
-        <v>217.1</v>
+        <v>228.1</v>
       </c>
       <c r="H82" t="n">
-        <v>36.8</v>
+        <v>37.2</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>60.08</v>
+        <v>27.49</v>
       </c>
       <c r="K82" t="n">
-        <v>-64.45999999999999</v>
+        <v>-99.14</v>
       </c>
       <c r="L82" t="n">
-        <v>88.12</v>
+        <v>102.88</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>4.21</v>
       </c>
       <c r="F83" t="n">
-        <v>12.96</v>
+        <v>14.13</v>
       </c>
       <c r="G83" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="H83" t="n">
-        <v>37.1</v>
+        <v>42.1</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-60.7</v>
+        <v>-85.06</v>
       </c>
       <c r="K83" t="n">
-        <v>-124.85</v>
+        <v>-156.68</v>
       </c>
       <c r="L83" t="n">
-        <v>138.82</v>
+        <v>178.28</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>4.75</v>
       </c>
       <c r="F84" t="n">
-        <v>13.59</v>
+        <v>14.95</v>
       </c>
       <c r="G84" t="n">
-        <v>220</v>
+        <v>231.4</v>
       </c>
       <c r="H84" t="n">
-        <v>38</v>
+        <v>38.6</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>181.29</v>
+        <v>196.27</v>
       </c>
       <c r="K84" t="n">
-        <v>-58.84</v>
+        <v>-101.43</v>
       </c>
       <c r="L84" t="n">
-        <v>190.6</v>
+        <v>220.93</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>4.67</v>
       </c>
       <c r="F85" t="n">
-        <v>13.03</v>
+        <v>14.95</v>
       </c>
       <c r="G85" t="n">
-        <v>212.2</v>
+        <v>220.3</v>
       </c>
       <c r="H85" t="n">
-        <v>42.4</v>
+        <v>34.7</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>135.89</v>
+        <v>146.85</v>
       </c>
       <c r="K85" t="n">
-        <v>146.88</v>
+        <v>162.36</v>
       </c>
       <c r="L85" t="n">
-        <v>200.1</v>
+        <v>218.92</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>4.27</v>
       </c>
       <c r="F86" t="n">
-        <v>12.89</v>
+        <v>13.78</v>
       </c>
       <c r="G86" t="n">
-        <v>207.7</v>
+        <v>217.5</v>
       </c>
       <c r="H86" t="n">
-        <v>35.9</v>
+        <v>32.5</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-205.36</v>
+        <v>-242.29</v>
       </c>
       <c r="K86" t="n">
-        <v>-287.25</v>
+        <v>-325.65</v>
       </c>
       <c r="L86" t="n">
-        <v>353.11</v>
+        <v>405.9</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>3.52</v>
       </c>
       <c r="F87" t="n">
-        <v>12.69</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>217.1</v>
+        <v>213.5</v>
       </c>
       <c r="H87" t="n">
-        <v>40.7</v>
+        <v>37.2</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>23.98</v>
+        <v>-3.16</v>
       </c>
       <c r="K87" t="n">
-        <v>-210.31</v>
+        <v>-237.38</v>
       </c>
       <c r="L87" t="n">
-        <v>211.68</v>
+        <v>237.4</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>4.24</v>
       </c>
       <c r="F88" t="n">
-        <v>13.07</v>
+        <v>14.95</v>
       </c>
       <c r="G88" t="n">
-        <v>227.2</v>
+        <v>221</v>
       </c>
       <c r="H88" t="n">
-        <v>41</v>
+        <v>42.2</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>107.83</v>
+        <v>121.7</v>
       </c>
       <c r="K88" t="n">
-        <v>177.45</v>
+        <v>212.11</v>
       </c>
       <c r="L88" t="n">
-        <v>207.64</v>
+        <v>244.54</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>40.48</v>
+        <v>46.06</v>
       </c>
       <c r="K14" t="n">
-        <v>46.2</v>
+        <v>52.57</v>
       </c>
       <c r="L14" t="n">
-        <v>61.43</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>13.3</v>
+        <v>14.51</v>
       </c>
       <c r="K15" t="n">
-        <v>58.22</v>
+        <v>63.51</v>
       </c>
       <c r="L15" t="n">
-        <v>59.72</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>98.58</v>
+        <v>111.87</v>
       </c>
       <c r="K16" t="n">
-        <v>-13.62</v>
+        <v>-15.46</v>
       </c>
       <c r="L16" t="n">
-        <v>99.51000000000001</v>
+        <v>112.93</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-116.75</v>
+        <v>-132.7</v>
       </c>
       <c r="K17" t="n">
-        <v>-49.18</v>
+        <v>-55.89</v>
       </c>
       <c r="L17" t="n">
-        <v>126.69</v>
+        <v>143.99</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>88.5</v>
+        <v>100.46</v>
       </c>
       <c r="K18" t="n">
-        <v>95.69</v>
+        <v>108.62</v>
       </c>
       <c r="L18" t="n">
-        <v>130.34</v>
+        <v>147.95</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>53.79</v>
+        <v>57.65</v>
       </c>
       <c r="K19" t="n">
-        <v>-49.95</v>
+        <v>-53.53</v>
       </c>
       <c r="L19" t="n">
-        <v>73.41</v>
+        <v>78.67</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-106.2</v>
+        <v>-120.85</v>
       </c>
       <c r="K20" t="n">
-        <v>-112.21</v>
+        <v>-127.69</v>
       </c>
       <c r="L20" t="n">
-        <v>154.5</v>
+        <v>175.81</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>151.17</v>
+        <v>171.8</v>
       </c>
       <c r="K21" t="n">
-        <v>83.20999999999999</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>172.56</v>
+        <v>196.11</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-73.78</v>
+        <v>-83.84999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-166.54</v>
+        <v>-189.28</v>
       </c>
       <c r="L22" t="n">
-        <v>182.15</v>
+        <v>207.02</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-163.71</v>
+        <v>-186.36</v>
       </c>
       <c r="K23" t="n">
-        <v>-228.63</v>
+        <v>-260.26</v>
       </c>
       <c r="L23" t="n">
-        <v>281.2</v>
+        <v>320.1</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-93.41</v>
+        <v>-106.35</v>
       </c>
       <c r="K24" t="n">
-        <v>146.1</v>
+        <v>166.35</v>
       </c>
       <c r="L24" t="n">
-        <v>173.41</v>
+        <v>197.44</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>189.15</v>
+        <v>212.43</v>
       </c>
       <c r="K25" t="n">
-        <v>-169.47</v>
+        <v>-190.33</v>
       </c>
       <c r="L25" t="n">
-        <v>253.97</v>
+        <v>285.22</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>-24.27</v>
+        <v>-26.89</v>
       </c>
       <c r="K26" t="n">
-        <v>-225.35</v>
+        <v>-249.68</v>
       </c>
       <c r="L26" t="n">
-        <v>226.66</v>
+        <v>251.12</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-29.92</v>
+        <v>-32.28</v>
       </c>
       <c r="K27" t="n">
-        <v>-363.86</v>
+        <v>-392.63</v>
       </c>
       <c r="L27" t="n">
-        <v>365.09</v>
+        <v>393.96</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>272.6</v>
+        <v>312.05</v>
       </c>
       <c r="K28" t="n">
-        <v>217.41</v>
+        <v>248.87</v>
       </c>
       <c r="L28" t="n">
-        <v>348.68</v>
+        <v>399.14</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="K29" t="n">
-        <v>79.78</v>
+        <v>90.77</v>
       </c>
       <c r="L29" t="n">
-        <v>79.79000000000001</v>
+        <v>90.77</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-39.5</v>
+        <v>-44.95</v>
       </c>
       <c r="K30" t="n">
-        <v>-48.4</v>
+        <v>-55.08</v>
       </c>
       <c r="L30" t="n">
-        <v>62.47</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-39.17</v>
+        <v>-42.63</v>
       </c>
       <c r="K31" t="n">
-        <v>-66.06</v>
+        <v>-71.90000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>76.8</v>
+        <v>83.59</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-148.61</v>
+        <v>-161.65</v>
       </c>
       <c r="K32" t="n">
-        <v>-36.98</v>
+        <v>-40.22</v>
       </c>
       <c r="L32" t="n">
-        <v>153.14</v>
+        <v>166.58</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>87.7</v>
+        <v>99.8</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.88</v>
+        <v>-1</v>
       </c>
       <c r="L33" t="n">
-        <v>87.70999999999999</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.210000000000001</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-79.89</v>
+        <v>-88.08</v>
       </c>
       <c r="L34" t="n">
-        <v>80.31</v>
+        <v>88.55</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-185.87</v>
+        <v>-211.3</v>
       </c>
       <c r="K35" t="n">
-        <v>112.53</v>
+        <v>127.93</v>
       </c>
       <c r="L35" t="n">
-        <v>217.28</v>
+        <v>247.02</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-46.3</v>
+        <v>-52.65</v>
       </c>
       <c r="K36" t="n">
-        <v>97.20999999999999</v>
+        <v>110.54</v>
       </c>
       <c r="L36" t="n">
-        <v>107.68</v>
+        <v>122.44</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>87.55</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-114.93</v>
+        <v>-129.04</v>
       </c>
       <c r="L37" t="n">
-        <v>144.48</v>
+        <v>162.21</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-100.29</v>
+        <v>-107.72</v>
       </c>
       <c r="K38" t="n">
-        <v>-57.41</v>
+        <v>-61.67</v>
       </c>
       <c r="L38" t="n">
-        <v>115.56</v>
+        <v>124.12</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>-92.86</v>
+        <v>-101.31</v>
       </c>
       <c r="K39" t="n">
-        <v>-156.92</v>
+        <v>-171.19</v>
       </c>
       <c r="L39" t="n">
-        <v>182.34</v>
+        <v>198.92</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-110.97</v>
+        <v>-124.6</v>
       </c>
       <c r="K40" t="n">
-        <v>-174.69</v>
+        <v>-196.14</v>
       </c>
       <c r="L40" t="n">
-        <v>206.96</v>
+        <v>232.37</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>111.32</v>
+        <v>123.13</v>
       </c>
       <c r="K41" t="n">
-        <v>-299.65</v>
+        <v>-331.43</v>
       </c>
       <c r="L41" t="n">
-        <v>319.66</v>
+        <v>353.56</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-83.97</v>
+        <v>-96.02</v>
       </c>
       <c r="K42" t="n">
-        <v>211.11</v>
+        <v>241.41</v>
       </c>
       <c r="L42" t="n">
-        <v>227.2</v>
+        <v>259.81</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>-31.02</v>
+        <v>-34.93</v>
       </c>
       <c r="K43" t="n">
-        <v>273.98</v>
+        <v>308.47</v>
       </c>
       <c r="L43" t="n">
-        <v>275.73</v>
+        <v>310.44</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-65.77</v>
+        <v>-74.84</v>
       </c>
       <c r="K44" t="n">
-        <v>-49.6</v>
+        <v>-56.44</v>
       </c>
       <c r="L44" t="n">
-        <v>82.37</v>
+        <v>93.73999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>45.52</v>
+        <v>50.17</v>
       </c>
       <c r="K45" t="n">
-        <v>82.65000000000001</v>
+        <v>91.11</v>
       </c>
       <c r="L45" t="n">
-        <v>94.36</v>
+        <v>104.01</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-55.13</v>
+        <v>-62.09</v>
       </c>
       <c r="K46" t="n">
-        <v>-101.39</v>
+        <v>-114.18</v>
       </c>
       <c r="L46" t="n">
-        <v>115.41</v>
+        <v>129.97</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>81.09999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="K47" t="n">
-        <v>-34.7</v>
+        <v>-37.67</v>
       </c>
       <c r="L47" t="n">
-        <v>88.20999999999999</v>
+        <v>95.76000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>88.88</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-70.63</v>
+        <v>-76.48</v>
       </c>
       <c r="L48" t="n">
-        <v>113.52</v>
+        <v>122.93</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-71.70999999999999</v>
+        <v>-81.16</v>
       </c>
       <c r="K49" t="n">
-        <v>-88.56999999999999</v>
+        <v>-100.25</v>
       </c>
       <c r="L49" t="n">
-        <v>113.96</v>
+        <v>128.98</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-67.08</v>
+        <v>-73.09</v>
       </c>
       <c r="K50" t="n">
-        <v>-203.08</v>
+        <v>-221.3</v>
       </c>
       <c r="L50" t="n">
-        <v>213.87</v>
+        <v>233.06</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>23.29</v>
+        <v>26.5</v>
       </c>
       <c r="K51" t="n">
-        <v>-103.38</v>
+        <v>-117.64</v>
       </c>
       <c r="L51" t="n">
-        <v>105.97</v>
+        <v>120.59</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-39.99</v>
+        <v>-42.94</v>
       </c>
       <c r="K52" t="n">
-        <v>168.58</v>
+        <v>181.01</v>
       </c>
       <c r="L52" t="n">
-        <v>173.26</v>
+        <v>186.04</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>236.35</v>
+        <v>263.86</v>
       </c>
       <c r="K53" t="n">
-        <v>163.9</v>
+        <v>182.98</v>
       </c>
       <c r="L53" t="n">
-        <v>287.62</v>
+        <v>321.1</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>69.73999999999999</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-156.16</v>
+        <v>-177.91</v>
       </c>
       <c r="L54" t="n">
-        <v>171.03</v>
+        <v>194.85</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>167.11</v>
+        <v>183.24</v>
       </c>
       <c r="K55" t="n">
-        <v>-53.28</v>
+        <v>-58.43</v>
       </c>
       <c r="L55" t="n">
-        <v>175.4</v>
+        <v>192.33</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-339.55</v>
+        <v>-372.6</v>
       </c>
       <c r="K56" t="n">
-        <v>74.93000000000001</v>
+        <v>82.22</v>
       </c>
       <c r="L56" t="n">
-        <v>347.72</v>
+        <v>381.57</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>142.79</v>
+        <v>163.32</v>
       </c>
       <c r="K57" t="n">
-        <v>236.58</v>
+        <v>270.59</v>
       </c>
       <c r="L57" t="n">
-        <v>276.33</v>
+        <v>316.06</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>184.46</v>
+        <v>211.38</v>
       </c>
       <c r="K58" t="n">
-        <v>268.15</v>
+        <v>307.28</v>
       </c>
       <c r="L58" t="n">
-        <v>325.47</v>
+        <v>372.97</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>9.32</v>
+        <v>10.57</v>
       </c>
       <c r="K59" t="n">
-        <v>96.23999999999999</v>
+        <v>109.15</v>
       </c>
       <c r="L59" t="n">
-        <v>96.69</v>
+        <v>109.66</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>72.90000000000001</v>
+        <v>82.62</v>
       </c>
       <c r="K60" t="n">
-        <v>86.01000000000001</v>
+        <v>97.48</v>
       </c>
       <c r="L60" t="n">
-        <v>112.75</v>
+        <v>127.78</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-68.01000000000001</v>
+        <v>-73.86</v>
       </c>
       <c r="K61" t="n">
-        <v>26.52</v>
+        <v>28.8</v>
       </c>
       <c r="L61" t="n">
-        <v>72.98999999999999</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-89.09999999999999</v>
+        <v>-101.37</v>
       </c>
       <c r="K62" t="n">
-        <v>-61.78</v>
+        <v>-70.28</v>
       </c>
       <c r="L62" t="n">
-        <v>108.42</v>
+        <v>123.35</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-80.04000000000001</v>
+        <v>-88.40000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-16.82</v>
+        <v>-18.57</v>
       </c>
       <c r="L63" t="n">
-        <v>81.79000000000001</v>
+        <v>90.33</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>93.16</v>
+        <v>105.46</v>
       </c>
       <c r="K64" t="n">
-        <v>-98.55</v>
+        <v>-111.56</v>
       </c>
       <c r="L64" t="n">
-        <v>135.61</v>
+        <v>153.51</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-14.94</v>
+        <v>-16.51</v>
       </c>
       <c r="K65" t="n">
-        <v>197.58</v>
+        <v>218.41</v>
       </c>
       <c r="L65" t="n">
-        <v>198.14</v>
+        <v>219.03</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>-140.45</v>
+        <v>-150.82</v>
       </c>
       <c r="K66" t="n">
-        <v>58.91</v>
+        <v>63.26</v>
       </c>
       <c r="L66" t="n">
-        <v>152.3</v>
+        <v>163.55</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>28.1</v>
+        <v>31.9</v>
       </c>
       <c r="K67" t="n">
-        <v>-203.92</v>
+        <v>-231.5</v>
       </c>
       <c r="L67" t="n">
-        <v>205.85</v>
+        <v>233.69</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>127.52</v>
+        <v>139.25</v>
       </c>
       <c r="K68" t="n">
-        <v>132.2</v>
+        <v>144.36</v>
       </c>
       <c r="L68" t="n">
-        <v>183.68</v>
+        <v>200.57</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-120.57</v>
+        <v>-137.34</v>
       </c>
       <c r="K69" t="n">
-        <v>62.69</v>
+        <v>71.41</v>
       </c>
       <c r="L69" t="n">
-        <v>135.89</v>
+        <v>154.8</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>41.46</v>
+        <v>44.58</v>
       </c>
       <c r="K70" t="n">
-        <v>-211.17</v>
+        <v>-227.1</v>
       </c>
       <c r="L70" t="n">
-        <v>215.2</v>
+        <v>231.44</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>283.12</v>
+        <v>324.12</v>
       </c>
       <c r="K71" t="n">
-        <v>-294.24</v>
+        <v>-336.84</v>
       </c>
       <c r="L71" t="n">
-        <v>408.34</v>
+        <v>467.46</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-62.21</v>
+        <v>-70</v>
       </c>
       <c r="K72" t="n">
-        <v>314.3</v>
+        <v>353.68</v>
       </c>
       <c r="L72" t="n">
-        <v>320.4</v>
+        <v>360.55</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-315.69</v>
+        <v>-361.31</v>
       </c>
       <c r="K73" t="n">
-        <v>-242.51</v>
+        <v>-277.54</v>
       </c>
       <c r="L73" t="n">
-        <v>398.08</v>
+        <v>455.6</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>53.45</v>
+        <v>60.48</v>
       </c>
       <c r="K74" t="n">
-        <v>-14.23</v>
+        <v>-16.1</v>
       </c>
       <c r="L74" t="n">
-        <v>55.31</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>43.97</v>
+        <v>49.54</v>
       </c>
       <c r="K75" t="n">
-        <v>101.1</v>
+        <v>113.93</v>
       </c>
       <c r="L75" t="n">
-        <v>110.25</v>
+        <v>124.23</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-25.54</v>
+        <v>-28.96</v>
       </c>
       <c r="K76" t="n">
-        <v>107.66</v>
+        <v>122.06</v>
       </c>
       <c r="L76" t="n">
-        <v>110.65</v>
+        <v>125.45</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-25.76</v>
+        <v>-29.2</v>
       </c>
       <c r="K77" t="n">
-        <v>-135.8</v>
+        <v>-153.92</v>
       </c>
       <c r="L77" t="n">
-        <v>138.23</v>
+        <v>156.66</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-31.73</v>
+        <v>-36.02</v>
       </c>
       <c r="K78" t="n">
-        <v>85.11</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>90.84</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>109.9</v>
+        <v>124.37</v>
       </c>
       <c r="K79" t="n">
-        <v>-71.62</v>
+        <v>-81.04000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>131.18</v>
+        <v>148.44</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>145.64</v>
+        <v>165.33</v>
       </c>
       <c r="K80" t="n">
-        <v>-120.5</v>
+        <v>-136.8</v>
       </c>
       <c r="L80" t="n">
-        <v>189.03</v>
+        <v>214.59</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-28.83</v>
+        <v>-30.83</v>
       </c>
       <c r="K81" t="n">
-        <v>-154.1</v>
+        <v>-164.79</v>
       </c>
       <c r="L81" t="n">
-        <v>156.77</v>
+        <v>167.65</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>27.49</v>
+        <v>29.5</v>
       </c>
       <c r="K82" t="n">
-        <v>-99.14</v>
+        <v>-106.39</v>
       </c>
       <c r="L82" t="n">
-        <v>102.88</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-85.06</v>
+        <v>-92.89</v>
       </c>
       <c r="K83" t="n">
-        <v>-156.68</v>
+        <v>-171.11</v>
       </c>
       <c r="L83" t="n">
-        <v>178.28</v>
+        <v>194.7</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>196.27</v>
+        <v>225.19</v>
       </c>
       <c r="K84" t="n">
-        <v>-101.43</v>
+        <v>-116.38</v>
       </c>
       <c r="L84" t="n">
-        <v>220.93</v>
+        <v>253.49</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>146.85</v>
+        <v>161.48</v>
       </c>
       <c r="K85" t="n">
-        <v>162.36</v>
+        <v>178.54</v>
       </c>
       <c r="L85" t="n">
-        <v>218.92</v>
+        <v>240.74</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-242.29</v>
+        <v>-271.01</v>
       </c>
       <c r="K86" t="n">
-        <v>-325.65</v>
+        <v>-364.25</v>
       </c>
       <c r="L86" t="n">
-        <v>405.9</v>
+        <v>454</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-3.16</v>
+        <v>-3.4</v>
       </c>
       <c r="K87" t="n">
-        <v>-237.38</v>
+        <v>-255.55</v>
       </c>
       <c r="L87" t="n">
-        <v>237.4</v>
+        <v>255.58</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>121.7</v>
+        <v>135.73</v>
       </c>
       <c r="K88" t="n">
-        <v>212.11</v>
+        <v>236.56</v>
       </c>
       <c r="L88" t="n">
-        <v>244.54</v>
+        <v>272.74</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>8.69</v>
+        <v>11.44</v>
       </c>
       <c r="G14" t="n">
-        <v>205</v>
+        <v>221.2</v>
       </c>
       <c r="H14" t="n">
-        <v>35.2</v>
+        <v>12.8</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>46.06</v>
+        <v>18.4</v>
       </c>
       <c r="K14" t="n">
-        <v>52.57</v>
+        <v>-53.22</v>
       </c>
       <c r="L14" t="n">
-        <v>69.90000000000001</v>
+        <v>56.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:50:39</t>
+          <t>05:51:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.07</v>
+        <v>3.33</v>
       </c>
       <c r="F15" t="n">
-        <v>9.18</v>
+        <v>9.4</v>
       </c>
       <c r="G15" t="n">
-        <v>228.9</v>
+        <v>222.8</v>
       </c>
       <c r="H15" t="n">
-        <v>34.6</v>
+        <v>32.3</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>14.51</v>
+        <v>-4.63</v>
       </c>
       <c r="K15" t="n">
-        <v>63.51</v>
+        <v>-59.03</v>
       </c>
       <c r="L15" t="n">
-        <v>65.15000000000001</v>
+        <v>59.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:52:55</t>
+          <t>05:52:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.81</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>10.88</v>
+        <v>9.08</v>
       </c>
       <c r="G16" t="n">
-        <v>235.9</v>
+        <v>222.7</v>
       </c>
       <c r="H16" t="n">
-        <v>39.2</v>
+        <v>39</v>
       </c>
       <c r="I16" t="n">
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>111.87</v>
+        <v>-32.63</v>
       </c>
       <c r="K16" t="n">
-        <v>-15.46</v>
+        <v>-38.44</v>
       </c>
       <c r="L16" t="n">
-        <v>112.93</v>
+        <v>50.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:56:24</t>
+          <t>05:57:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.49</v>
+        <v>3.83</v>
       </c>
       <c r="F17" t="n">
-        <v>14.94</v>
+        <v>14.95</v>
       </c>
       <c r="G17" t="n">
-        <v>212.3</v>
+        <v>217.9</v>
       </c>
       <c r="H17" t="n">
-        <v>43.2</v>
+        <v>49.5</v>
       </c>
       <c r="I17" t="n">
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-132.7</v>
+        <v>-85.31</v>
       </c>
       <c r="K17" t="n">
-        <v>-55.89</v>
+        <v>0.47</v>
       </c>
       <c r="L17" t="n">
-        <v>143.99</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:58:39</t>
+          <t>05:59:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="F18" t="n">
-        <v>14.95</v>
+        <v>11.93</v>
       </c>
       <c r="G18" t="n">
-        <v>218.6</v>
+        <v>230.1</v>
       </c>
       <c r="H18" t="n">
-        <v>46.7</v>
+        <v>57.7</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>100.46</v>
+        <v>113.43</v>
       </c>
       <c r="K18" t="n">
-        <v>108.62</v>
+        <v>-5.27</v>
       </c>
       <c r="L18" t="n">
-        <v>147.95</v>
+        <v>113.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:00:18</t>
+          <t>06:01:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="F19" t="n">
-        <v>12.68</v>
+        <v>10.51</v>
       </c>
       <c r="G19" t="n">
-        <v>219.3</v>
+        <v>221.6</v>
       </c>
       <c r="H19" t="n">
-        <v>33.6</v>
+        <v>25</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>57.65</v>
+        <v>-51.48</v>
       </c>
       <c r="K19" t="n">
-        <v>-53.53</v>
+        <v>46.34</v>
       </c>
       <c r="L19" t="n">
-        <v>78.67</v>
+        <v>69.26000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:06:20</t>
+          <t>06:07:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="F20" t="n">
-        <v>10.37</v>
+        <v>7.86</v>
       </c>
       <c r="G20" t="n">
-        <v>217.8</v>
+        <v>238.6</v>
       </c>
       <c r="H20" t="n">
-        <v>35.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-120.85</v>
+        <v>-57.86</v>
       </c>
       <c r="K20" t="n">
-        <v>-127.69</v>
+        <v>6.69</v>
       </c>
       <c r="L20" t="n">
-        <v>175.81</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:08:59</t>
+          <t>06:08:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.98</v>
+        <v>3.03</v>
       </c>
       <c r="F21" t="n">
-        <v>13.8</v>
+        <v>12.58</v>
       </c>
       <c r="G21" t="n">
-        <v>226.1</v>
+        <v>220.1</v>
       </c>
       <c r="H21" t="n">
-        <v>39.8</v>
+        <v>67</v>
       </c>
       <c r="I21" t="n">
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>171.8</v>
+        <v>-62.96</v>
       </c>
       <c r="K21" t="n">
-        <v>94.56999999999999</v>
+        <v>-7.62</v>
       </c>
       <c r="L21" t="n">
-        <v>196.11</v>
+        <v>63.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:11:00</t>
+          <t>06:10:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="F22" t="n">
-        <v>13.01</v>
+        <v>11.77</v>
       </c>
       <c r="G22" t="n">
-        <v>230.9</v>
+        <v>209.5</v>
       </c>
       <c r="H22" t="n">
-        <v>31.2</v>
+        <v>23.4</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-83.84999999999999</v>
+        <v>96.67</v>
       </c>
       <c r="K22" t="n">
-        <v>-189.28</v>
+        <v>-69.26000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>207.02</v>
+        <v>118.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:15:46</t>
+          <t>06:15:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.56</v>
+        <v>4.33</v>
       </c>
       <c r="F23" t="n">
-        <v>14.92</v>
+        <v>14.95</v>
       </c>
       <c r="G23" t="n">
-        <v>206.4</v>
+        <v>213.3</v>
       </c>
       <c r="H23" t="n">
-        <v>36.4</v>
+        <v>61.5</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-186.36</v>
+        <v>227.97</v>
       </c>
       <c r="K23" t="n">
-        <v>-260.26</v>
+        <v>-28.46</v>
       </c>
       <c r="L23" t="n">
-        <v>320.1</v>
+        <v>229.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:18:03</t>
+          <t>06:16:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.73</v>
+        <v>3.01</v>
       </c>
       <c r="F24" t="n">
-        <v>11.86</v>
+        <v>11.2</v>
       </c>
       <c r="G24" t="n">
-        <v>220.9</v>
+        <v>210.6</v>
       </c>
       <c r="H24" t="n">
-        <v>34.7</v>
+        <v>36.1</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>-106.35</v>
+        <v>-157.78</v>
       </c>
       <c r="K24" t="n">
-        <v>166.35</v>
+        <v>-14.18</v>
       </c>
       <c r="L24" t="n">
-        <v>197.44</v>
+        <v>158.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:19:46</t>
+          <t>06:19:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="F25" t="n">
-        <v>6.95</v>
+        <v>11.24</v>
       </c>
       <c r="G25" t="n">
-        <v>228.1</v>
+        <v>213</v>
       </c>
       <c r="H25" t="n">
-        <v>39.8</v>
+        <v>61.7</v>
       </c>
       <c r="I25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>212.43</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-190.33</v>
+        <v>-247.16</v>
       </c>
       <c r="L25" t="n">
-        <v>285.22</v>
+        <v>257.21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:24:24</t>
+          <t>06:22:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.33</v>
+        <v>4.26</v>
       </c>
       <c r="F26" t="n">
-        <v>11.53</v>
+        <v>14.75</v>
       </c>
       <c r="G26" t="n">
-        <v>211.2</v>
+        <v>209.5</v>
       </c>
       <c r="H26" t="n">
-        <v>36.2</v>
+        <v>60.7</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-26.89</v>
+        <v>166.52</v>
       </c>
       <c r="K26" t="n">
-        <v>-249.68</v>
+        <v>-203.02</v>
       </c>
       <c r="L26" t="n">
-        <v>251.12</v>
+        <v>262.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:26:24</t>
+          <t>06:24:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="F27" t="n">
-        <v>11.93</v>
+        <v>14.25</v>
       </c>
       <c r="G27" t="n">
-        <v>212.3</v>
+        <v>220.8</v>
       </c>
       <c r="H27" t="n">
-        <v>35.2</v>
+        <v>34.5</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-32.28</v>
+        <v>194.93</v>
       </c>
       <c r="K27" t="n">
-        <v>-392.63</v>
+        <v>120.49</v>
       </c>
       <c r="L27" t="n">
-        <v>393.96</v>
+        <v>229.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:27:47</t>
+          <t>06:25:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.02</v>
+        <v>2.71</v>
       </c>
       <c r="F28" t="n">
-        <v>10.69</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H28" t="n">
-        <v>45</v>
+        <v>46.2</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>312.05</v>
+        <v>7.61</v>
       </c>
       <c r="K28" t="n">
-        <v>248.87</v>
+        <v>-181.11</v>
       </c>
       <c r="L28" t="n">
-        <v>399.14</v>
+        <v>181.27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:39:27</t>
+          <t>06:38:53</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.3</v>
+        <v>4.74</v>
       </c>
       <c r="F29" t="n">
-        <v>9.699999999999999</v>
+        <v>14.95</v>
       </c>
       <c r="G29" t="n">
-        <v>226.5</v>
+        <v>233.1</v>
       </c>
       <c r="H29" t="n">
-        <v>39.8</v>
+        <v>65.5</v>
       </c>
       <c r="I29" t="n">
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>0.19</v>
+        <v>-98.17</v>
       </c>
       <c r="K29" t="n">
-        <v>90.77</v>
+        <v>-45.79</v>
       </c>
       <c r="L29" t="n">
-        <v>90.77</v>
+        <v>108.33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:40:09</t>
+          <t>06:40:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="F30" t="n">
-        <v>8.75</v>
+        <v>12.88</v>
       </c>
       <c r="G30" t="n">
-        <v>215.1</v>
+        <v>213.9</v>
       </c>
       <c r="H30" t="n">
-        <v>35.9</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-44.95</v>
+        <v>33.5</v>
       </c>
       <c r="K30" t="n">
-        <v>-55.08</v>
+        <v>30.18</v>
       </c>
       <c r="L30" t="n">
-        <v>71.09</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:41:45</t>
+          <t>06:42:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.74</v>
+        <v>3.33</v>
       </c>
       <c r="F31" t="n">
-        <v>12.39</v>
+        <v>9.99</v>
       </c>
       <c r="G31" t="n">
-        <v>225.5</v>
+        <v>223.9</v>
       </c>
       <c r="H31" t="n">
-        <v>41.4</v>
+        <v>41</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-42.63</v>
+        <v>-22.64</v>
       </c>
       <c r="K31" t="n">
-        <v>-71.90000000000001</v>
+        <v>-38.29</v>
       </c>
       <c r="L31" t="n">
-        <v>83.59</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:47:50</t>
+          <t>06:48:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="F32" t="n">
-        <v>12.5</v>
+        <v>11.06</v>
       </c>
       <c r="G32" t="n">
-        <v>240.7</v>
+        <v>219.5</v>
       </c>
       <c r="H32" t="n">
-        <v>37.9</v>
+        <v>18.8</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-161.65</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-40.22</v>
+        <v>-31.57</v>
       </c>
       <c r="L32" t="n">
-        <v>166.58</v>
+        <v>75.23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:49:53</t>
+          <t>06:50:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="F33" t="n">
-        <v>7.12</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>227.4</v>
+        <v>210.9</v>
       </c>
       <c r="H33" t="n">
-        <v>34.2</v>
+        <v>38.1</v>
       </c>
       <c r="I33" t="n">
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>99.8</v>
+        <v>11.18</v>
       </c>
       <c r="K33" t="n">
-        <v>-1</v>
+        <v>-73.59</v>
       </c>
       <c r="L33" t="n">
-        <v>99.8</v>
+        <v>74.43000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:51:26</t>
+          <t>06:52:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.11</v>
+        <v>5.22</v>
       </c>
       <c r="F34" t="n">
         <v>14.95</v>
       </c>
       <c r="G34" t="n">
-        <v>213.5</v>
+        <v>209.8</v>
       </c>
       <c r="H34" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-9.050000000000001</v>
+        <v>-69.22</v>
       </c>
       <c r="K34" t="n">
-        <v>-88.08</v>
+        <v>116.7</v>
       </c>
       <c r="L34" t="n">
-        <v>88.55</v>
+        <v>135.68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:56:00</t>
+          <t>06:57:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="F35" t="n">
-        <v>8.06</v>
+        <v>10.93</v>
       </c>
       <c r="G35" t="n">
-        <v>221.7</v>
+        <v>232.5</v>
       </c>
       <c r="H35" t="n">
-        <v>41.2</v>
+        <v>46.7</v>
       </c>
       <c r="I35" t="n">
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-211.3</v>
+        <v>42.51</v>
       </c>
       <c r="K35" t="n">
-        <v>127.93</v>
+        <v>-95.19</v>
       </c>
       <c r="L35" t="n">
-        <v>247.02</v>
+        <v>104.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:57:22</t>
+          <t>07:00:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.67</v>
+        <v>4.84</v>
       </c>
       <c r="F36" t="n">
-        <v>13.55</v>
+        <v>14.41</v>
       </c>
       <c r="G36" t="n">
-        <v>199.7</v>
+        <v>217.8</v>
       </c>
       <c r="H36" t="n">
-        <v>35.3</v>
+        <v>57.5</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-52.65</v>
+        <v>-28.25</v>
       </c>
       <c r="K36" t="n">
-        <v>110.54</v>
+        <v>-177.9</v>
       </c>
       <c r="L36" t="n">
-        <v>122.44</v>
+        <v>180.13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:59:30</t>
+          <t>07:02:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.29</v>
+        <v>3.01</v>
       </c>
       <c r="F37" t="n">
-        <v>11.09</v>
+        <v>8.43</v>
       </c>
       <c r="G37" t="n">
-        <v>223.2</v>
+        <v>214.7</v>
       </c>
       <c r="H37" t="n">
-        <v>37.3</v>
+        <v>30.4</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>98.29000000000001</v>
+        <v>-67.17</v>
       </c>
       <c r="K37" t="n">
-        <v>-129.04</v>
+        <v>-80.20999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>162.21</v>
+        <v>104.62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:04:27</t>
+          <t>07:05:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.49</v>
+        <v>2.97</v>
       </c>
       <c r="F38" t="n">
-        <v>7.69</v>
+        <v>9.82</v>
       </c>
       <c r="G38" t="n">
-        <v>207.6</v>
+        <v>229.4</v>
       </c>
       <c r="H38" t="n">
-        <v>33.9</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-107.72</v>
+        <v>22.14</v>
       </c>
       <c r="K38" t="n">
-        <v>-61.67</v>
+        <v>118.79</v>
       </c>
       <c r="L38" t="n">
-        <v>124.12</v>
+        <v>120.84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:05:54</t>
+          <t>07:07:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.82</v>
+        <v>3.22</v>
       </c>
       <c r="F39" t="n">
-        <v>11.5</v>
+        <v>11.19</v>
       </c>
       <c r="G39" t="n">
-        <v>209</v>
+        <v>218.7</v>
       </c>
       <c r="H39" t="n">
-        <v>38.5</v>
+        <v>35.9</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-101.31</v>
+        <v>171.09</v>
       </c>
       <c r="K39" t="n">
-        <v>-171.19</v>
+        <v>-59.61</v>
       </c>
       <c r="L39" t="n">
-        <v>198.92</v>
+        <v>181.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:06:35</t>
+          <t>07:09:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.17</v>
+        <v>4.21</v>
       </c>
       <c r="F40" t="n">
-        <v>14.34</v>
+        <v>14.95</v>
       </c>
       <c r="G40" t="n">
-        <v>226</v>
+        <v>238.6</v>
       </c>
       <c r="H40" t="n">
-        <v>37.1</v>
+        <v>19.6</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-124.6</v>
+        <v>-15.64</v>
       </c>
       <c r="K40" t="n">
-        <v>-196.14</v>
+        <v>261.09</v>
       </c>
       <c r="L40" t="n">
-        <v>232.37</v>
+        <v>261.56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:12:06</t>
+          <t>07:14:01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.36</v>
+        <v>3.95</v>
       </c>
       <c r="F41" t="n">
-        <v>12.76</v>
+        <v>12.65</v>
       </c>
       <c r="G41" t="n">
-        <v>197</v>
+        <v>233.9</v>
       </c>
       <c r="H41" t="n">
-        <v>42.8</v>
+        <v>17.7</v>
       </c>
       <c r="I41" t="n">
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>123.13</v>
+        <v>-163</v>
       </c>
       <c r="K41" t="n">
-        <v>-331.43</v>
+        <v>-260.78</v>
       </c>
       <c r="L41" t="n">
-        <v>353.56</v>
+        <v>307.53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:12:57</t>
+          <t>07:15:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="F42" t="n">
-        <v>10.27</v>
+        <v>10.86</v>
       </c>
       <c r="G42" t="n">
-        <v>222.1</v>
+        <v>216.7</v>
       </c>
       <c r="H42" t="n">
-        <v>41.9</v>
+        <v>48.2</v>
       </c>
       <c r="I42" t="n">
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-96.02</v>
+        <v>-186.08</v>
       </c>
       <c r="K42" t="n">
-        <v>241.41</v>
+        <v>53.53</v>
       </c>
       <c r="L42" t="n">
-        <v>259.81</v>
+        <v>193.62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:14:34</t>
+          <t>07:15:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.77</v>
+        <v>4.56</v>
       </c>
       <c r="F43" t="n">
         <v>14.95</v>
       </c>
       <c r="G43" t="n">
-        <v>208</v>
+        <v>213.4</v>
       </c>
       <c r="H43" t="n">
-        <v>46.1</v>
+        <v>6.9</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-34.93</v>
+        <v>-34.16</v>
       </c>
       <c r="K43" t="n">
-        <v>308.47</v>
+        <v>-284.65</v>
       </c>
       <c r="L43" t="n">
-        <v>310.44</v>
+        <v>286.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:25:25</t>
+          <t>07:24:54</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.78</v>
+        <v>4.35</v>
       </c>
       <c r="F44" t="n">
-        <v>8.859999999999999</v>
+        <v>13.91</v>
       </c>
       <c r="G44" t="n">
-        <v>223.1</v>
+        <v>214.3</v>
       </c>
       <c r="H44" t="n">
-        <v>41.5</v>
+        <v>65</v>
       </c>
       <c r="I44" t="n">
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-74.84</v>
+        <v>34.67</v>
       </c>
       <c r="K44" t="n">
-        <v>-56.44</v>
+        <v>62.07</v>
       </c>
       <c r="L44" t="n">
-        <v>93.73999999999999</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:27:18</t>
+          <t>07:26:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.16</v>
+        <v>3.64</v>
       </c>
       <c r="F45" t="n">
-        <v>12.57</v>
+        <v>13.16</v>
       </c>
       <c r="G45" t="n">
-        <v>236.1</v>
+        <v>210.4</v>
       </c>
       <c r="H45" t="n">
-        <v>34.3</v>
+        <v>17.7</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>50.17</v>
+        <v>36.5</v>
       </c>
       <c r="K45" t="n">
-        <v>91.11</v>
+        <v>-45.78</v>
       </c>
       <c r="L45" t="n">
-        <v>104.01</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:30:09</t>
+          <t>07:27:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.54</v>
+        <v>3.33</v>
       </c>
       <c r="F46" t="n">
-        <v>14.95</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>213.7</v>
+        <v>221.1</v>
       </c>
       <c r="H46" t="n">
-        <v>38.6</v>
+        <v>26.1</v>
       </c>
       <c r="I46" t="n">
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-62.09</v>
+        <v>39.22</v>
       </c>
       <c r="K46" t="n">
-        <v>-114.18</v>
+        <v>-15.96</v>
       </c>
       <c r="L46" t="n">
-        <v>129.97</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:34:10</t>
+          <t>07:32:13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="F47" t="n">
         <v>14.95</v>
       </c>
       <c r="G47" t="n">
-        <v>219.4</v>
+        <v>213.8</v>
       </c>
       <c r="H47" t="n">
-        <v>33</v>
+        <v>56.4</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>88.03</v>
+        <v>38.48</v>
       </c>
       <c r="K47" t="n">
-        <v>-37.67</v>
+        <v>36.83</v>
       </c>
       <c r="L47" t="n">
-        <v>95.76000000000001</v>
+        <v>53.26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:35:37</t>
+          <t>07:33:31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.88</v>
+        <v>4.18</v>
       </c>
       <c r="F48" t="n">
-        <v>12.78</v>
+        <v>12.7</v>
       </c>
       <c r="G48" t="n">
-        <v>232.9</v>
+        <v>217</v>
       </c>
       <c r="H48" t="n">
-        <v>40.1</v>
+        <v>60.1</v>
       </c>
       <c r="I48" t="n">
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>96.23999999999999</v>
+        <v>72.92</v>
       </c>
       <c r="K48" t="n">
-        <v>-76.48</v>
+        <v>34.05</v>
       </c>
       <c r="L48" t="n">
-        <v>122.93</v>
+        <v>80.48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:37:57</t>
+          <t>07:35:04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.4</v>
+        <v>3.23</v>
       </c>
       <c r="F49" t="n">
-        <v>13.22</v>
+        <v>13.48</v>
       </c>
       <c r="G49" t="n">
-        <v>234.6</v>
+        <v>206.7</v>
       </c>
       <c r="H49" t="n">
-        <v>39.3</v>
+        <v>63.3</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-81.16</v>
+        <v>-50</v>
       </c>
       <c r="K49" t="n">
-        <v>-100.25</v>
+        <v>-17.2</v>
       </c>
       <c r="L49" t="n">
-        <v>128.98</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:41:56</t>
+          <t>07:40:03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.89</v>
+        <v>4.92</v>
       </c>
       <c r="F50" t="n">
-        <v>11.6</v>
+        <v>14.95</v>
       </c>
       <c r="G50" t="n">
-        <v>216.3</v>
+        <v>215</v>
       </c>
       <c r="H50" t="n">
-        <v>37.5</v>
+        <v>46.9</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-73.09</v>
+        <v>21.84</v>
       </c>
       <c r="K50" t="n">
-        <v>-221.3</v>
+        <v>-188.57</v>
       </c>
       <c r="L50" t="n">
-        <v>233.06</v>
+        <v>189.83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:44:23</t>
+          <t>07:42:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.21</v>
+        <v>4.3</v>
       </c>
       <c r="F51" t="n">
-        <v>9.6</v>
+        <v>14.24</v>
       </c>
       <c r="G51" t="n">
-        <v>226.3</v>
+        <v>202.5</v>
       </c>
       <c r="H51" t="n">
-        <v>46.3</v>
+        <v>59.8</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>26.5</v>
+        <v>12.96</v>
       </c>
       <c r="K51" t="n">
-        <v>-117.64</v>
+        <v>-34.26</v>
       </c>
       <c r="L51" t="n">
-        <v>120.59</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:45:56</t>
+          <t>07:44:16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="F52" t="n">
-        <v>13.13</v>
+        <v>11.46</v>
       </c>
       <c r="G52" t="n">
-        <v>221.5</v>
+        <v>208.6</v>
       </c>
       <c r="H52" t="n">
-        <v>30.6</v>
+        <v>53.6</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-42.94</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>181.01</v>
+        <v>-99.22</v>
       </c>
       <c r="L52" t="n">
-        <v>186.04</v>
+        <v>138.78</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:51:00</t>
+          <t>07:49:12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.77</v>
+        <v>3.96</v>
       </c>
       <c r="F53" t="n">
-        <v>14.95</v>
+        <v>11.82</v>
       </c>
       <c r="G53" t="n">
-        <v>212.3</v>
+        <v>225.5</v>
       </c>
       <c r="H53" t="n">
-        <v>36.1</v>
+        <v>70.8</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>263.86</v>
+        <v>198.41</v>
       </c>
       <c r="K53" t="n">
-        <v>182.98</v>
+        <v>46.34</v>
       </c>
       <c r="L53" t="n">
-        <v>321.1</v>
+        <v>203.75</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:52:13</t>
+          <t>07:50:16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.27</v>
+        <v>4.84</v>
       </c>
       <c r="F54" t="n">
-        <v>12.33</v>
+        <v>14.95</v>
       </c>
       <c r="G54" t="n">
-        <v>228.2</v>
+        <v>224.8</v>
       </c>
       <c r="H54" t="n">
-        <v>31</v>
+        <v>15.6</v>
       </c>
       <c r="I54" t="n">
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>79.45999999999999</v>
+        <v>-76.02</v>
       </c>
       <c r="K54" t="n">
-        <v>-177.91</v>
+        <v>-188.85</v>
       </c>
       <c r="L54" t="n">
-        <v>194.85</v>
+        <v>203.57</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:53:53</t>
+          <t>07:51:55</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.51</v>
+        <v>3.45</v>
       </c>
       <c r="F55" t="n">
         <v>14.95</v>
       </c>
       <c r="G55" t="n">
-        <v>233.9</v>
+        <v>220.6</v>
       </c>
       <c r="H55" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>183.24</v>
+        <v>-140.25</v>
       </c>
       <c r="K55" t="n">
-        <v>-58.43</v>
+        <v>114.1</v>
       </c>
       <c r="L55" t="n">
-        <v>192.33</v>
+        <v>180.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:58:33</t>
+          <t>07:55:37</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.01</v>
+        <v>3.81</v>
       </c>
       <c r="F56" t="n">
-        <v>12.23</v>
+        <v>11.86</v>
       </c>
       <c r="G56" t="n">
-        <v>215.9</v>
+        <v>233</v>
       </c>
       <c r="H56" t="n">
-        <v>35.4</v>
+        <v>25.6</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-372.6</v>
+        <v>-102.18</v>
       </c>
       <c r="K56" t="n">
-        <v>82.22</v>
+        <v>-87.84</v>
       </c>
       <c r="L56" t="n">
-        <v>381.57</v>
+        <v>134.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:00:23</t>
+          <t>07:57:32</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.9</v>
+        <v>3.32</v>
       </c>
       <c r="F57" t="n">
-        <v>8.970000000000001</v>
+        <v>13.15</v>
       </c>
       <c r="G57" t="n">
-        <v>223.2</v>
+        <v>212.3</v>
       </c>
       <c r="H57" t="n">
-        <v>43.8</v>
+        <v>38.8</v>
       </c>
       <c r="I57" t="n">
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>163.32</v>
+        <v>-107.59</v>
       </c>
       <c r="K57" t="n">
-        <v>270.59</v>
+        <v>93.33</v>
       </c>
       <c r="L57" t="n">
-        <v>316.06</v>
+        <v>142.43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:00:53</t>
+          <t>07:58:44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.19</v>
+        <v>2.96</v>
       </c>
       <c r="F58" t="n">
-        <v>14.95</v>
+        <v>10.55</v>
       </c>
       <c r="G58" t="n">
-        <v>213.3</v>
+        <v>219.4</v>
       </c>
       <c r="H58" t="n">
-        <v>41.5</v>
+        <v>37.6</v>
       </c>
       <c r="I58" t="n">
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>211.38</v>
+        <v>-168.5</v>
       </c>
       <c r="K58" t="n">
-        <v>307.28</v>
+        <v>-51.56</v>
       </c>
       <c r="L58" t="n">
-        <v>372.97</v>
+        <v>176.21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:10:08</t>
+          <t>08:09:14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="F59" t="n">
-        <v>13.67</v>
+        <v>8.93</v>
       </c>
       <c r="G59" t="n">
-        <v>219.9</v>
+        <v>217.1</v>
       </c>
       <c r="H59" t="n">
-        <v>45.5</v>
+        <v>63.2</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>10.57</v>
+        <v>-64.62</v>
       </c>
       <c r="K59" t="n">
-        <v>109.15</v>
+        <v>-10.94</v>
       </c>
       <c r="L59" t="n">
-        <v>109.66</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:11:02</t>
+          <t>08:10:53</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.09</v>
+        <v>3.53</v>
       </c>
       <c r="F60" t="n">
-        <v>14.95</v>
+        <v>13.18</v>
       </c>
       <c r="G60" t="n">
-        <v>214.5</v>
+        <v>211.3</v>
       </c>
       <c r="H60" t="n">
-        <v>36.1</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>82.62</v>
+        <v>-29.35</v>
       </c>
       <c r="K60" t="n">
-        <v>97.48</v>
+        <v>43.26</v>
       </c>
       <c r="L60" t="n">
-        <v>127.78</v>
+        <v>52.28</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:12:56</t>
+          <t>08:12:38</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="F61" t="n">
-        <v>14.22</v>
+        <v>13.17</v>
       </c>
       <c r="G61" t="n">
-        <v>215.8</v>
+        <v>218.2</v>
       </c>
       <c r="H61" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-73.86</v>
+        <v>4.67</v>
       </c>
       <c r="K61" t="n">
-        <v>28.8</v>
+        <v>43.67</v>
       </c>
       <c r="L61" t="n">
-        <v>79.28</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:18:10</t>
+          <t>08:17:33</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.29</v>
+        <v>3.87</v>
       </c>
       <c r="F62" t="n">
-        <v>10.47</v>
+        <v>14.95</v>
       </c>
       <c r="G62" t="n">
-        <v>221.2</v>
+        <v>223.9</v>
       </c>
       <c r="H62" t="n">
-        <v>42</v>
+        <v>36.5</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-101.37</v>
+        <v>-83.72</v>
       </c>
       <c r="K62" t="n">
-        <v>-70.28</v>
+        <v>10.02</v>
       </c>
       <c r="L62" t="n">
-        <v>123.35</v>
+        <v>84.31999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:19:53</t>
+          <t>08:19:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.73</v>
+        <v>3.66</v>
       </c>
       <c r="F63" t="n">
-        <v>14.95</v>
+        <v>11.85</v>
       </c>
       <c r="G63" t="n">
-        <v>220.4</v>
+        <v>235.6</v>
       </c>
       <c r="H63" t="n">
-        <v>34.9</v>
+        <v>44.7</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-88.40000000000001</v>
+        <v>-70.84</v>
       </c>
       <c r="K63" t="n">
-        <v>-18.57</v>
+        <v>29.63</v>
       </c>
       <c r="L63" t="n">
-        <v>90.33</v>
+        <v>76.79000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:22:02</t>
+          <t>08:20:47</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.36</v>
+        <v>4.22</v>
       </c>
       <c r="F64" t="n">
-        <v>14.26</v>
+        <v>13.52</v>
       </c>
       <c r="G64" t="n">
-        <v>223.5</v>
+        <v>221.3</v>
       </c>
       <c r="H64" t="n">
-        <v>42.4</v>
+        <v>36.7</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>105.46</v>
+        <v>69.91</v>
       </c>
       <c r="K64" t="n">
-        <v>-111.56</v>
+        <v>42.9</v>
       </c>
       <c r="L64" t="n">
-        <v>153.51</v>
+        <v>82.03</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:28:05</t>
+          <t>08:26:19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.18</v>
+        <v>3.74</v>
       </c>
       <c r="F65" t="n">
-        <v>11.98</v>
+        <v>14.95</v>
       </c>
       <c r="G65" t="n">
-        <v>217.3</v>
+        <v>215.9</v>
       </c>
       <c r="H65" t="n">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-16.51</v>
+        <v>38.66</v>
       </c>
       <c r="K65" t="n">
-        <v>218.41</v>
+        <v>-107.99</v>
       </c>
       <c r="L65" t="n">
-        <v>219.03</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:29:42</t>
+          <t>08:28:36</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.35</v>
+        <v>3.79</v>
       </c>
       <c r="F66" t="n">
-        <v>11.5</v>
+        <v>14.95</v>
       </c>
       <c r="G66" t="n">
-        <v>203.6</v>
+        <v>219</v>
       </c>
       <c r="H66" t="n">
-        <v>36.7</v>
+        <v>59.2</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-150.82</v>
+        <v>-130.57</v>
       </c>
       <c r="K66" t="n">
-        <v>63.26</v>
+        <v>-57.22</v>
       </c>
       <c r="L66" t="n">
-        <v>163.55</v>
+        <v>142.56</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:30:51</t>
+          <t>08:29:22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.8</v>
+        <v>4.34</v>
       </c>
       <c r="F67" t="n">
-        <v>14.95</v>
+        <v>14.51</v>
       </c>
       <c r="G67" t="n">
-        <v>210.1</v>
+        <v>229.3</v>
       </c>
       <c r="H67" t="n">
-        <v>30.1</v>
+        <v>18.3</v>
       </c>
       <c r="I67" t="n">
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>31.9</v>
+        <v>60.18</v>
       </c>
       <c r="K67" t="n">
-        <v>-231.5</v>
+        <v>-105.45</v>
       </c>
       <c r="L67" t="n">
-        <v>233.69</v>
+        <v>121.41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:34:53</t>
+          <t>08:34:12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="F68" t="n">
-        <v>14.95</v>
+        <v>11.35</v>
       </c>
       <c r="G68" t="n">
-        <v>223.2</v>
+        <v>214.1</v>
       </c>
       <c r="H68" t="n">
-        <v>36.8</v>
+        <v>32</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>139.25</v>
+        <v>-130.4</v>
       </c>
       <c r="K68" t="n">
-        <v>144.36</v>
+        <v>84.72</v>
       </c>
       <c r="L68" t="n">
-        <v>200.57</v>
+        <v>155.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:36:33</t>
+          <t>08:36:10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.14</v>
+        <v>3.63</v>
       </c>
       <c r="F69" t="n">
-        <v>14.85</v>
+        <v>11.25</v>
       </c>
       <c r="G69" t="n">
-        <v>207.5</v>
+        <v>218.4</v>
       </c>
       <c r="H69" t="n">
-        <v>42.9</v>
+        <v>57.2</v>
       </c>
       <c r="I69" t="n">
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-137.34</v>
+        <v>-211.14</v>
       </c>
       <c r="K69" t="n">
-        <v>71.41</v>
+        <v>45.16</v>
       </c>
       <c r="L69" t="n">
-        <v>154.8</v>
+        <v>215.91</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:38:10</t>
+          <t>08:37:05</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.37</v>
+        <v>4.75</v>
       </c>
       <c r="F70" t="n">
-        <v>14.95</v>
+        <v>14.61</v>
       </c>
       <c r="G70" t="n">
-        <v>218.5</v>
+        <v>207.4</v>
       </c>
       <c r="H70" t="n">
-        <v>35.6</v>
+        <v>49</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>44.58</v>
+        <v>-187.88</v>
       </c>
       <c r="K70" t="n">
-        <v>-227.1</v>
+        <v>112.83</v>
       </c>
       <c r="L70" t="n">
-        <v>231.44</v>
+        <v>219.16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:42:37</t>
+          <t>08:42:04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.03</v>
+        <v>4.18</v>
       </c>
       <c r="F71" t="n">
-        <v>14.33</v>
+        <v>14.8</v>
       </c>
       <c r="G71" t="n">
-        <v>201.8</v>
+        <v>213.4</v>
       </c>
       <c r="H71" t="n">
-        <v>37.1</v>
+        <v>24.4</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>324.12</v>
+        <v>241.09</v>
       </c>
       <c r="K71" t="n">
-        <v>-336.84</v>
+        <v>-141.64</v>
       </c>
       <c r="L71" t="n">
-        <v>467.46</v>
+        <v>279.62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:44:22</t>
+          <t>08:43:19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.51</v>
+        <v>4.55</v>
       </c>
       <c r="F72" t="n">
-        <v>14.02</v>
+        <v>14.95</v>
       </c>
       <c r="G72" t="n">
-        <v>223.3</v>
+        <v>227.8</v>
       </c>
       <c r="H72" t="n">
-        <v>45.3</v>
+        <v>55.7</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>-70</v>
+        <v>-1.21</v>
       </c>
       <c r="K72" t="n">
-        <v>353.68</v>
+        <v>-242.49</v>
       </c>
       <c r="L72" t="n">
-        <v>360.55</v>
+        <v>242.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:46:12</t>
+          <t>08:44:38</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.99</v>
+        <v>4.91</v>
       </c>
       <c r="F73" t="n">
-        <v>14.34</v>
+        <v>14.95</v>
       </c>
       <c r="G73" t="n">
-        <v>226.5</v>
+        <v>222.8</v>
       </c>
       <c r="H73" t="n">
-        <v>42.5</v>
+        <v>65.7</v>
       </c>
       <c r="I73" t="n">
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-361.31</v>
+        <v>-234.64</v>
       </c>
       <c r="K73" t="n">
-        <v>-277.54</v>
+        <v>-48.63</v>
       </c>
       <c r="L73" t="n">
-        <v>455.6</v>
+        <v>239.63</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:54:07</t>
+          <t>08:54:52</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.45</v>
+        <v>4.67</v>
       </c>
       <c r="F74" t="n">
         <v>14.95</v>
       </c>
       <c r="G74" t="n">
-        <v>220.3</v>
+        <v>229.2</v>
       </c>
       <c r="H74" t="n">
-        <v>37.8</v>
+        <v>30.5</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>60.48</v>
+        <v>-71.37</v>
       </c>
       <c r="K74" t="n">
-        <v>-16.1</v>
+        <v>-69.26000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>62.58</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:55:40</t>
+          <t>08:56:54</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.4</v>
+        <v>4.55</v>
       </c>
       <c r="F75" t="n">
         <v>14.95</v>
       </c>
       <c r="G75" t="n">
-        <v>230.6</v>
+        <v>210.9</v>
       </c>
       <c r="H75" t="n">
-        <v>36.7</v>
+        <v>46.3</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>49.54</v>
+        <v>84.56</v>
       </c>
       <c r="K75" t="n">
-        <v>113.93</v>
+        <v>-24.81</v>
       </c>
       <c r="L75" t="n">
-        <v>124.23</v>
+        <v>88.12</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:57:15</t>
+          <t>08:58:20</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.01</v>
+        <v>3.93</v>
       </c>
       <c r="F76" t="n">
-        <v>13.14</v>
+        <v>11.3</v>
       </c>
       <c r="G76" t="n">
-        <v>222.3</v>
+        <v>223.2</v>
       </c>
       <c r="H76" t="n">
-        <v>38.4</v>
+        <v>54.8</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-28.96</v>
+        <v>45.82</v>
       </c>
       <c r="K76" t="n">
-        <v>122.06</v>
+        <v>-58.51</v>
       </c>
       <c r="L76" t="n">
-        <v>125.45</v>
+        <v>74.31999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:01:51</t>
+          <t>09:03:08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.08</v>
+        <v>3.41</v>
       </c>
       <c r="F77" t="n">
-        <v>14.95</v>
+        <v>10.37</v>
       </c>
       <c r="G77" t="n">
-        <v>235.1</v>
+        <v>226.9</v>
       </c>
       <c r="H77" t="n">
-        <v>44.1</v>
+        <v>54.7</v>
       </c>
       <c r="I77" t="n">
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-29.2</v>
+        <v>32.29</v>
       </c>
       <c r="K77" t="n">
-        <v>-153.92</v>
+        <v>59.44</v>
       </c>
       <c r="L77" t="n">
-        <v>156.66</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:03:41</t>
+          <t>09:05:09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.78</v>
+        <v>4.73</v>
       </c>
       <c r="F78" t="n">
-        <v>10.87</v>
+        <v>14.95</v>
       </c>
       <c r="G78" t="n">
-        <v>220.2</v>
+        <v>225.9</v>
       </c>
       <c r="H78" t="n">
-        <v>32.2</v>
+        <v>11</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-36.02</v>
+        <v>-171.59</v>
       </c>
       <c r="K78" t="n">
-        <v>96.59999999999999</v>
+        <v>-11.36</v>
       </c>
       <c r="L78" t="n">
-        <v>103.1</v>
+        <v>171.96</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:05:25</t>
+          <t>09:07:14</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.43</v>
+        <v>4.32</v>
       </c>
       <c r="F79" t="n">
         <v>14.95</v>
       </c>
       <c r="G79" t="n">
-        <v>216</v>
+        <v>227.4</v>
       </c>
       <c r="H79" t="n">
-        <v>41.4</v>
+        <v>39.2</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>124.37</v>
+        <v>-75.34999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-81.04000000000001</v>
+        <v>-97.43000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>148.44</v>
+        <v>123.17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:11:09</t>
+          <t>09:12:10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.79</v>
+        <v>4.64</v>
       </c>
       <c r="F80" t="n">
         <v>14.95</v>
       </c>
       <c r="G80" t="n">
-        <v>209.1</v>
+        <v>208.6</v>
       </c>
       <c r="H80" t="n">
-        <v>35.3</v>
+        <v>19.5</v>
       </c>
       <c r="I80" t="n">
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>165.33</v>
+        <v>-48.4</v>
       </c>
       <c r="K80" t="n">
-        <v>-136.8</v>
+        <v>-133.26</v>
       </c>
       <c r="L80" t="n">
-        <v>214.59</v>
+        <v>141.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:13:01</t>
+          <t>09:14:15</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.79</v>
+        <v>4.73</v>
       </c>
       <c r="F81" t="n">
         <v>14.95</v>
       </c>
       <c r="G81" t="n">
-        <v>220.9</v>
+        <v>208.4</v>
       </c>
       <c r="H81" t="n">
-        <v>39.3</v>
+        <v>68.5</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-30.83</v>
+        <v>145.29</v>
       </c>
       <c r="K81" t="n">
-        <v>-164.79</v>
+        <v>59.36</v>
       </c>
       <c r="L81" t="n">
-        <v>167.65</v>
+        <v>156.95</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:14:34</t>
+          <t>09:16:46</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.73</v>
+        <v>4.16</v>
       </c>
       <c r="F82" t="n">
-        <v>12.27</v>
+        <v>11.3</v>
       </c>
       <c r="G82" t="n">
-        <v>228.1</v>
+        <v>216.8</v>
       </c>
       <c r="H82" t="n">
-        <v>37.2</v>
+        <v>53.9</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>29.5</v>
+        <v>134.38</v>
       </c>
       <c r="K82" t="n">
-        <v>-106.39</v>
+        <v>61.36</v>
       </c>
       <c r="L82" t="n">
-        <v>110.4</v>
+        <v>147.73</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:19:21</t>
+          <t>09:21:25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.21</v>
+        <v>4.32</v>
       </c>
       <c r="F83" t="n">
-        <v>14.13</v>
+        <v>14.67</v>
       </c>
       <c r="G83" t="n">
-        <v>219</v>
+        <v>222.8</v>
       </c>
       <c r="H83" t="n">
-        <v>42.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I83" t="n">
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-92.89</v>
+        <v>-187.72</v>
       </c>
       <c r="K83" t="n">
-        <v>-171.11</v>
+        <v>-32.97</v>
       </c>
       <c r="L83" t="n">
-        <v>194.7</v>
+        <v>190.59</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:21:49</t>
+          <t>09:23:33</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.75</v>
+        <v>4.48</v>
       </c>
       <c r="F84" t="n">
-        <v>14.95</v>
+        <v>13.37</v>
       </c>
       <c r="G84" t="n">
-        <v>231.4</v>
+        <v>230.6</v>
       </c>
       <c r="H84" t="n">
-        <v>38.6</v>
+        <v>57.2</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>225.19</v>
+        <v>-35.66</v>
       </c>
       <c r="K84" t="n">
-        <v>-116.38</v>
+        <v>-252.57</v>
       </c>
       <c r="L84" t="n">
-        <v>253.49</v>
+        <v>255.07</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:22:59</t>
+          <t>09:25:32</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="F85" t="n">
         <v>14.95</v>
       </c>
       <c r="G85" t="n">
-        <v>220.3</v>
+        <v>227.6</v>
       </c>
       <c r="H85" t="n">
-        <v>34.7</v>
+        <v>40</v>
       </c>
       <c r="I85" t="n">
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>161.48</v>
+        <v>148.55</v>
       </c>
       <c r="K85" t="n">
-        <v>178.54</v>
+        <v>-128.17</v>
       </c>
       <c r="L85" t="n">
-        <v>240.74</v>
+        <v>196.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:27:13</t>
+          <t>09:30:14</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="F86" t="n">
-        <v>13.78</v>
+        <v>14.95</v>
       </c>
       <c r="G86" t="n">
-        <v>217.5</v>
+        <v>215.9</v>
       </c>
       <c r="H86" t="n">
-        <v>32.5</v>
+        <v>75.5</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-271.01</v>
+        <v>213.12</v>
       </c>
       <c r="K86" t="n">
-        <v>-364.25</v>
+        <v>-191.99</v>
       </c>
       <c r="L86" t="n">
-        <v>454</v>
+        <v>286.84</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:28:29</t>
+          <t>09:31:48</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.52</v>
+        <v>3.98</v>
       </c>
       <c r="F87" t="n">
-        <v>9.550000000000001</v>
+        <v>14.95</v>
       </c>
       <c r="G87" t="n">
-        <v>213.5</v>
+        <v>222.9</v>
       </c>
       <c r="H87" t="n">
-        <v>37.2</v>
+        <v>79.8</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-3.4</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-255.55</v>
+        <v>-213.71</v>
       </c>
       <c r="L87" t="n">
-        <v>255.58</v>
+        <v>230.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:30:06</t>
+          <t>09:33:39</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.24</v>
+        <v>4.81</v>
       </c>
       <c r="F88" t="n">
         <v>14.95</v>
       </c>
       <c r="G88" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H88" t="n">
-        <v>42.2</v>
+        <v>35.8</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>135.73</v>
+        <v>-255.96</v>
       </c>
       <c r="K88" t="n">
-        <v>236.56</v>
+        <v>-182.4</v>
       </c>
       <c r="L88" t="n">
-        <v>272.74</v>
+        <v>314.3</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>2.49</v>
       </c>
       <c r="F14" t="n">
-        <v>11.44</v>
+        <v>7.12</v>
       </c>
       <c r="G14" t="n">
-        <v>221.2</v>
+        <v>220.3</v>
       </c>
       <c r="H14" t="n">
-        <v>12.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>18.4</v>
+        <v>27.49</v>
       </c>
       <c r="K14" t="n">
-        <v>-53.22</v>
+        <v>26.39</v>
       </c>
       <c r="L14" t="n">
-        <v>56.32</v>
+        <v>38.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:51:12</t>
+          <t>05:50:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.33</v>
+        <v>4.1</v>
       </c>
       <c r="F15" t="n">
-        <v>9.4</v>
+        <v>10.8</v>
       </c>
       <c r="G15" t="n">
-        <v>222.8</v>
+        <v>217.2</v>
       </c>
       <c r="H15" t="n">
-        <v>32.3</v>
+        <v>30.5</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.63</v>
+        <v>6.55</v>
       </c>
       <c r="K15" t="n">
-        <v>-59.03</v>
+        <v>75.94</v>
       </c>
       <c r="L15" t="n">
-        <v>59.21</v>
+        <v>76.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:52:29</t>
+          <t>05:52:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="F16" t="n">
-        <v>9.08</v>
+        <v>13.82</v>
       </c>
       <c r="G16" t="n">
-        <v>222.7</v>
+        <v>216.9</v>
       </c>
       <c r="H16" t="n">
-        <v>39</v>
+        <v>42.4</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-32.63</v>
+        <v>-63.62</v>
       </c>
       <c r="K16" t="n">
-        <v>-38.44</v>
+        <v>41.65</v>
       </c>
       <c r="L16" t="n">
-        <v>50.42</v>
+        <v>76.04000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:57:34</t>
+          <t>05:56:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.83</v>
+        <v>3.32</v>
       </c>
       <c r="F17" t="n">
-        <v>14.95</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>217.9</v>
+        <v>220.4</v>
       </c>
       <c r="H17" t="n">
-        <v>49.5</v>
+        <v>73.8</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-85.31</v>
+        <v>59.55</v>
       </c>
       <c r="K17" t="n">
-        <v>0.47</v>
+        <v>45.41</v>
       </c>
       <c r="L17" t="n">
-        <v>85.31</v>
+        <v>74.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:59:34</t>
+          <t>05:58:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="F18" t="n">
-        <v>11.93</v>
+        <v>14.85</v>
       </c>
       <c r="G18" t="n">
-        <v>230.1</v>
+        <v>221.5</v>
       </c>
       <c r="H18" t="n">
-        <v>57.7</v>
+        <v>10.4</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" t="n">
-        <v>113.43</v>
+        <v>26.13</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.27</v>
+        <v>-101.55</v>
       </c>
       <c r="L18" t="n">
-        <v>113.56</v>
+        <v>104.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:01:43</t>
+          <t>05:59:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="F19" t="n">
-        <v>10.51</v>
+        <v>12.01</v>
       </c>
       <c r="G19" t="n">
-        <v>221.6</v>
+        <v>225.4</v>
       </c>
       <c r="H19" t="n">
-        <v>25</v>
+        <v>26.8</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-51.48</v>
+        <v>-56.12</v>
       </c>
       <c r="K19" t="n">
-        <v>46.34</v>
+        <v>70.48</v>
       </c>
       <c r="L19" t="n">
-        <v>69.26000000000001</v>
+        <v>90.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:07:10</t>
+          <t>06:05:28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.81</v>
+        <v>3.73</v>
       </c>
       <c r="F20" t="n">
-        <v>7.86</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>238.6</v>
+        <v>222.9</v>
       </c>
       <c r="H20" t="n">
-        <v>73.59999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>-57.86</v>
+        <v>129.07</v>
       </c>
       <c r="K20" t="n">
-        <v>6.69</v>
+        <v>-65.43000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>58.24</v>
+        <v>144.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:08:22</t>
+          <t>06:07:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.03</v>
+        <v>4.25</v>
       </c>
       <c r="F21" t="n">
-        <v>12.58</v>
+        <v>14.95</v>
       </c>
       <c r="G21" t="n">
-        <v>220.1</v>
+        <v>216.3</v>
       </c>
       <c r="H21" t="n">
-        <v>67</v>
+        <v>36.6</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-62.96</v>
+        <v>-120.04</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.62</v>
+        <v>-80.92</v>
       </c>
       <c r="L21" t="n">
-        <v>63.42</v>
+        <v>144.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:10:57</t>
+          <t>06:07:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.75</v>
+        <v>3.11</v>
       </c>
       <c r="F22" t="n">
-        <v>11.77</v>
+        <v>10.01</v>
       </c>
       <c r="G22" t="n">
-        <v>209.5</v>
+        <v>220.3</v>
       </c>
       <c r="H22" t="n">
-        <v>23.4</v>
+        <v>31.8</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>96.67</v>
+        <v>1.99</v>
       </c>
       <c r="K22" t="n">
-        <v>-69.26000000000001</v>
+        <v>119.16</v>
       </c>
       <c r="L22" t="n">
-        <v>118.92</v>
+        <v>119.18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:15:33</t>
+          <t>06:12:41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.33</v>
+        <v>3.82</v>
       </c>
       <c r="F23" t="n">
-        <v>14.95</v>
+        <v>10.98</v>
       </c>
       <c r="G23" t="n">
-        <v>213.3</v>
+        <v>210</v>
       </c>
       <c r="H23" t="n">
-        <v>61.5</v>
+        <v>62</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>227.97</v>
+        <v>38.38</v>
       </c>
       <c r="K23" t="n">
-        <v>-28.46</v>
+        <v>-238.92</v>
       </c>
       <c r="L23" t="n">
-        <v>229.74</v>
+        <v>241.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:16:25</t>
+          <t>06:14:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.01</v>
+        <v>3.72</v>
       </c>
       <c r="F24" t="n">
-        <v>11.2</v>
+        <v>10.88</v>
       </c>
       <c r="G24" t="n">
-        <v>210.6</v>
+        <v>204.6</v>
       </c>
       <c r="H24" t="n">
-        <v>36.1</v>
+        <v>24.2</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-157.78</v>
+        <v>-234.27</v>
       </c>
       <c r="K24" t="n">
-        <v>-14.18</v>
+        <v>-168.49</v>
       </c>
       <c r="L24" t="n">
-        <v>158.42</v>
+        <v>288.56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:19:02</t>
+          <t>06:15:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="F25" t="n">
-        <v>11.24</v>
+        <v>9.76</v>
       </c>
       <c r="G25" t="n">
-        <v>213</v>
+        <v>209.6</v>
       </c>
       <c r="H25" t="n">
-        <v>61.7</v>
+        <v>42.1</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>71.18000000000001</v>
+        <v>-32.31</v>
       </c>
       <c r="K25" t="n">
-        <v>-247.16</v>
+        <v>-218.04</v>
       </c>
       <c r="L25" t="n">
-        <v>257.21</v>
+        <v>220.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:22:31</t>
+          <t>06:20:42</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.26</v>
+        <v>3.7</v>
       </c>
       <c r="F26" t="n">
-        <v>14.75</v>
+        <v>10.37</v>
       </c>
       <c r="G26" t="n">
-        <v>209.5</v>
+        <v>224.5</v>
       </c>
       <c r="H26" t="n">
-        <v>60.7</v>
+        <v>22</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>166.52</v>
+        <v>-257.28</v>
       </c>
       <c r="K26" t="n">
-        <v>-203.02</v>
+        <v>-176</v>
       </c>
       <c r="L26" t="n">
-        <v>262.57</v>
+        <v>311.72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:24:10</t>
+          <t>06:21:59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.79</v>
+        <v>3.52</v>
       </c>
       <c r="F27" t="n">
-        <v>14.25</v>
+        <v>14.95</v>
       </c>
       <c r="G27" t="n">
-        <v>220.8</v>
+        <v>214.7</v>
       </c>
       <c r="H27" t="n">
-        <v>34.5</v>
+        <v>51.2</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>194.93</v>
+        <v>174.62</v>
       </c>
       <c r="K27" t="n">
-        <v>120.49</v>
+        <v>-209.07</v>
       </c>
       <c r="L27" t="n">
-        <v>229.17</v>
+        <v>272.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:25:52</t>
+          <t>06:23:32</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.71</v>
+        <v>3.83</v>
       </c>
       <c r="F28" t="n">
-        <v>8.619999999999999</v>
+        <v>10.66</v>
       </c>
       <c r="G28" t="n">
-        <v>222</v>
+        <v>224.6</v>
       </c>
       <c r="H28" t="n">
-        <v>46.2</v>
+        <v>67.7</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>7.61</v>
+        <v>-425.55</v>
       </c>
       <c r="K28" t="n">
-        <v>-181.11</v>
+        <v>-34.03</v>
       </c>
       <c r="L28" t="n">
-        <v>181.27</v>
+        <v>426.91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:38:53</t>
+          <t>06:33:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.74</v>
+        <v>3.55</v>
       </c>
       <c r="F29" t="n">
-        <v>14.95</v>
+        <v>13.36</v>
       </c>
       <c r="G29" t="n">
-        <v>233.1</v>
+        <v>210.5</v>
       </c>
       <c r="H29" t="n">
-        <v>65.5</v>
+        <v>45.5</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>-98.17</v>
+        <v>-71.25</v>
       </c>
       <c r="K29" t="n">
-        <v>-45.79</v>
+        <v>17.2</v>
       </c>
       <c r="L29" t="n">
-        <v>108.33</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:40:48</t>
+          <t>06:34:20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.17</v>
+        <v>4.68</v>
       </c>
       <c r="F30" t="n">
-        <v>12.88</v>
+        <v>14.45</v>
       </c>
       <c r="G30" t="n">
-        <v>213.9</v>
+        <v>217.2</v>
       </c>
       <c r="H30" t="n">
-        <v>79.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>33.5</v>
+        <v>-41.3</v>
       </c>
       <c r="K30" t="n">
-        <v>30.18</v>
+        <v>-98.08</v>
       </c>
       <c r="L30" t="n">
-        <v>45.09</v>
+        <v>106.43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:42:28</t>
+          <t>06:35:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="F31" t="n">
-        <v>9.99</v>
+        <v>9.07</v>
       </c>
       <c r="G31" t="n">
-        <v>223.9</v>
+        <v>237.7</v>
       </c>
       <c r="H31" t="n">
-        <v>41</v>
+        <v>59.9</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.64</v>
+        <v>-61.54</v>
       </c>
       <c r="K31" t="n">
-        <v>-38.29</v>
+        <v>-46.49</v>
       </c>
       <c r="L31" t="n">
-        <v>44.48</v>
+        <v>77.13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:48:07</t>
+          <t>06:39:06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.78</v>
+        <v>3.17</v>
       </c>
       <c r="F32" t="n">
-        <v>11.06</v>
+        <v>10.84</v>
       </c>
       <c r="G32" t="n">
-        <v>219.5</v>
+        <v>226.4</v>
       </c>
       <c r="H32" t="n">
-        <v>18.8</v>
+        <v>46.5</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>68.29000000000001</v>
+        <v>-63.65</v>
       </c>
       <c r="K32" t="n">
-        <v>-31.57</v>
+        <v>22.85</v>
       </c>
       <c r="L32" t="n">
-        <v>75.23</v>
+        <v>67.63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:50:04</t>
+          <t>06:40:42</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.47</v>
+        <v>3.63</v>
       </c>
       <c r="F33" t="n">
-        <v>9.449999999999999</v>
+        <v>10.88</v>
       </c>
       <c r="G33" t="n">
-        <v>210.9</v>
+        <v>214.6</v>
       </c>
       <c r="H33" t="n">
-        <v>38.1</v>
+        <v>52.7</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>11.18</v>
+        <v>-77.75</v>
       </c>
       <c r="K33" t="n">
-        <v>-73.59</v>
+        <v>36.51</v>
       </c>
       <c r="L33" t="n">
-        <v>74.43000000000001</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:52:00</t>
+          <t>06:41:41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.22</v>
+        <v>4.29</v>
       </c>
       <c r="F34" t="n">
-        <v>14.95</v>
+        <v>13.37</v>
       </c>
       <c r="G34" t="n">
-        <v>209.8</v>
+        <v>219.5</v>
       </c>
       <c r="H34" t="n">
-        <v>45.6</v>
+        <v>27.8</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-69.22</v>
+        <v>-54.32</v>
       </c>
       <c r="K34" t="n">
-        <v>116.7</v>
+        <v>-120.28</v>
       </c>
       <c r="L34" t="n">
-        <v>135.68</v>
+        <v>131.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:57:59</t>
+          <t>06:46:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="F35" t="n">
-        <v>10.93</v>
+        <v>11.47</v>
       </c>
       <c r="G35" t="n">
-        <v>232.5</v>
+        <v>220.3</v>
       </c>
       <c r="H35" t="n">
-        <v>46.7</v>
+        <v>45.7</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>42.51</v>
+        <v>-41.01</v>
       </c>
       <c r="K35" t="n">
-        <v>-95.19</v>
+        <v>120.57</v>
       </c>
       <c r="L35" t="n">
-        <v>104.25</v>
+        <v>127.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:00:30</t>
+          <t>06:47:21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.84</v>
+        <v>3.17</v>
       </c>
       <c r="F36" t="n">
-        <v>14.41</v>
+        <v>11.27</v>
       </c>
       <c r="G36" t="n">
-        <v>217.8</v>
+        <v>224.2</v>
       </c>
       <c r="H36" t="n">
-        <v>57.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-28.25</v>
+        <v>14.87</v>
       </c>
       <c r="K36" t="n">
-        <v>-177.9</v>
+        <v>122.31</v>
       </c>
       <c r="L36" t="n">
-        <v>180.13</v>
+        <v>123.21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:02:10</t>
+          <t>06:48:50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.01</v>
+        <v>2.76</v>
       </c>
       <c r="F37" t="n">
-        <v>8.43</v>
+        <v>6.42</v>
       </c>
       <c r="G37" t="n">
-        <v>214.7</v>
+        <v>215.9</v>
       </c>
       <c r="H37" t="n">
-        <v>30.4</v>
+        <v>44.5</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>-67.17</v>
+        <v>-46.08</v>
       </c>
       <c r="K37" t="n">
-        <v>-80.20999999999999</v>
+        <v>-106.31</v>
       </c>
       <c r="L37" t="n">
-        <v>104.62</v>
+        <v>115.87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:05:43</t>
+          <t>06:54:03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.97</v>
+        <v>3.29</v>
       </c>
       <c r="F38" t="n">
-        <v>9.82</v>
+        <v>11.28</v>
       </c>
       <c r="G38" t="n">
-        <v>229.4</v>
+        <v>222.7</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>22.14</v>
+        <v>-144.53</v>
       </c>
       <c r="K38" t="n">
-        <v>118.79</v>
+        <v>-173.78</v>
       </c>
       <c r="L38" t="n">
-        <v>120.84</v>
+        <v>226.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:07:48</t>
+          <t>06:56:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.22</v>
+        <v>4.06</v>
       </c>
       <c r="F39" t="n">
-        <v>11.19</v>
+        <v>14.95</v>
       </c>
       <c r="G39" t="n">
-        <v>218.7</v>
+        <v>217.9</v>
       </c>
       <c r="H39" t="n">
-        <v>35.9</v>
+        <v>49.5</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>171.09</v>
+        <v>-269.18</v>
       </c>
       <c r="K39" t="n">
-        <v>-59.61</v>
+        <v>62.35</v>
       </c>
       <c r="L39" t="n">
-        <v>181.18</v>
+        <v>276.31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:09:48</t>
+          <t>06:58:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.21</v>
+        <v>4.14</v>
       </c>
       <c r="F40" t="n">
-        <v>14.95</v>
+        <v>13.24</v>
       </c>
       <c r="G40" t="n">
-        <v>238.6</v>
+        <v>230.1</v>
       </c>
       <c r="H40" t="n">
-        <v>19.6</v>
+        <v>57.7</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-15.64</v>
+        <v>421.87</v>
       </c>
       <c r="K40" t="n">
-        <v>261.09</v>
+        <v>31.32</v>
       </c>
       <c r="L40" t="n">
-        <v>261.56</v>
+        <v>423.03</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:14:01</t>
+          <t>07:03:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="F41" t="n">
-        <v>12.65</v>
+        <v>11.76</v>
       </c>
       <c r="G41" t="n">
-        <v>233.9</v>
+        <v>221.6</v>
       </c>
       <c r="H41" t="n">
-        <v>17.7</v>
+        <v>25</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-163</v>
+        <v>-144.1</v>
       </c>
       <c r="K41" t="n">
-        <v>-260.78</v>
+        <v>203.38</v>
       </c>
       <c r="L41" t="n">
-        <v>307.53</v>
+        <v>249.26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:15:14</t>
+          <t>07:04:16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="F42" t="n">
-        <v>10.86</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>216.7</v>
+        <v>238.6</v>
       </c>
       <c r="H42" t="n">
-        <v>48.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>-186.08</v>
+        <v>-143.12</v>
       </c>
       <c r="K42" t="n">
-        <v>53.53</v>
+        <v>37.14</v>
       </c>
       <c r="L42" t="n">
-        <v>193.62</v>
+        <v>147.86</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:15:52</t>
+          <t>07:05:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.56</v>
+        <v>3.26</v>
       </c>
       <c r="F43" t="n">
-        <v>14.95</v>
+        <v>13.73</v>
       </c>
       <c r="G43" t="n">
-        <v>213.4</v>
+        <v>220.1</v>
       </c>
       <c r="H43" t="n">
-        <v>6.9</v>
+        <v>67</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>-34.16</v>
+        <v>-163.63</v>
       </c>
       <c r="K43" t="n">
-        <v>-284.65</v>
+        <v>6.93</v>
       </c>
       <c r="L43" t="n">
-        <v>286.69</v>
+        <v>163.78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:24:54</t>
+          <t>07:17:29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.35</v>
+        <v>4.01</v>
       </c>
       <c r="F44" t="n">
-        <v>13.91</v>
+        <v>13.18</v>
       </c>
       <c r="G44" t="n">
-        <v>214.3</v>
+        <v>209.5</v>
       </c>
       <c r="H44" t="n">
-        <v>65</v>
+        <v>23.4</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>34.67</v>
+        <v>67.19</v>
       </c>
       <c r="K44" t="n">
-        <v>62.07</v>
+        <v>-25.84</v>
       </c>
       <c r="L44" t="n">
-        <v>71.09999999999999</v>
+        <v>71.98999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:26:38</t>
+          <t>07:19:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.64</v>
+        <v>4.58</v>
       </c>
       <c r="F45" t="n">
-        <v>13.16</v>
+        <v>14.95</v>
       </c>
       <c r="G45" t="n">
-        <v>210.4</v>
+        <v>213.3</v>
       </c>
       <c r="H45" t="n">
-        <v>17.7</v>
+        <v>61.5</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>36.5</v>
+        <v>98.36</v>
       </c>
       <c r="K45" t="n">
-        <v>-45.78</v>
+        <v>10.88</v>
       </c>
       <c r="L45" t="n">
-        <v>58.55</v>
+        <v>98.95999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:27:19</t>
+          <t>07:20:47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="F46" t="n">
-        <v>8.279999999999999</v>
+        <v>12.43</v>
       </c>
       <c r="G46" t="n">
-        <v>221.1</v>
+        <v>210.6</v>
       </c>
       <c r="H46" t="n">
-        <v>26.1</v>
+        <v>36.1</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>39.22</v>
+        <v>-63.16</v>
       </c>
       <c r="K46" t="n">
-        <v>-15.96</v>
+        <v>6.27</v>
       </c>
       <c r="L46" t="n">
-        <v>42.34</v>
+        <v>63.47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:32:13</t>
+          <t>07:25:41</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.27</v>
+        <v>3.65</v>
       </c>
       <c r="F47" t="n">
-        <v>14.95</v>
+        <v>12.57</v>
       </c>
       <c r="G47" t="n">
-        <v>213.8</v>
+        <v>213</v>
       </c>
       <c r="H47" t="n">
-        <v>56.4</v>
+        <v>61.7</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>38.48</v>
+        <v>51.91</v>
       </c>
       <c r="K47" t="n">
-        <v>36.83</v>
+        <v>-121.27</v>
       </c>
       <c r="L47" t="n">
-        <v>53.26</v>
+        <v>131.91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:33:31</t>
+          <t>07:28:07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.18</v>
+        <v>4.51</v>
       </c>
       <c r="F48" t="n">
-        <v>12.7</v>
+        <v>14.95</v>
       </c>
       <c r="G48" t="n">
-        <v>217</v>
+        <v>209.5</v>
       </c>
       <c r="H48" t="n">
-        <v>60.1</v>
+        <v>60.7</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>72.92</v>
+        <v>96.53</v>
       </c>
       <c r="K48" t="n">
-        <v>34.05</v>
+        <v>-68.16</v>
       </c>
       <c r="L48" t="n">
-        <v>80.48</v>
+        <v>118.17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:35:04</t>
+          <t>07:29:34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.23</v>
+        <v>4.04</v>
       </c>
       <c r="F49" t="n">
-        <v>13.48</v>
+        <v>14.95</v>
       </c>
       <c r="G49" t="n">
-        <v>206.7</v>
+        <v>220.8</v>
       </c>
       <c r="H49" t="n">
-        <v>63.3</v>
+        <v>34.5</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-50</v>
+        <v>77.69</v>
       </c>
       <c r="K49" t="n">
-        <v>-17.2</v>
+        <v>55.72</v>
       </c>
       <c r="L49" t="n">
-        <v>52.87</v>
+        <v>95.61</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:40:03</t>
+          <t>07:33:09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.92</v>
+        <v>2.96</v>
       </c>
       <c r="F50" t="n">
-        <v>14.95</v>
+        <v>9.85</v>
       </c>
       <c r="G50" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H50" t="n">
-        <v>46.9</v>
+        <v>46.2</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J50" t="n">
-        <v>21.84</v>
+        <v>21.64</v>
       </c>
       <c r="K50" t="n">
-        <v>-188.57</v>
+        <v>-110.87</v>
       </c>
       <c r="L50" t="n">
-        <v>189.83</v>
+        <v>112.96</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:42:20</t>
+          <t>07:34:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.3</v>
+        <v>4.95</v>
       </c>
       <c r="F51" t="n">
-        <v>14.24</v>
+        <v>14.95</v>
       </c>
       <c r="G51" t="n">
-        <v>202.5</v>
+        <v>233.1</v>
       </c>
       <c r="H51" t="n">
-        <v>59.8</v>
+        <v>65.5</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>12.96</v>
+        <v>-221.25</v>
       </c>
       <c r="K51" t="n">
-        <v>-34.26</v>
+        <v>-84.63</v>
       </c>
       <c r="L51" t="n">
-        <v>36.63</v>
+        <v>236.89</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:44:16</t>
+          <t>07:35:49</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="F52" t="n">
-        <v>11.46</v>
+        <v>13.96</v>
       </c>
       <c r="G52" t="n">
-        <v>208.6</v>
+        <v>213.9</v>
       </c>
       <c r="H52" t="n">
-        <v>53.6</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>97.04000000000001</v>
+        <v>77.16</v>
       </c>
       <c r="K52" t="n">
-        <v>-99.22</v>
+        <v>76.84</v>
       </c>
       <c r="L52" t="n">
-        <v>138.78</v>
+        <v>108.89</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:49:12</t>
+          <t>07:41:59</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.96</v>
+        <v>3.55</v>
       </c>
       <c r="F53" t="n">
-        <v>11.82</v>
+        <v>11.16</v>
       </c>
       <c r="G53" t="n">
-        <v>225.5</v>
+        <v>223.9</v>
       </c>
       <c r="H53" t="n">
-        <v>70.8</v>
+        <v>41</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>198.41</v>
+        <v>-82.05</v>
       </c>
       <c r="K53" t="n">
-        <v>46.34</v>
+        <v>-160.45</v>
       </c>
       <c r="L53" t="n">
-        <v>203.75</v>
+        <v>180.21</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:50:16</t>
+          <t>07:44:19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.84</v>
+        <v>3.99</v>
       </c>
       <c r="F54" t="n">
-        <v>14.95</v>
+        <v>12.22</v>
       </c>
       <c r="G54" t="n">
-        <v>224.8</v>
+        <v>219.5</v>
       </c>
       <c r="H54" t="n">
-        <v>15.6</v>
+        <v>18.8</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>-76.02</v>
+        <v>219.06</v>
       </c>
       <c r="K54" t="n">
-        <v>-188.85</v>
+        <v>-42.72</v>
       </c>
       <c r="L54" t="n">
-        <v>203.57</v>
+        <v>223.19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:51:55</t>
+          <t>07:46:39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.45</v>
+        <v>3.68</v>
       </c>
       <c r="F55" t="n">
-        <v>14.95</v>
+        <v>10.58</v>
       </c>
       <c r="G55" t="n">
-        <v>220.6</v>
+        <v>210.9</v>
       </c>
       <c r="H55" t="n">
-        <v>39.7</v>
+        <v>38.1</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-140.25</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>114.1</v>
+        <v>-201.56</v>
       </c>
       <c r="L55" t="n">
-        <v>180.8</v>
+        <v>212.45</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:55:37</t>
+          <t>07:52:41</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.81</v>
+        <v>5.44</v>
       </c>
       <c r="F56" t="n">
-        <v>11.86</v>
+        <v>14.95</v>
       </c>
       <c r="G56" t="n">
-        <v>233</v>
+        <v>209.8</v>
       </c>
       <c r="H56" t="n">
-        <v>25.6</v>
+        <v>45.6</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-102.18</v>
+        <v>-185.18</v>
       </c>
       <c r="K56" t="n">
-        <v>-87.84</v>
+        <v>339.15</v>
       </c>
       <c r="L56" t="n">
-        <v>134.75</v>
+        <v>386.42</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:57:32</t>
+          <t>07:53:41</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.32</v>
+        <v>4.14</v>
       </c>
       <c r="F57" t="n">
-        <v>13.15</v>
+        <v>14.03</v>
       </c>
       <c r="G57" t="n">
-        <v>212.3</v>
+        <v>231.3</v>
       </c>
       <c r="H57" t="n">
-        <v>38.8</v>
+        <v>33.9</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-107.59</v>
+        <v>-224.25</v>
       </c>
       <c r="K57" t="n">
-        <v>93.33</v>
+        <v>94.97</v>
       </c>
       <c r="L57" t="n">
-        <v>142.43</v>
+        <v>243.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:58:44</t>
+          <t>07:55:01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.96</v>
+        <v>4.33</v>
       </c>
       <c r="F58" t="n">
-        <v>10.55</v>
+        <v>14.95</v>
       </c>
       <c r="G58" t="n">
-        <v>219.4</v>
+        <v>214.1</v>
       </c>
       <c r="H58" t="n">
-        <v>37.6</v>
+        <v>57.5</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-168.5</v>
+        <v>-87.93000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>-51.56</v>
+        <v>-353.4</v>
       </c>
       <c r="L58" t="n">
-        <v>176.21</v>
+        <v>364.18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:09:14</t>
+          <t>08:03:36</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.72</v>
+        <v>4.02</v>
       </c>
       <c r="F59" t="n">
-        <v>8.93</v>
+        <v>10.03</v>
       </c>
       <c r="G59" t="n">
-        <v>217.1</v>
+        <v>208.9</v>
       </c>
       <c r="H59" t="n">
-        <v>63.2</v>
+        <v>33.1</v>
       </c>
       <c r="I59" t="n">
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-64.62</v>
+        <v>61.69</v>
       </c>
       <c r="K59" t="n">
-        <v>-10.94</v>
+        <v>50.07</v>
       </c>
       <c r="L59" t="n">
-        <v>65.54000000000001</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:10:53</t>
+          <t>08:04:03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.53</v>
+        <v>4.64</v>
       </c>
       <c r="F60" t="n">
-        <v>13.18</v>
+        <v>11.85</v>
       </c>
       <c r="G60" t="n">
-        <v>211.3</v>
+        <v>220.1</v>
       </c>
       <c r="H60" t="n">
-        <v>75.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-29.35</v>
+        <v>-102.66</v>
       </c>
       <c r="K60" t="n">
-        <v>43.26</v>
+        <v>34.6</v>
       </c>
       <c r="L60" t="n">
-        <v>52.28</v>
+        <v>108.33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:12:38</t>
+          <t>08:05:19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.21</v>
+        <v>4.36</v>
       </c>
       <c r="F61" t="n">
-        <v>13.17</v>
+        <v>12.1</v>
       </c>
       <c r="G61" t="n">
-        <v>218.2</v>
+        <v>224.2</v>
       </c>
       <c r="H61" t="n">
-        <v>34.3</v>
+        <v>53.4</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>4.67</v>
+        <v>-12.98</v>
       </c>
       <c r="K61" t="n">
-        <v>43.67</v>
+        <v>60.21</v>
       </c>
       <c r="L61" t="n">
-        <v>43.92</v>
+        <v>61.59</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:17:33</t>
+          <t>08:08:47</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.87</v>
+        <v>4.55</v>
       </c>
       <c r="F62" t="n">
         <v>14.95</v>
       </c>
       <c r="G62" t="n">
-        <v>223.9</v>
+        <v>227.8</v>
       </c>
       <c r="H62" t="n">
-        <v>36.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-83.72</v>
+        <v>-112.33</v>
       </c>
       <c r="K62" t="n">
-        <v>10.02</v>
+        <v>23.06</v>
       </c>
       <c r="L62" t="n">
-        <v>84.31999999999999</v>
+        <v>114.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:19:39</t>
+          <t>08:10:40</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.66</v>
+        <v>4.61</v>
       </c>
       <c r="F63" t="n">
-        <v>11.85</v>
+        <v>11.6</v>
       </c>
       <c r="G63" t="n">
-        <v>235.6</v>
+        <v>224.8</v>
       </c>
       <c r="H63" t="n">
-        <v>44.7</v>
+        <v>54.3</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-70.84</v>
+        <v>-194.53</v>
       </c>
       <c r="K63" t="n">
-        <v>29.63</v>
+        <v>183.37</v>
       </c>
       <c r="L63" t="n">
-        <v>76.79000000000001</v>
+        <v>267.33</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:20:47</t>
+          <t>08:12:06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.22</v>
+        <v>3.85</v>
       </c>
       <c r="F64" t="n">
-        <v>13.52</v>
+        <v>14.95</v>
       </c>
       <c r="G64" t="n">
-        <v>221.3</v>
+        <v>220.7</v>
       </c>
       <c r="H64" t="n">
-        <v>36.7</v>
+        <v>24</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J64" t="n">
-        <v>69.91</v>
+        <v>92.8</v>
       </c>
       <c r="K64" t="n">
-        <v>42.9</v>
+        <v>-78.34</v>
       </c>
       <c r="L64" t="n">
-        <v>82.03</v>
+        <v>121.45</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:26:19</t>
+          <t>08:15:52</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.74</v>
+        <v>4.99</v>
       </c>
       <c r="F65" t="n">
         <v>14.95</v>
       </c>
       <c r="G65" t="n">
-        <v>215.9</v>
+        <v>220.5</v>
       </c>
       <c r="H65" t="n">
-        <v>37.5</v>
+        <v>28.8</v>
       </c>
       <c r="I65" t="n">
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>38.66</v>
+        <v>61.15</v>
       </c>
       <c r="K65" t="n">
-        <v>-107.99</v>
+        <v>-188.39</v>
       </c>
       <c r="L65" t="n">
-        <v>114.7</v>
+        <v>198.06</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:28:36</t>
+          <t>08:17:31</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.79</v>
+        <v>4.03</v>
       </c>
       <c r="F66" t="n">
-        <v>14.95</v>
+        <v>14.49</v>
       </c>
       <c r="G66" t="n">
-        <v>219</v>
+        <v>230.3</v>
       </c>
       <c r="H66" t="n">
-        <v>59.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-130.57</v>
+        <v>126.81</v>
       </c>
       <c r="K66" t="n">
-        <v>-57.22</v>
+        <v>76.98</v>
       </c>
       <c r="L66" t="n">
-        <v>142.56</v>
+        <v>148.35</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:29:22</t>
+          <t>08:18:22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.34</v>
+        <v>3.51</v>
       </c>
       <c r="F67" t="n">
-        <v>14.51</v>
+        <v>10.35</v>
       </c>
       <c r="G67" t="n">
-        <v>229.3</v>
+        <v>224</v>
       </c>
       <c r="H67" t="n">
-        <v>18.3</v>
+        <v>68.3</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>60.18</v>
+        <v>-112.89</v>
       </c>
       <c r="K67" t="n">
-        <v>-105.45</v>
+        <v>33.26</v>
       </c>
       <c r="L67" t="n">
-        <v>121.41</v>
+        <v>117.68</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:34:12</t>
+          <t>08:23:50</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="F68" t="n">
-        <v>11.35</v>
+        <v>13.65</v>
       </c>
       <c r="G68" t="n">
-        <v>214.1</v>
+        <v>220.4</v>
       </c>
       <c r="H68" t="n">
-        <v>32</v>
+        <v>22.1</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-130.4</v>
+        <v>-129.61</v>
       </c>
       <c r="K68" t="n">
-        <v>84.72</v>
+        <v>-238.23</v>
       </c>
       <c r="L68" t="n">
-        <v>155.5</v>
+        <v>271.21</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:36:10</t>
+          <t>08:26:09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.63</v>
+        <v>3.28</v>
       </c>
       <c r="F69" t="n">
-        <v>11.25</v>
+        <v>7.46</v>
       </c>
       <c r="G69" t="n">
-        <v>218.4</v>
+        <v>237.6</v>
       </c>
       <c r="H69" t="n">
-        <v>57.2</v>
+        <v>25.5</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-211.14</v>
+        <v>-59.63</v>
       </c>
       <c r="K69" t="n">
-        <v>45.16</v>
+        <v>-178.36</v>
       </c>
       <c r="L69" t="n">
-        <v>215.91</v>
+        <v>188.06</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:37:05</t>
+          <t>08:28:17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.75</v>
+        <v>4.49</v>
       </c>
       <c r="F70" t="n">
-        <v>14.61</v>
+        <v>14.95</v>
       </c>
       <c r="G70" t="n">
-        <v>207.4</v>
+        <v>224.9</v>
       </c>
       <c r="H70" t="n">
-        <v>49</v>
+        <v>34.8</v>
       </c>
       <c r="I70" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-187.88</v>
+        <v>284.26</v>
       </c>
       <c r="K70" t="n">
-        <v>112.83</v>
+        <v>132.7</v>
       </c>
       <c r="L70" t="n">
-        <v>219.16</v>
+        <v>313.71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:42:04</t>
+          <t>08:34:10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.18</v>
+        <v>3.75</v>
       </c>
       <c r="F71" t="n">
-        <v>14.8</v>
+        <v>14.95</v>
       </c>
       <c r="G71" t="n">
-        <v>213.4</v>
+        <v>230.5</v>
       </c>
       <c r="H71" t="n">
-        <v>24.4</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>241.09</v>
+        <v>69.36</v>
       </c>
       <c r="K71" t="n">
-        <v>-141.64</v>
+        <v>-224.53</v>
       </c>
       <c r="L71" t="n">
-        <v>279.62</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:43:19</t>
+          <t>08:35:37</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.55</v>
+        <v>3.45</v>
       </c>
       <c r="F72" t="n">
-        <v>14.95</v>
+        <v>10.7</v>
       </c>
       <c r="G72" t="n">
-        <v>227.8</v>
+        <v>216.4</v>
       </c>
       <c r="H72" t="n">
-        <v>55.7</v>
+        <v>40.2</v>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-1.21</v>
+        <v>65.3</v>
       </c>
       <c r="K72" t="n">
-        <v>-242.49</v>
+        <v>-268.87</v>
       </c>
       <c r="L72" t="n">
-        <v>242.5</v>
+        <v>276.68</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:44:38</t>
+          <t>08:37:46</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.91</v>
+        <v>4.43</v>
       </c>
       <c r="F73" t="n">
-        <v>14.95</v>
+        <v>11.46</v>
       </c>
       <c r="G73" t="n">
-        <v>222.8</v>
+        <v>214.2</v>
       </c>
       <c r="H73" t="n">
-        <v>65.7</v>
+        <v>65.8</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-234.64</v>
+        <v>-1.36</v>
       </c>
       <c r="K73" t="n">
-        <v>-48.63</v>
+        <v>-412.04</v>
       </c>
       <c r="L73" t="n">
-        <v>239.63</v>
+        <v>412.04</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:54:52</t>
+          <t>08:50:46</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.67</v>
+        <v>4.28</v>
       </c>
       <c r="F74" t="n">
         <v>14.95</v>
       </c>
       <c r="G74" t="n">
-        <v>229.2</v>
+        <v>207.8</v>
       </c>
       <c r="H74" t="n">
-        <v>30.5</v>
+        <v>45.5</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-71.37</v>
+        <v>124.12</v>
       </c>
       <c r="K74" t="n">
-        <v>-69.26000000000001</v>
+        <v>-43.61</v>
       </c>
       <c r="L74" t="n">
-        <v>99.45</v>
+        <v>131.56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:56:54</t>
+          <t>08:53:24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.55</v>
+        <v>4.12</v>
       </c>
       <c r="F75" t="n">
         <v>14.95</v>
       </c>
       <c r="G75" t="n">
-        <v>210.9</v>
+        <v>223.3</v>
       </c>
       <c r="H75" t="n">
-        <v>46.3</v>
+        <v>33.6</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>84.56</v>
+        <v>-6.9</v>
       </c>
       <c r="K75" t="n">
-        <v>-24.81</v>
+        <v>-85.59</v>
       </c>
       <c r="L75" t="n">
-        <v>88.12</v>
+        <v>85.87</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:58:20</t>
+          <t>08:55:20</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.93</v>
+        <v>5.11</v>
       </c>
       <c r="F76" t="n">
-        <v>11.3</v>
+        <v>14.95</v>
       </c>
       <c r="G76" t="n">
-        <v>223.2</v>
+        <v>222.1</v>
       </c>
       <c r="H76" t="n">
-        <v>54.8</v>
+        <v>69.7</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>45.82</v>
+        <v>69.63</v>
       </c>
       <c r="K76" t="n">
-        <v>-58.51</v>
+        <v>78.39</v>
       </c>
       <c r="L76" t="n">
-        <v>74.31999999999999</v>
+        <v>104.85</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:03:08</t>
+          <t>08:59:49</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="F77" t="n">
-        <v>10.37</v>
+        <v>11.67</v>
       </c>
       <c r="G77" t="n">
-        <v>226.9</v>
+        <v>215.8</v>
       </c>
       <c r="H77" t="n">
-        <v>54.7</v>
+        <v>24.9</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>32.29</v>
+        <v>-4.13</v>
       </c>
       <c r="K77" t="n">
-        <v>59.44</v>
+        <v>-88.16</v>
       </c>
       <c r="L77" t="n">
-        <v>67.64</v>
+        <v>88.26000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:05:09</t>
+          <t>09:01:59</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.73</v>
+        <v>3.67</v>
       </c>
       <c r="F78" t="n">
         <v>14.95</v>
       </c>
       <c r="G78" t="n">
-        <v>225.9</v>
+        <v>216.7</v>
       </c>
       <c r="H78" t="n">
-        <v>11</v>
+        <v>30.1</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>-171.59</v>
+        <v>-60.55</v>
       </c>
       <c r="K78" t="n">
-        <v>-11.36</v>
+        <v>42.19</v>
       </c>
       <c r="L78" t="n">
-        <v>171.96</v>
+        <v>73.81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:07:14</t>
+          <t>09:03:57</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.32</v>
+        <v>4.11</v>
       </c>
       <c r="F79" t="n">
-        <v>14.95</v>
+        <v>13.38</v>
       </c>
       <c r="G79" t="n">
-        <v>227.4</v>
+        <v>202.1</v>
       </c>
       <c r="H79" t="n">
-        <v>39.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J79" t="n">
-        <v>-75.34999999999999</v>
+        <v>29.41</v>
       </c>
       <c r="K79" t="n">
-        <v>-97.43000000000001</v>
+        <v>109.15</v>
       </c>
       <c r="L79" t="n">
-        <v>123.17</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:12:10</t>
+          <t>09:09:50</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.64</v>
+        <v>4.76</v>
       </c>
       <c r="F80" t="n">
-        <v>14.95</v>
+        <v>14.85</v>
       </c>
       <c r="G80" t="n">
-        <v>208.6</v>
+        <v>227.2</v>
       </c>
       <c r="H80" t="n">
-        <v>19.5</v>
+        <v>11.4</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>-48.4</v>
+        <v>-72.78</v>
       </c>
       <c r="K80" t="n">
-        <v>-133.26</v>
+        <v>107.27</v>
       </c>
       <c r="L80" t="n">
-        <v>141.77</v>
+        <v>129.63</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:14:15</t>
+          <t>09:11:58</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.73</v>
+        <v>4.18</v>
       </c>
       <c r="F81" t="n">
-        <v>14.95</v>
+        <v>14.74</v>
       </c>
       <c r="G81" t="n">
-        <v>208.4</v>
+        <v>214.3</v>
       </c>
       <c r="H81" t="n">
-        <v>68.5</v>
+        <v>46.9</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>145.29</v>
+        <v>-105.66</v>
       </c>
       <c r="K81" t="n">
-        <v>59.36</v>
+        <v>127.63</v>
       </c>
       <c r="L81" t="n">
-        <v>156.95</v>
+        <v>165.69</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:16:46</t>
+          <t>09:13:44</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.16</v>
+        <v>4.72</v>
       </c>
       <c r="F82" t="n">
-        <v>11.3</v>
+        <v>14.95</v>
       </c>
       <c r="G82" t="n">
-        <v>216.8</v>
+        <v>220.2</v>
       </c>
       <c r="H82" t="n">
-        <v>53.9</v>
+        <v>92.3</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>134.38</v>
+        <v>-173.2</v>
       </c>
       <c r="K82" t="n">
-        <v>61.36</v>
+        <v>-137.69</v>
       </c>
       <c r="L82" t="n">
-        <v>147.73</v>
+        <v>221.26</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:21:25</t>
+          <t>09:18:01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.32</v>
+        <v>3.88</v>
       </c>
       <c r="F83" t="n">
-        <v>14.67</v>
+        <v>13.35</v>
       </c>
       <c r="G83" t="n">
-        <v>222.8</v>
+        <v>223.5</v>
       </c>
       <c r="H83" t="n">
-        <v>92.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-187.72</v>
+        <v>-70.17</v>
       </c>
       <c r="K83" t="n">
-        <v>-32.97</v>
+        <v>-249.03</v>
       </c>
       <c r="L83" t="n">
-        <v>190.59</v>
+        <v>258.73</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:23:33</t>
+          <t>09:20:07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.48</v>
+        <v>4.12</v>
       </c>
       <c r="F84" t="n">
-        <v>13.37</v>
+        <v>12.2</v>
       </c>
       <c r="G84" t="n">
-        <v>230.6</v>
+        <v>228.7</v>
       </c>
       <c r="H84" t="n">
-        <v>57.2</v>
+        <v>39.5</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-35.66</v>
+        <v>-262.46</v>
       </c>
       <c r="K84" t="n">
-        <v>-252.57</v>
+        <v>248.81</v>
       </c>
       <c r="L84" t="n">
-        <v>255.07</v>
+        <v>361.65</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:25:32</t>
+          <t>09:22:51</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="F85" t="n">
         <v>14.95</v>
       </c>
       <c r="G85" t="n">
-        <v>227.6</v>
+        <v>230.6</v>
       </c>
       <c r="H85" t="n">
-        <v>40</v>
+        <v>28.9</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>148.55</v>
+        <v>-76.64</v>
       </c>
       <c r="K85" t="n">
-        <v>-128.17</v>
+        <v>-278.48</v>
       </c>
       <c r="L85" t="n">
-        <v>196.2</v>
+        <v>288.84</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:30:14</t>
+          <t>09:28:34</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="F86" t="n">
         <v>14.95</v>
       </c>
       <c r="G86" t="n">
-        <v>215.9</v>
+        <v>219.2</v>
       </c>
       <c r="H86" t="n">
-        <v>75.5</v>
+        <v>7</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>213.12</v>
+        <v>-341.88</v>
       </c>
       <c r="K86" t="n">
-        <v>-191.99</v>
+        <v>-169.02</v>
       </c>
       <c r="L86" t="n">
-        <v>286.84</v>
+        <v>381.38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:31:48</t>
+          <t>09:30:31</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.98</v>
+        <v>3.71</v>
       </c>
       <c r="F87" t="n">
-        <v>14.95</v>
+        <v>11.5</v>
       </c>
       <c r="G87" t="n">
-        <v>222.9</v>
+        <v>215.2</v>
       </c>
       <c r="H87" t="n">
-        <v>79.8</v>
+        <v>20.8</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>86.26000000000001</v>
+        <v>353.24</v>
       </c>
       <c r="K87" t="n">
-        <v>-213.71</v>
+        <v>-68.65000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>230.46</v>
+        <v>359.85</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:33:39</t>
+          <t>09:32:12</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.81</v>
+        <v>4.61</v>
       </c>
       <c r="F88" t="n">
         <v>14.95</v>
       </c>
       <c r="G88" t="n">
-        <v>223</v>
+        <v>218.3</v>
       </c>
       <c r="H88" t="n">
-        <v>35.8</v>
+        <v>35</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J88" t="n">
-        <v>-255.96</v>
+        <v>367.85</v>
       </c>
       <c r="K88" t="n">
-        <v>-182.4</v>
+        <v>-238.49</v>
       </c>
       <c r="L88" t="n">
-        <v>314.3</v>
+        <v>438.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>33.16</v>
+        <v>37.57</v>
       </c>
       <c r="K14" t="n">
-        <v>38.96</v>
+        <v>44.13</v>
       </c>
       <c r="L14" t="n">
-        <v>51.16</v>
+        <v>57.96</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>12.92</v>
+        <v>15</v>
       </c>
       <c r="K15" t="n">
-        <v>47.71</v>
+        <v>55.41</v>
       </c>
       <c r="L15" t="n">
-        <v>49.43</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>82.14</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.88</v>
+        <v>-11.27</v>
       </c>
       <c r="L16" t="n">
-        <v>82.86</v>
+        <v>85.84</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-88.73999999999999</v>
+        <v>-94.54000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-34.84</v>
+        <v>-37.12</v>
       </c>
       <c r="L17" t="n">
-        <v>95.34</v>
+        <v>101.57</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>71.90000000000001</v>
+        <v>76.64</v>
       </c>
       <c r="K18" t="n">
-        <v>79.39</v>
+        <v>84.62</v>
       </c>
       <c r="L18" t="n">
-        <v>107.11</v>
+        <v>114.17</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>49.54</v>
+        <v>59.28</v>
       </c>
       <c r="K19" t="n">
-        <v>-33.26</v>
+        <v>-39.8</v>
       </c>
       <c r="L19" t="n">
-        <v>59.67</v>
+        <v>71.41</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-86.28</v>
+        <v>-95.95999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-90.34999999999999</v>
+        <v>-100.49</v>
       </c>
       <c r="L20" t="n">
-        <v>124.93</v>
+        <v>138.95</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>124.69</v>
+        <v>140.27</v>
       </c>
       <c r="K21" t="n">
-        <v>72.13</v>
+        <v>81.14</v>
       </c>
       <c r="L21" t="n">
-        <v>144.05</v>
+        <v>162.04</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-49.39</v>
+        <v>-55.21</v>
       </c>
       <c r="K22" t="n">
-        <v>-136.71</v>
+        <v>-152.83</v>
       </c>
       <c r="L22" t="n">
-        <v>145.35</v>
+        <v>162.49</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-123.97</v>
+        <v>-140.3</v>
       </c>
       <c r="K23" t="n">
-        <v>-161.67</v>
+        <v>-182.96</v>
       </c>
       <c r="L23" t="n">
-        <v>203.73</v>
+        <v>230.56</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-30.95</v>
+        <v>-38.12</v>
       </c>
       <c r="K24" t="n">
-        <v>136.77</v>
+        <v>168.45</v>
       </c>
       <c r="L24" t="n">
-        <v>140.23</v>
+        <v>172.71</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>203.64</v>
+        <v>219.27</v>
       </c>
       <c r="K25" t="n">
-        <v>-152</v>
+        <v>-163.66</v>
       </c>
       <c r="L25" t="n">
-        <v>254.11</v>
+        <v>273.62</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>14.07</v>
+        <v>18.47</v>
       </c>
       <c r="K26" t="n">
-        <v>-171.82</v>
+        <v>-225.61</v>
       </c>
       <c r="L26" t="n">
-        <v>172.4</v>
+        <v>226.37</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-10.81</v>
+        <v>-12.59</v>
       </c>
       <c r="K27" t="n">
-        <v>-309.4</v>
+        <v>-360.36</v>
       </c>
       <c r="L27" t="n">
-        <v>309.59</v>
+        <v>360.58</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>248.86</v>
+        <v>294.63</v>
       </c>
       <c r="K28" t="n">
-        <v>217.22</v>
+        <v>257.17</v>
       </c>
       <c r="L28" t="n">
-        <v>330.33</v>
+        <v>391.08</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="K29" t="n">
-        <v>68.11</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>68.12</v>
+        <v>74.28</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-32.08</v>
+        <v>-37.66</v>
       </c>
       <c r="K30" t="n">
-        <v>-39.07</v>
+        <v>-45.86</v>
       </c>
       <c r="L30" t="n">
-        <v>50.56</v>
+        <v>59.34</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-31.51</v>
+        <v>-35</v>
       </c>
       <c r="K31" t="n">
-        <v>-53.96</v>
+        <v>-59.94</v>
       </c>
       <c r="L31" t="n">
-        <v>62.49</v>
+        <v>69.41</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-132.72</v>
+        <v>-132.59</v>
       </c>
       <c r="K32" t="n">
-        <v>-33.2</v>
+        <v>-33.17</v>
       </c>
       <c r="L32" t="n">
-        <v>136.81</v>
+        <v>136.67</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>80.98</v>
+        <v>88.25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="L33" t="n">
-        <v>80.98</v>
+        <v>88.25</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.58</v>
+        <v>-1.92</v>
       </c>
       <c r="K34" t="n">
-        <v>-48.83</v>
+        <v>-59.46</v>
       </c>
       <c r="L34" t="n">
-        <v>48.86</v>
+        <v>59.49</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-175.61</v>
+        <v>-182.96</v>
       </c>
       <c r="K35" t="n">
-        <v>118</v>
+        <v>122.94</v>
       </c>
       <c r="L35" t="n">
-        <v>211.58</v>
+        <v>220.42</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-21.08</v>
+        <v>-26.41</v>
       </c>
       <c r="K36" t="n">
-        <v>90.95</v>
+        <v>113.97</v>
       </c>
       <c r="L36" t="n">
-        <v>93.36</v>
+        <v>116.99</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>84.89</v>
+        <v>96.55</v>
       </c>
       <c r="K37" t="n">
-        <v>-90.81999999999999</v>
+        <v>-103.3</v>
       </c>
       <c r="L37" t="n">
-        <v>124.32</v>
+        <v>141.39</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-43.78</v>
+        <v>-54.51</v>
       </c>
       <c r="K38" t="n">
-        <v>4.38</v>
+        <v>5.45</v>
       </c>
       <c r="L38" t="n">
-        <v>44</v>
+        <v>54.78</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-70.04000000000001</v>
+        <v>-83.44</v>
       </c>
       <c r="K39" t="n">
-        <v>-110.67</v>
+        <v>-131.83</v>
       </c>
       <c r="L39" t="n">
-        <v>130.97</v>
+        <v>156.02</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-69.8</v>
+        <v>-85.56999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-133.18</v>
+        <v>-163.26</v>
       </c>
       <c r="L40" t="n">
-        <v>150.36</v>
+        <v>184.32</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>102.67</v>
+        <v>134.29</v>
       </c>
       <c r="K41" t="n">
-        <v>-242.85</v>
+        <v>-317.65</v>
       </c>
       <c r="L41" t="n">
-        <v>263.66</v>
+        <v>344.87</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-11.12</v>
+        <v>-14.54</v>
       </c>
       <c r="K42" t="n">
-        <v>193.81</v>
+        <v>253.38</v>
       </c>
       <c r="L42" t="n">
-        <v>194.13</v>
+        <v>253.8</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-17.95</v>
+        <v>-25.01</v>
       </c>
       <c r="K43" t="n">
-        <v>241.15</v>
+        <v>335.91</v>
       </c>
       <c r="L43" t="n">
-        <v>241.82</v>
+        <v>336.84</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.1</v>
+        <v>-58.28</v>
       </c>
       <c r="K44" t="n">
-        <v>-42.08</v>
+        <v>-43.72</v>
       </c>
       <c r="L44" t="n">
-        <v>70.13</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>40.75</v>
+        <v>42.76</v>
       </c>
       <c r="K45" t="n">
-        <v>71.45</v>
+        <v>74.98</v>
       </c>
       <c r="L45" t="n">
-        <v>82.26000000000001</v>
+        <v>86.31</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-49.64</v>
+        <v>-51.76</v>
       </c>
       <c r="K46" t="n">
-        <v>-91.12</v>
+        <v>-95</v>
       </c>
       <c r="L46" t="n">
-        <v>103.76</v>
+        <v>108.18</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>69.63</v>
+        <v>80.8</v>
       </c>
       <c r="K47" t="n">
-        <v>-23.98</v>
+        <v>-27.83</v>
       </c>
       <c r="L47" t="n">
-        <v>73.64</v>
+        <v>85.45999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>84.3</v>
+        <v>89.56</v>
       </c>
       <c r="K48" t="n">
-        <v>-62.1</v>
+        <v>-65.97</v>
       </c>
       <c r="L48" t="n">
-        <v>104.7</v>
+        <v>111.23</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-55.89</v>
+        <v>-60.6</v>
       </c>
       <c r="K49" t="n">
-        <v>-72.03</v>
+        <v>-78.09</v>
       </c>
       <c r="L49" t="n">
-        <v>91.17</v>
+        <v>98.84</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-59.13</v>
+        <v>-62.25</v>
       </c>
       <c r="K50" t="n">
-        <v>-189.01</v>
+        <v>-198.99</v>
       </c>
       <c r="L50" t="n">
-        <v>198.05</v>
+        <v>208.5</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>40.14</v>
+        <v>49.54</v>
       </c>
       <c r="K51" t="n">
-        <v>-73.95999999999999</v>
+        <v>-91.27</v>
       </c>
       <c r="L51" t="n">
-        <v>84.15000000000001</v>
+        <v>103.85</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-27.58</v>
+        <v>-29.75</v>
       </c>
       <c r="K52" t="n">
-        <v>156.69</v>
+        <v>169.05</v>
       </c>
       <c r="L52" t="n">
-        <v>159.1</v>
+        <v>171.65</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>221.47</v>
+        <v>260.71</v>
       </c>
       <c r="K53" t="n">
-        <v>167.27</v>
+        <v>196.9</v>
       </c>
       <c r="L53" t="n">
-        <v>277.54</v>
+        <v>326.71</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>101.75</v>
+        <v>126.77</v>
       </c>
       <c r="K54" t="n">
-        <v>-93.64</v>
+        <v>-116.66</v>
       </c>
       <c r="L54" t="n">
-        <v>138.28</v>
+        <v>172.28</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>158.09</v>
+        <v>202.14</v>
       </c>
       <c r="K55" t="n">
-        <v>-16.38</v>
+        <v>-20.94</v>
       </c>
       <c r="L55" t="n">
-        <v>158.94</v>
+        <v>203.23</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-301.44</v>
+        <v>-358.9</v>
       </c>
       <c r="K56" t="n">
-        <v>99.34</v>
+        <v>118.28</v>
       </c>
       <c r="L56" t="n">
-        <v>317.39</v>
+        <v>377.89</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>139.37</v>
+        <v>171.23</v>
       </c>
       <c r="K57" t="n">
-        <v>223.26</v>
+        <v>274.3</v>
       </c>
       <c r="L57" t="n">
-        <v>263.19</v>
+        <v>323.35</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>154.61</v>
+        <v>194.48</v>
       </c>
       <c r="K58" t="n">
-        <v>243.46</v>
+        <v>306.23</v>
       </c>
       <c r="L58" t="n">
-        <v>288.4</v>
+        <v>362.77</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>8.25</v>
+        <v>8.82</v>
       </c>
       <c r="K59" t="n">
-        <v>81.02</v>
+        <v>86.61</v>
       </c>
       <c r="L59" t="n">
-        <v>81.44</v>
+        <v>87.06</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>62.46</v>
+        <v>64.87</v>
       </c>
       <c r="K60" t="n">
-        <v>73.89</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>96.75</v>
+        <v>100.48</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-57.86</v>
+        <v>-65.78</v>
       </c>
       <c r="K61" t="n">
-        <v>24.73</v>
+        <v>28.11</v>
       </c>
       <c r="L61" t="n">
-        <v>62.92</v>
+        <v>71.53</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-71.90000000000001</v>
+        <v>-76.43000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-48.8</v>
+        <v>-51.88</v>
       </c>
       <c r="L62" t="n">
-        <v>86.90000000000001</v>
+        <v>92.37</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-61.15</v>
+        <v>-73.05</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.81</v>
+        <v>-10.53</v>
       </c>
       <c r="L63" t="n">
-        <v>61.78</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>76.94</v>
+        <v>79.77</v>
       </c>
       <c r="K64" t="n">
-        <v>-76.97</v>
+        <v>-79.8</v>
       </c>
       <c r="L64" t="n">
-        <v>108.83</v>
+        <v>112.83</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.71</v>
+        <v>-6.09</v>
       </c>
       <c r="K65" t="n">
-        <v>177.78</v>
+        <v>189.45</v>
       </c>
       <c r="L65" t="n">
-        <v>177.87</v>
+        <v>189.55</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-118.41</v>
+        <v>-129.22</v>
       </c>
       <c r="K66" t="n">
-        <v>60.52</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>132.98</v>
+        <v>145.11</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>35.07</v>
+        <v>39.66</v>
       </c>
       <c r="K67" t="n">
-        <v>-166.82</v>
+        <v>-188.65</v>
       </c>
       <c r="L67" t="n">
-        <v>170.46</v>
+        <v>192.78</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>121.81</v>
+        <v>147.42</v>
       </c>
       <c r="K68" t="n">
-        <v>122.93</v>
+        <v>148.77</v>
       </c>
       <c r="L68" t="n">
-        <v>173.06</v>
+        <v>209.44</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-49.26</v>
+        <v>-63.86</v>
       </c>
       <c r="K69" t="n">
-        <v>120.32</v>
+        <v>155.97</v>
       </c>
       <c r="L69" t="n">
-        <v>130.01</v>
+        <v>168.54</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>63.25</v>
+        <v>75.75</v>
       </c>
       <c r="K70" t="n">
-        <v>-176.75</v>
+        <v>-211.66</v>
       </c>
       <c r="L70" t="n">
-        <v>187.73</v>
+        <v>224.81</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>252.04</v>
+        <v>295.95</v>
       </c>
       <c r="K71" t="n">
-        <v>-221.82</v>
+        <v>-260.46</v>
       </c>
       <c r="L71" t="n">
-        <v>335.75</v>
+        <v>394.24</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-26.18</v>
+        <v>-31.1</v>
       </c>
       <c r="K72" t="n">
-        <v>274.59</v>
+        <v>326.17</v>
       </c>
       <c r="L72" t="n">
-        <v>275.83</v>
+        <v>327.65</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-252.35</v>
+        <v>-298.35</v>
       </c>
       <c r="K73" t="n">
-        <v>-188.4</v>
+        <v>-222.74</v>
       </c>
       <c r="L73" t="n">
-        <v>314.92</v>
+        <v>372.32</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>46.18</v>
+        <v>55.55</v>
       </c>
       <c r="K74" t="n">
-        <v>-8.210000000000001</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>46.9</v>
+        <v>56.42</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>40.31</v>
+        <v>42.16</v>
       </c>
       <c r="K75" t="n">
-        <v>89.76000000000001</v>
+        <v>93.89</v>
       </c>
       <c r="L75" t="n">
-        <v>98.40000000000001</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.32</v>
+        <v>-21.82</v>
       </c>
       <c r="K76" t="n">
-        <v>93.86</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>96.25</v>
+        <v>98.48</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-19.18</v>
+        <v>-20.09</v>
       </c>
       <c r="K77" t="n">
-        <v>-113.36</v>
+        <v>-118.71</v>
       </c>
       <c r="L77" t="n">
-        <v>114.97</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-22.42</v>
+        <v>-24.94</v>
       </c>
       <c r="K78" t="n">
-        <v>71.66</v>
+        <v>79.7</v>
       </c>
       <c r="L78" t="n">
-        <v>75.09</v>
+        <v>83.51000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>92.06999999999999</v>
+        <v>98.11</v>
       </c>
       <c r="K79" t="n">
-        <v>-55.89</v>
+        <v>-59.56</v>
       </c>
       <c r="L79" t="n">
-        <v>107.71</v>
+        <v>114.78</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>130.27</v>
+        <v>149.6</v>
       </c>
       <c r="K80" t="n">
-        <v>-84.22</v>
+        <v>-96.70999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>155.12</v>
+        <v>178.14</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="K81" t="n">
-        <v>-138.3</v>
+        <v>-177.5</v>
       </c>
       <c r="L81" t="n">
-        <v>138.3</v>
+        <v>177.5</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>60.08</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-64.45999999999999</v>
+        <v>-81.7</v>
       </c>
       <c r="L82" t="n">
-        <v>88.12</v>
+        <v>111.68</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-60.7</v>
+        <v>-77.58</v>
       </c>
       <c r="K83" t="n">
-        <v>-124.85</v>
+        <v>-159.59</v>
       </c>
       <c r="L83" t="n">
-        <v>138.82</v>
+        <v>177.44</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>181.29</v>
+        <v>228.31</v>
       </c>
       <c r="K84" t="n">
-        <v>-58.84</v>
+        <v>-74.11</v>
       </c>
       <c r="L84" t="n">
-        <v>190.6</v>
+        <v>240.04</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>135.89</v>
+        <v>167.08</v>
       </c>
       <c r="K85" t="n">
-        <v>146.88</v>
+        <v>180.6</v>
       </c>
       <c r="L85" t="n">
-        <v>200.1</v>
+        <v>246.03</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-205.36</v>
+        <v>-247.59</v>
       </c>
       <c r="K86" t="n">
-        <v>-287.25</v>
+        <v>-346.31</v>
       </c>
       <c r="L86" t="n">
-        <v>353.11</v>
+        <v>425.71</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>23.98</v>
+        <v>30.29</v>
       </c>
       <c r="K87" t="n">
-        <v>-210.31</v>
+        <v>-265.6</v>
       </c>
       <c r="L87" t="n">
-        <v>211.68</v>
+        <v>267.33</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>107.83</v>
+        <v>145.37</v>
       </c>
       <c r="K88" t="n">
-        <v>177.45</v>
+        <v>239.23</v>
       </c>
       <c r="L88" t="n">
-        <v>207.64</v>
+        <v>279.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-23.xlsx
+++ b/output/2025-04-23.xlsx
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>15.13</v>
       </c>
       <c r="K15" t="n">
-        <v>55.41</v>
+        <v>55.87</v>
       </c>
       <c r="L15" t="n">
-        <v>57.4</v>
+        <v>57.89</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>85.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="K16" t="n">
-        <v>-11.27</v>
+        <v>-13.07</v>
       </c>
       <c r="L16" t="n">
-        <v>85.84</v>
+        <v>99.56</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-94.54000000000001</v>
+        <v>-100.45</v>
       </c>
       <c r="K17" t="n">
-        <v>-37.12</v>
+        <v>-39.44</v>
       </c>
       <c r="L17" t="n">
-        <v>101.57</v>
+        <v>107.92</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>76.64</v>
+        <v>84.62</v>
       </c>
       <c r="K18" t="n">
-        <v>84.62</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>114.17</v>
+        <v>126.05</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>59.28</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-39.8</v>
+        <v>-43.62</v>
       </c>
       <c r="L19" t="n">
-        <v>71.41</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="K29" t="n">
-        <v>74.26000000000001</v>
+        <v>77.87</v>
       </c>
       <c r="L29" t="n">
-        <v>74.28</v>
+        <v>77.88</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-37.66</v>
+        <v>-38.78</v>
       </c>
       <c r="K30" t="n">
-        <v>-45.86</v>
+        <v>-47.23</v>
       </c>
       <c r="L30" t="n">
-        <v>59.34</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-35</v>
+        <v>-40.02</v>
       </c>
       <c r="K31" t="n">
-        <v>-59.94</v>
+        <v>-68.54000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>69.41</v>
+        <v>79.36</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-132.59</v>
+        <v>-148.4</v>
       </c>
       <c r="K32" t="n">
-        <v>-33.17</v>
+        <v>-37.12</v>
       </c>
       <c r="L32" t="n">
-        <v>136.67</v>
+        <v>152.97</v>
       </c>
     </row>
     <row r="33">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.92</v>
+        <v>-2.24</v>
       </c>
       <c r="K34" t="n">
-        <v>-59.46</v>
+        <v>-69.36</v>
       </c>
       <c r="L34" t="n">
-        <v>59.49</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>42.76</v>
+        <v>53.28</v>
       </c>
       <c r="K45" t="n">
-        <v>74.98</v>
+        <v>93.41</v>
       </c>
       <c r="L45" t="n">
-        <v>86.31</v>
+        <v>107.54</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-51.76</v>
+        <v>-84.36</v>
       </c>
       <c r="K46" t="n">
-        <v>-95</v>
+        <v>-154.84</v>
       </c>
       <c r="L46" t="n">
-        <v>108.18</v>
+        <v>176.33</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>80.8</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-27.83</v>
+        <v>-33.39</v>
       </c>
       <c r="L47" t="n">
-        <v>85.45999999999999</v>
+        <v>102.52</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>89.56</v>
+        <v>117.64</v>
       </c>
       <c r="K48" t="n">
-        <v>-65.97</v>
+        <v>-86.66</v>
       </c>
       <c r="L48" t="n">
-        <v>111.23</v>
+        <v>146.11</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-60.6</v>
+        <v>-73.94</v>
       </c>
       <c r="K49" t="n">
-        <v>-78.09</v>
+        <v>-95.28</v>
       </c>
       <c r="L49" t="n">
-        <v>98.84</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>8.82</v>
+        <v>10.53</v>
       </c>
       <c r="K59" t="n">
-        <v>86.61</v>
+        <v>103.38</v>
       </c>
       <c r="L59" t="n">
-        <v>87.06</v>
+        <v>103.91</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>64.87</v>
+        <v>79.67</v>
       </c>
       <c r="K60" t="n">
-        <v>76.73999999999999</v>
+        <v>94.25</v>
       </c>
       <c r="L60" t="n">
-        <v>100.48</v>
+        <v>123.42</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-65.78</v>
+        <v>-82.12</v>
       </c>
       <c r="K61" t="n">
-        <v>28.11</v>
+        <v>35.09</v>
       </c>
       <c r="L61" t="n">
-        <v>71.53</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-76.43000000000001</v>
+        <v>-78.97</v>
       </c>
       <c r="K62" t="n">
-        <v>-51.88</v>
+        <v>-53.6</v>
       </c>
       <c r="L62" t="n">
-        <v>92.37</v>
+        <v>95.45</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-73.05</v>
+        <v>-80.41</v>
       </c>
       <c r="K63" t="n">
-        <v>-10.53</v>
+        <v>-11.59</v>
       </c>
       <c r="L63" t="n">
-        <v>73.8</v>
+        <v>81.23999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>79.77</v>
+        <v>96.73</v>
       </c>
       <c r="K64" t="n">
-        <v>-79.8</v>
+        <v>-96.77</v>
       </c>
       <c r="L64" t="n">
-        <v>112.83</v>
+        <v>136.82</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>55.55</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-9.869999999999999</v>
+        <v>-13.05</v>
       </c>
       <c r="L74" t="n">
-        <v>56.42</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>42.16</v>
+        <v>66.98</v>
       </c>
       <c r="K75" t="n">
-        <v>93.89</v>
+        <v>149.13</v>
       </c>
       <c r="L75" t="n">
-        <v>102.92</v>
+        <v>163.48</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.82</v>
+        <v>-26.36</v>
       </c>
       <c r="K76" t="n">
-        <v>96.04000000000001</v>
+        <v>116.04</v>
       </c>
       <c r="L76" t="n">
-        <v>98.48</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-20.09</v>
+        <v>-23.33</v>
       </c>
       <c r="K77" t="n">
-        <v>-118.71</v>
+        <v>-137.85</v>
       </c>
       <c r="L77" t="n">
-        <v>120.4</v>
+        <v>139.81</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-24.94</v>
+        <v>-27.66</v>
       </c>
       <c r="K78" t="n">
-        <v>79.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>83.51000000000001</v>
+        <v>92.62</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>98.11</v>
+        <v>120.27</v>
       </c>
       <c r="K79" t="n">
-        <v>-59.56</v>
+        <v>-73.01000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>114.78</v>
+        <v>140.69</v>
       </c>
     </row>
     <row r="80">
